--- a/Kỹ Thuật lập trình/C/05. PREPROCESSOR & COMPILATION.xlsx
+++ b/Kỹ Thuật lập trình/C/05. PREPROCESSOR & COMPILATION.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Mục Lục" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1421">
   <si>
     <t>🔄 PREPROCESSOR &amp; COMPILATION</t>
   </si>
@@ -3890,17 +3890,2228 @@
   <si>
     <t>XIV. CHEATSHEET VÀ QUICK REFERENCE</t>
   </si>
+  <si>
+    <t>1. Tổng quan về Quy trình Biên dịch (Compilation Process)</t>
+  </si>
+  <si>
+    <t>Quy trình biên dịch trong C là quá trình chuyển đổi mã nguồn từ ngôn ngữ bậc cao sang mã máy có thể thực thi. Quy trình này gồm 4 giai đoạn chính:</t>
+  </si>
+  <si>
+    <t>Source Code (.c) → Preprocessor → Compiler → Assembler → Linker → Executable</t>
+  </si>
+  <si>
+    <t>2. Các Giai đoạn Biên dịch (Compilation Stages)</t>
+  </si>
+  <si>
+    <t>2.1 Giai đoạn Tiền xử lý (Preprocessing Stage)</t>
+  </si>
+  <si>
+    <t>Khái niệm:</t>
+  </si>
+  <si>
+    <t>Giai đoạn đầu tiên của quy trình biên dịch</t>
+  </si>
+  <si>
+    <t>Xử lý các chỉ thị tiền xử lý (preprocessor directives)</t>
+  </si>
+  <si>
+    <t>Chức năng chính:</t>
+  </si>
+  <si>
+    <t>Ví dụ thực tế:</t>
+  </si>
+  <si>
+    <t>// File: hello.c</t>
+  </si>
+  <si>
+    <t>#define PI 3.14159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #define LOG(x) printf("Debug: %s\n", x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #define LOG(x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    LOG("Program started");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Value of PI: %f\n", PI);</t>
+  </si>
+  <si>
+    <t>Lệnh xem output preprocessing:</t>
+  </si>
+  <si>
+    <t>gcc -E hello.c -o hello.i</t>
+  </si>
+  <si>
+    <t>cpp hello.c &gt; hello.i</t>
+  </si>
+  <si>
+    <t>Kết quả sau preprocessing:</t>
+  </si>
+  <si>
+    <t>2.2 Giai đoạn Biên dịch sang Assembly (Compilation to Assembly)</t>
+  </si>
+  <si>
+    <t>Chuyển đổi mã C đã tiền xử lý thành mã assembly</t>
+  </si>
+  <si>
+    <t>Thực hiện các tối ưu hóa (optimization)</t>
+  </si>
+  <si>
+    <t>Chức năng:</t>
+  </si>
+  <si>
+    <t>Lệnh tạo assembly code:</t>
+  </si>
+  <si>
+    <t>gcc -S hello.c -o hello.s</t>
+  </si>
+  <si>
+    <t>Ví dụ mã assembly (x86-64):</t>
+  </si>
+  <si>
+    <t>.section .data</t>
+  </si>
+  <si>
+    <t>format: .string "Value of PI: %f\n"</t>
+  </si>
+  <si>
+    <t>.section .text</t>
+  </si>
+  <si>
+    <t>.globl main</t>
+  </si>
+  <si>
+    <t>main:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    pushq %rbp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movq %rsp, %rbp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movsd .LC0(%rip), %xmm0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    leaq format(%rip), %rdi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    call printf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl $0, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    popq %rbp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ret</t>
+  </si>
+  <si>
+    <t>2.3 Giai đoạn Assembly sang Object Code (Assembly to Object Code)</t>
+  </si>
+  <si>
+    <t>Chuyển đổi mã assembly thành mã máy</t>
+  </si>
+  <si>
+    <t>Mã nhị phân nhưng chưa thể thực thi độc lập</t>
+  </si>
+  <si>
+    <t>Lệnh tạo object file:</t>
+  </si>
+  <si>
+    <t>gcc -c hello.c -o hello.o</t>
+  </si>
+  <si>
+    <t># hoặc từ assembly</t>
+  </si>
+  <si>
+    <t>as hello.s -o hello.o</t>
+  </si>
+  <si>
+    <t>Cấu trúc Object File (.o):</t>
+  </si>
+  <si>
+    <t>Xem nội dung object file:</t>
+  </si>
+  <si>
+    <t>objdump -d hello.o        # Disassemble</t>
+  </si>
+  <si>
+    <t>nm hello.o                # Symbol table</t>
+  </si>
+  <si>
+    <t>readelf -a hello.o        # Detailed info</t>
+  </si>
+  <si>
+    <t>2.4 Giai đoạn Liên kết (Linking Stage)</t>
+  </si>
+  <si>
+    <t>Kết hợp các object files và libraries</t>
+  </si>
+  <si>
+    <t>Giải quyết external references</t>
+  </si>
+  <si>
+    <t>Tạo ra executable file cuối cùng</t>
+  </si>
+  <si>
+    <t>Lệnh linking:</t>
+  </si>
+  <si>
+    <t>gcc hello.o -o hello</t>
+  </si>
+  <si>
+    <t># hoặc sử dụng linker trực tiếp</t>
+  </si>
+  <si>
+    <t>ld hello.o -lc -o hello</t>
+  </si>
+  <si>
+    <t>3. Các Tùy chọn Compiler (Compiler Options)</t>
+  </si>
+  <si>
+    <t>3.1 Warning Flags</t>
+  </si>
+  <si>
+    <t>-Wall (Warning All):</t>
+  </si>
+  <si>
+    <t>gcc -Wall program.c -o program</t>
+  </si>
+  <si>
+    <t>Bật các cảnh báo phổ biến:</t>
+  </si>
+  <si>
+    <t>Biến không sử dụng</t>
+  </si>
+  <si>
+    <t>Hàm không trả về giá trị</t>
+  </si>
+  <si>
+    <t>Comparison giữa signed và unsigned</t>
+  </si>
+  <si>
+    <t>Format string không khớp</t>
+  </si>
+  <si>
+    <t>-Wextra:</t>
+  </si>
+  <si>
+    <t>gcc -Wall -Wextra program.c -o program</t>
+  </si>
+  <si>
+    <t>Thêm các cảnh báo mở rộng:</t>
+  </si>
+  <si>
+    <t>Tham số hàm không sử dụng</t>
+  </si>
+  <si>
+    <t>So sánh với zero</t>
+  </si>
+  <si>
+    <t>Missing field initializers</t>
+  </si>
+  <si>
+    <t>Ví dụ code có warning:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int unused_var = 10;  // Warning: unused variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d\n", x);    // Warning: uninitialized variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return;               // Warning: return with no value</t>
+  </si>
+  <si>
+    <t>Các warning flags khác:</t>
+  </si>
+  <si>
+    <t>-Werror              # Treat warnings as errors</t>
+  </si>
+  <si>
+    <t>-Wno-unused-variable # Disable unused variable warning</t>
+  </si>
+  <si>
+    <t>-Wpedantic          # Strict ISO C compliance</t>
+  </si>
+  <si>
+    <t>-Wshadow            # Variable shadowing</t>
+  </si>
+  <si>
+    <t>-Wconversion        # Type conversions</t>
+  </si>
+  <si>
+    <t>3.2 Optimization Levels</t>
+  </si>
+  <si>
+    <t>-O0 (No Optimization - Default):</t>
+  </si>
+  <si>
+    <t>gcc -O0 program.c -o program</t>
+  </si>
+  <si>
+    <t>Không tối ưu hóa</t>
+  </si>
+  <si>
+    <t>Biên dịch nhanh nhất</t>
+  </si>
+  <si>
+    <t>Dễ debug nhất</t>
+  </si>
+  <si>
+    <t>Kích thước và tốc độ không tối ưu</t>
+  </si>
+  <si>
+    <t>-O1 (Basic Optimization):</t>
+  </si>
+  <si>
+    <t>gcc -O1 program.c -o program</t>
+  </si>
+  <si>
+    <t>Tối ưu hóa cơ bản:</t>
+  </si>
+  <si>
+    <t>Dead code elimination</t>
+  </si>
+  <si>
+    <t>Basic constant folding</t>
+  </si>
+  <si>
+    <t>Register allocation cải thiện</t>
+  </si>
+  <si>
+    <t>-O2 (Moderate Optimization - Recommended):</t>
+  </si>
+  <si>
+    <t>gcc -O2 program.c -o program</t>
+  </si>
+  <si>
+    <t>Tối ưu hóa vừa phải:</t>
+  </si>
+  <si>
+    <t>Function inlining</t>
+  </si>
+  <si>
+    <t>Loop optimization</t>
+  </si>
+  <si>
+    <t>Instruction scheduling</t>
+  </si>
+  <si>
+    <t>Common subexpression elimination</t>
+  </si>
+  <si>
+    <t>-O3 (Aggressive Optimization):</t>
+  </si>
+  <si>
+    <t>gcc -O3 program.c -o program</t>
+  </si>
+  <si>
+    <t>Tối ưu hóa mạnh:</t>
+  </si>
+  <si>
+    <t>Aggressive inlining</t>
+  </si>
+  <si>
+    <t>Vectorization</t>
+  </si>
+  <si>
+    <t>Loop unrolling</t>
+  </si>
+  <si>
+    <t>Inter-procedural optimization</t>
+  </si>
+  <si>
+    <t>-Os (Size Optimization):</t>
+  </si>
+  <si>
+    <t>gcc -Os program.c -o program</t>
+  </si>
+  <si>
+    <t>Tối ưu hóa kích thước:</t>
+  </si>
+  <si>
+    <t>Giảm kích thước executable</t>
+  </si>
+  <si>
+    <t>Thích hợp cho embedded systems</t>
+  </si>
+  <si>
+    <t>-Ofast (Maximum Performance):</t>
+  </si>
+  <si>
+    <t>gcc -Ofast program.c -o program</t>
+  </si>
+  <si>
+    <t>Bao gồm -O3 và các tối ưu hóa không tuân thủ chuẩn</t>
+  </si>
+  <si>
+    <t>Có thể thay đổi hành vi chương trình</t>
+  </si>
+  <si>
+    <t>3.3 Debug Information (-g)</t>
+  </si>
+  <si>
+    <t>Mục đích:</t>
+  </si>
+  <si>
+    <t>Tạo thông tin debug cho debugger (gdb)</t>
+  </si>
+  <si>
+    <t>Không ảnh hưởng đến logic chương trình</t>
+  </si>
+  <si>
+    <t>Tăng kích thước executable</t>
+  </si>
+  <si>
+    <t>Các mức debug:</t>
+  </si>
+  <si>
+    <t>gcc -g program.c -o program          # Debug info cơ bản</t>
+  </si>
+  <si>
+    <t>gcc -g3 program.c -o program         # Maximum debug info</t>
+  </si>
+  <si>
+    <t>gcc -ggdb program.c -o program       # GDB-specific info</t>
+  </si>
+  <si>
+    <t>Debug với gdb:</t>
+  </si>
+  <si>
+    <t>gcc -g -O0 program.c -o program      # Best for debugging</t>
+  </si>
+  <si>
+    <t>gdb ./program</t>
+  </si>
+  <si>
+    <t>Lệnh gdb cơ bản:</t>
+  </si>
+  <si>
+    <t>(gdb) break main        # Set breakpoint</t>
+  </si>
+  <si>
+    <t>(gdb) run              # Run program</t>
+  </si>
+  <si>
+    <t>(gdb) step             # Step into</t>
+  </si>
+  <si>
+    <t>(gdb) next             # Step over</t>
+  </si>
+  <si>
+    <t>(gdb) print variable   # Print value</t>
+  </si>
+  <si>
+    <t>(gdb) backtrace        # Show call stack</t>
+  </si>
+  <si>
+    <t>3.4 Standard Compliance</t>
+  </si>
+  <si>
+    <t>-std=c89 hoặc -std=c90:</t>
+  </si>
+  <si>
+    <t>gcc -std=c89 program.c -o program</t>
+  </si>
+  <si>
+    <t>Tuân thủ chuẩn C89/C90</t>
+  </si>
+  <si>
+    <t>Không hỗ trợ C99 features</t>
+  </si>
+  <si>
+    <t>-std=c99:</t>
+  </si>
+  <si>
+    <t>gcc -std=c99 program.c -o program</t>
+  </si>
+  <si>
+    <t>C99 features:</t>
+  </si>
+  <si>
+    <t>Variable declarations anywhere</t>
+  </si>
+  <si>
+    <t>for(int i=0; i&lt;n; i++)</t>
+  </si>
+  <si>
+    <t>Variable length arrays</t>
+  </si>
+  <si>
+    <t>-std=c11:</t>
+  </si>
+  <si>
+    <t>gcc -std=c11 program.c -o program</t>
+  </si>
+  <si>
+    <t>C11 features:</t>
+  </si>
+  <si>
+    <t>_Static_assert</t>
+  </si>
+  <si>
+    <t>_Generic</t>
+  </si>
+  <si>
+    <t>Thread support</t>
+  </si>
+  <si>
+    <t>Anonymous structs/unions</t>
+  </si>
+  <si>
+    <t>-std=c17 hoặc -std=c18:</t>
+  </si>
+  <si>
+    <t>gcc -std=c17 program.c -o program</t>
+  </si>
+  <si>
+    <t>Bug fixes cho C11</t>
+  </si>
+  <si>
+    <t>Không có features mới</t>
+  </si>
+  <si>
+    <t>4. Quy trình Liên kết (Linking Process)</t>
+  </si>
+  <si>
+    <t>4.1 Object Files (.o)</t>
+  </si>
+  <si>
+    <t>Đặc điểm:</t>
+  </si>
+  <si>
+    <t>Chứa mã máy đã biên dịch</t>
+  </si>
+  <si>
+    <t>Chứa symbol table</t>
+  </si>
+  <si>
+    <t>Chưa thể thực thi độc lập</t>
+  </si>
+  <si>
+    <t>Cần linking để tạo executable</t>
+  </si>
+  <si>
+    <t>Tạo và sử dụng object files:</t>
+  </si>
+  <si>
+    <t># Tạo object files</t>
+  </si>
+  <si>
+    <t>gcc -c main.c -o main.o</t>
+  </si>
+  <si>
+    <t>gcc -c utils.c -o utils.o</t>
+  </si>
+  <si>
+    <t># Link object files</t>
+  </si>
+  <si>
+    <t>gcc main.o utils.o -o program</t>
+  </si>
+  <si>
+    <t># Hoặc compile và link riêng biệt</t>
+  </si>
+  <si>
+    <t>gcc -c *.c           # Tạo tất cả .o files</t>
+  </si>
+  <si>
+    <t>gcc *.o -o program   # Link tất cả</t>
+  </si>
+  <si>
+    <t>// utils.h</t>
+  </si>
+  <si>
+    <t>4.2 Static Libraries (.a)</t>
+  </si>
+  <si>
+    <t>Archive của object files</t>
+  </si>
+  <si>
+    <t>Được nhúng vào executable khi linking</t>
+  </si>
+  <si>
+    <t>Không cần file library khi chạy</t>
+  </si>
+  <si>
+    <t>Tạo static library:</t>
+  </si>
+  <si>
+    <t># Compile to object files</t>
+  </si>
+  <si>
+    <t>gcc -c lib_func1.c -o lib_func1.o</t>
+  </si>
+  <si>
+    <t>gcc -c lib_func2.c -o lib_func2.o</t>
+  </si>
+  <si>
+    <t># Create static library</t>
+  </si>
+  <si>
+    <t>ar rcs libmylib.a lib_func1.o lib_func2.o</t>
+  </si>
+  <si>
+    <t># Link with static library</t>
+  </si>
+  <si>
+    <t>gcc main.c -L. -lmylib -o program</t>
+  </si>
+  <si>
+    <t>gcc main.c libmylib.a -o program</t>
+  </si>
+  <si>
+    <t>Ví dụ tạo math library:</t>
+  </si>
+  <si>
+    <t>// mathlib.c</t>
+  </si>
+  <si>
+    <t>int multiply(int a, int b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return a * b;</t>
+  </si>
+  <si>
+    <t>int divide(int a, int b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if(b != 0) return a / b;</t>
+  </si>
+  <si>
+    <t>// mathlib.h</t>
+  </si>
+  <si>
+    <t>#ifndef MATHLIB_H</t>
+  </si>
+  <si>
+    <t>#define MATHLIB_H</t>
+  </si>
+  <si>
+    <t>int multiply(int a, int b);</t>
+  </si>
+  <si>
+    <t>int divide(int a, int b);</t>
+  </si>
+  <si>
+    <t>#include "mathlib.h"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("5 * 3 = %d\n", multiply(5, 3));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("10 / 2 = %d\n", divide(10, 2));</t>
+  </si>
+  <si>
+    <t>Commands:</t>
+  </si>
+  <si>
+    <t>gcc -c mathlib.c -o mathlib.o</t>
+  </si>
+  <si>
+    <t>ar rcs libmath.a mathlib.o</t>
+  </si>
+  <si>
+    <t>gcc main.c -L. -lmath -o calculator</t>
+  </si>
+  <si>
+    <t>4.3 Dynamic Libraries (.so)</t>
+  </si>
+  <si>
+    <t>Shared Object files</t>
+  </si>
+  <si>
+    <t>Được tải khi runtime</t>
+  </si>
+  <si>
+    <t>Tiết kiệm memory và disk space</t>
+  </si>
+  <si>
+    <t>Có thể update library độc lập</t>
+  </si>
+  <si>
+    <t>Tạo dynamic library:</t>
+  </si>
+  <si>
+    <t># Compile with position independent code</t>
+  </si>
+  <si>
+    <t>gcc -fPIC -c lib_func.c -o lib_func.o</t>
+  </si>
+  <si>
+    <t># Create shared library</t>
+  </si>
+  <si>
+    <t>gcc -shared -o libmylib.so lib_func.o</t>
+  </si>
+  <si>
+    <t># Link with dynamic library</t>
+  </si>
+  <si>
+    <t># Run with library path</t>
+  </si>
+  <si>
+    <t>LD_LIBRARY_PATH=. ./program</t>
+  </si>
+  <si>
+    <t>So sánh Static vs Dynamic Libraries:</t>
+  </si>
+  <si>
+    <t>Aspect</t>
+  </si>
+  <si>
+    <t>Static Library</t>
+  </si>
+  <si>
+    <t>Dynamic Library</t>
+  </si>
+  <si>
+    <t>File extension</t>
+  </si>
+  <si>
+    <t>.a</t>
+  </si>
+  <si>
+    <t>.so</t>
+  </si>
+  <si>
+    <t>Linking time</t>
+  </si>
+  <si>
+    <t>Compile time</t>
+  </si>
+  <si>
+    <t>Runtime</t>
+  </si>
+  <si>
+    <t>Executable size</t>
+  </si>
+  <si>
+    <t>Lớn hơn</t>
+  </si>
+  <si>
+    <t>Nhỏ hơn</t>
+  </si>
+  <si>
+    <t>Memory usage</t>
+  </si>
+  <si>
+    <t>Cao hơn</t>
+  </si>
+  <si>
+    <t>Thấp hơn</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Nhanh hơn</t>
+  </si>
+  <si>
+    <t>Chậm hơn một chút</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>Dễ dàng</t>
+  </si>
+  <si>
+    <t>Cần distribute library</t>
+  </si>
+  <si>
+    <t>Updates</t>
+  </si>
+  <si>
+    <t>Cần recompile</t>
+  </si>
+  <si>
+    <t>Có thể update riêng</t>
+  </si>
+  <si>
+    <t>4.4 Symbol Resolution</t>
+  </si>
+  <si>
+    <t>Quá trình tìm và liên kết các symbol references</t>
+  </si>
+  <si>
+    <t>Giải quyết external function calls</t>
+  </si>
+  <si>
+    <t>Xử lý global variables</t>
+  </si>
+  <si>
+    <t>Các loại symbols:</t>
+  </si>
+  <si>
+    <t>Ví dụ symbol resolution:</t>
+  </si>
+  <si>
+    <t>// file1.c</t>
+  </si>
+  <si>
+    <t>extern int global_var;  // External symbol</t>
+  </si>
+  <si>
+    <t>static int local_var;   // Local symbol</t>
+  </si>
+  <si>
+    <t>void external_func();   // External symbol</t>
+  </si>
+  <si>
+    <t>void defined_func() {   // Defined symbol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    global_var = 10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    external_func();</t>
+  </si>
+  <si>
+    <t>// file2.c</t>
+  </si>
+  <si>
+    <t>int global_var = 0;     // Definition</t>
+  </si>
+  <si>
+    <t>void external_func() {  // Definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("External function called\n");</t>
+  </si>
+  <si>
+    <t>Xem symbols:</t>
+  </si>
+  <si>
+    <t>nm file.o                    # List symbols</t>
+  </si>
+  <si>
+    <t>objdump -t file.o           # Symbol table</t>
+  </si>
+  <si>
+    <t>readelf -s file.o           # ELF symbol table</t>
+  </si>
+  <si>
+    <t>Symbol types trong nm:</t>
+  </si>
+  <si>
+    <t>5. Bẫy thường gặp (Common Pitfalls)</t>
+  </si>
+  <si>
+    <t>5.1 Header Guard Issues</t>
+  </si>
+  <si>
+    <t>// Wrong - missing header guard</t>
+  </si>
+  <si>
+    <t>void func();</t>
+  </si>
+  <si>
+    <t>// Correct</t>
+  </si>
+  <si>
+    <t>5.2 Linking Order Issues</t>
+  </si>
+  <si>
+    <t># Wrong order - library before object</t>
+  </si>
+  <si>
+    <t>gcc -lm main.o -o program</t>
+  </si>
+  <si>
+    <t># Correct order - library after object</t>
+  </si>
+  <si>
+    <t>gcc main.o -lm -o program</t>
+  </si>
+  <si>
+    <t>5.3 Missing Library Path</t>
+  </si>
+  <si>
+    <t># Wrong - library not found</t>
+  </si>
+  <si>
+    <t>gcc main.c -lmylib -o program</t>
+  </si>
+  <si>
+    <t># Correct - specify library path</t>
+  </si>
+  <si>
+    <t>gcc main.c -L/path/to/lib -lmylib -o program</t>
+  </si>
+  <si>
+    <t>5.4 Optimization và Debug Conflicts</t>
+  </si>
+  <si>
+    <t># Bad for debugging</t>
+  </si>
+  <si>
+    <t>gcc -O3 -g program.c -o program</t>
+  </si>
+  <si>
+    <t># Good for debugging</t>
+  </si>
+  <si>
+    <t>gcc -O0 -g program.c -o program</t>
+  </si>
+  <si>
+    <t>5.5 Standard Mismatch</t>
+  </si>
+  <si>
+    <t>// C99 code compiled with C89</t>
+  </si>
+  <si>
+    <t>for(int i = 0; i &lt; 10; i++) { // Error in C89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // code</t>
+  </si>
+  <si>
+    <t>6. Ứng dụng thực tế (Practical Applications)</t>
+  </si>
+  <si>
+    <t>6.1 Makefile cho Multi-file Project</t>
+  </si>
+  <si>
+    <t>CC = gcc</t>
+  </si>
+  <si>
+    <t>CFLAGS = -Wall -Wextra -std=c99 -g</t>
+  </si>
+  <si>
+    <t>TARGET = myprogram</t>
+  </si>
+  <si>
+    <t>SOURCES = main.c utils.c math_lib.c</t>
+  </si>
+  <si>
+    <t>OBJECTS = $(SOURCES:.c=.o)</t>
+  </si>
+  <si>
+    <t>$(TARGET): $(OBJECTS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        $(CC) $(OBJECTS) -o $(TARGET)</t>
+  </si>
+  <si>
+    <t>%.o: %.c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        $(CC) $(CFLAGS) -c $&lt; -o $@</t>
+  </si>
+  <si>
+    <t>clean:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        rm -f $(OBJECTS) $(TARGET)</t>
+  </si>
+  <si>
+    <t>.PHONY: clean</t>
+  </si>
+  <si>
+    <t>6.2 Build Script Example</t>
+  </si>
+  <si>
+    <t>#!/bin/bash</t>
+  </si>
+  <si>
+    <t># build.sh</t>
+  </si>
+  <si>
+    <t># Compilation flags</t>
+  </si>
+  <si>
+    <t>CFLAGS="-Wall -Wextra -std=c99"</t>
+  </si>
+  <si>
+    <t>SOURCES="main.c utils.c"</t>
+  </si>
+  <si>
+    <t>TARGET="myapp"</t>
+  </si>
+  <si>
+    <t># Debug build</t>
+  </si>
+  <si>
+    <t>if [ "$1" = "debug" ]; then</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    gcc $CFLAGS -g -O0 $SOURCES -o ${TARGET}_debug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    echo "Debug build completed"</t>
+  </si>
+  <si>
+    <t># Release build</t>
+  </si>
+  <si>
+    <t>elif [ "$1" = "release" ]; then</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    gcc $CFLAGS -O2 -DNDEBUG $SOURCES -o $TARGET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    strip $TARGET  # Remove debug symbols</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    echo "Release build completed"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    echo "Usage: ./build.sh [debug|release]"</t>
+  </si>
+  <si>
+    <t>fi</t>
+  </si>
+  <si>
+    <t>6.3 Cross-compilation Example</t>
+  </si>
+  <si>
+    <t># For ARM architecture</t>
+  </si>
+  <si>
+    <t>arm-linux-gnueabi-gcc -Wall -O2 program.c -o program_arm</t>
+  </si>
+  <si>
+    <t># For Windows (using MinGW)</t>
+  </si>
+  <si>
+    <t>x86_64-w64-mingw32-gcc program.c -o program.exe</t>
+  </si>
+  <si>
+    <t>6.4 Performance Profiling</t>
+  </si>
+  <si>
+    <t># Compile with profiling support</t>
+  </si>
+  <si>
+    <t>gcc -pg -O2 program.c -o program</t>
+  </si>
+  <si>
+    <t># Run program to generate profile data</t>
+  </si>
+  <si>
+    <t>./program</t>
+  </si>
+  <si>
+    <t># Analyze with gprof</t>
+  </si>
+  <si>
+    <t>gprof program gmon.out &gt; profile.txt</t>
+  </si>
+  <si>
+    <t>7. Best Practices</t>
+  </si>
+  <si>
+    <t>7.1 Compilation Best Practices</t>
+  </si>
+  <si>
+    <t>Chọn optimization level phù hợp</t>
+  </si>
+  <si>
+    <t>Tách compilation và linking khi cần thiết</t>
+  </si>
+  <si>
+    <t>7.2 Project Organization</t>
+  </si>
+  <si>
+    <t>├── src/           # Source files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">├── include/       # Header files  </t>
+  </si>
+  <si>
+    <t>├── lib/           # Libraries</t>
+  </si>
+  <si>
+    <t>├── build/         # Build artifacts</t>
+  </si>
+  <si>
+    <t>├── Makefile       # Build script</t>
+  </si>
+  <si>
+    <t>└── README.md      # Documentation</t>
+  </si>
+  <si>
+    <t>7.3 Dependency Management</t>
+  </si>
+  <si>
+    <t>Sử dụng package managers (vcpkg, Conan)</t>
+  </si>
+  <si>
+    <t>Document dependencies rõ ràng</t>
+  </si>
+  <si>
+    <t>Version control cho libraries</t>
+  </si>
+  <si>
+    <t>Automated build và test</t>
+  </si>
+  <si>
+    <r>
+      <t>File inclusion:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chèn nội dung của header files (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Macro expansion:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thay thế macro definitions (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Conditional compilation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Xử lý các điều kiện (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#ifdef</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#ifndef</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Comment removal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Loại bỏ comments</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tất cả </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> được thay bằng nội dung file header</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>PI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> được thay bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>3.14159</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LOG(x)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> được expand theo điều kiện DEBUG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lexical analysis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Phân tích từ vựng</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Syntax analysis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Phân tích cú pháp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Semantic analysis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Phân tích ngữ nghĩa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Code generation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sinh mã assembly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Optimization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tối ưu hóa mã</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Instruction encoding:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mã hóa instructions thành binary</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Address calculation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tính toán địa chỉ tương đối</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Symbol table creation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tạo bảng ký hiệu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Symbol resolution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Giải quyết các ký hiệu chưa định nghĩa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Relocation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Điều chỉnh địa chỉ tuyệt đối</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Library linking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Liên kết thư viện</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Entry point setting:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thiết lập điểm vào chương trình</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> comments</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> type</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Defined symbols:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Symbols định nghĩa trong module hiện tại</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>External symbols:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Symbols được reference nhưng định nghĩa ở nơi khác</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Local symbols:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Symbols chỉ visible trong module hiện tại</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Text (code) section symbol</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Initialized data section symbol</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: BSS (uninitialized data) section symbol</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Undefined symbol (external reference)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Local symbols</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Luôn sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>-Wall -Wextra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>-g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho development builds</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tạo ra file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (intermediate file)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tạo ra file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (assembly file)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tạo ra file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (object file)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Text section:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chứa mã máy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BSS section:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chứa dữ liệu chưa khởi tạo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Relocation table:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thông tin relocate</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   Các section khác thường có (bạn chưa nhắc đến)</t>
+  </si>
+  <si>
+    <t>Khi chương trình chạy, hệ điều hành cấp bộ nhớ và gán = 0.</t>
+  </si>
+  <si>
+    <r>
+      <t>Data section:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chứa dữ liệu đã khởi tạo- </t>
+    </r>
+  </si>
+  <si>
+    <t>Kích thước: Xác định trong file object vì đã có giá trị ban đầu.</t>
+  </si>
+  <si>
+    <t>Tên biến, hàm, địa chỉ, kích thước, loại (function, object...).</t>
+  </si>
+  <si>
+    <r>
+      <t>Symbol table:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bảng ký hiệu, Chứa:</t>
+    </r>
+  </si>
+  <si>
+    <t>Ví dụ:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Không chiếm dung lượng trong file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (chỉ lưu kích thước).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng cho </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>linker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để liên kết nhiều object file.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Chứa gì:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Các thông tin để linker biết phải thay đổi (relocate) địa chỉ nào khi ghép nhiều </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thành executable.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.text</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, khi gọi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>printf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, compiler chưa biết địa chỉ chính xác → relocation record đánh dấu chỗ cần sửa.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>.rodata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: dữ liệu chỉ đọc (const, literal string).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>.comment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: thông tin version của compiler.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>.debug_*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: chứa thông tin debug (khi biên dịch với </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>-g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>.shstrtab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bảng tên các section.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SONAME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (vd: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>libmylib.so.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) để tách </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ABI major</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; tăng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>1 → 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>break ABI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Symlink thường: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>libmylib.so → libmylib.so.1 → libmylib.so.1.0.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thay thế binary an toàn nếu </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>giữ nguyên ABI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>ABI &amp; versioning -&gt; Không cần rebuild là ở đây</t>
+  </si>
+  <si>
+    <t>thực tế nếu chỉ sửa file.a thì không cần rebuild lại hết, chỉ cần build lại.a và linking lại.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> .so thậm chí không cần linking lại (điều này đúng với các thay đổi giữ nguyên file header.h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nói về rebuild ở đây là quá trình linking là chính xác nhất, </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4009,8 +6220,29 @@
       <name val="Arial Unicode MS"/>
       <charset val="163"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4035,8 +6267,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -4096,18 +6340,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4116,15 +6397,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4133,58 +6414,115 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5352,20 +7690,20 @@
       <c r="AW58" s="25"/>
     </row>
     <row r="59" spans="1:49">
-      <c r="Q59" s="34"/>
-      <c r="R59" s="34"/>
-      <c r="S59" s="34"/>
-      <c r="T59" s="34"/>
-      <c r="U59" s="34"/>
-      <c r="V59" s="34"/>
-      <c r="W59" s="34"/>
-      <c r="X59" s="34"/>
-      <c r="Y59" s="34"/>
-      <c r="Z59" s="34"/>
-      <c r="AA59" s="34"/>
-      <c r="AB59" s="34"/>
-      <c r="AC59" s="34"/>
-      <c r="AD59" s="34"/>
+      <c r="Q59" s="36"/>
+      <c r="R59" s="36"/>
+      <c r="S59" s="36"/>
+      <c r="T59" s="36"/>
+      <c r="U59" s="36"/>
+      <c r="V59" s="36"/>
+      <c r="W59" s="36"/>
+      <c r="X59" s="36"/>
+      <c r="Y59" s="36"/>
+      <c r="Z59" s="36"/>
+      <c r="AA59" s="36"/>
+      <c r="AB59" s="36"/>
+      <c r="AC59" s="36"/>
+      <c r="AD59" s="36"/>
       <c r="AI59" s="26"/>
       <c r="AJ59" s="25"/>
       <c r="AK59" s="25"/>
@@ -5397,24 +7735,24 @@
       <c r="J60" s="19"/>
       <c r="K60" s="19"/>
       <c r="L60" s="19"/>
-      <c r="Q60" s="35" t="s">
+      <c r="Q60" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="R60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="T60" s="35"/>
-      <c r="U60" s="35"/>
-      <c r="V60" s="35"/>
-      <c r="W60" s="35"/>
-      <c r="X60" s="35" t="s">
+      <c r="R60" s="37"/>
+      <c r="S60" s="37"/>
+      <c r="T60" s="37"/>
+      <c r="U60" s="37"/>
+      <c r="V60" s="37"/>
+      <c r="W60" s="37"/>
+      <c r="X60" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="Y60" s="35"/>
-      <c r="Z60" s="35"/>
-      <c r="AA60" s="35"/>
-      <c r="AB60" s="35"/>
-      <c r="AC60" s="35"/>
-      <c r="AD60" s="35"/>
+      <c r="Y60" s="37"/>
+      <c r="Z60" s="37"/>
+      <c r="AA60" s="37"/>
+      <c r="AB60" s="37"/>
+      <c r="AC60" s="37"/>
+      <c r="AD60" s="37"/>
       <c r="AI60" s="26"/>
       <c r="AJ60" s="25"/>
       <c r="AK60" s="25"/>
@@ -5435,24 +7773,24 @@
       <c r="B61" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="Q61" s="33" t="s">
+      <c r="Q61" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="R61" s="33"/>
-      <c r="S61" s="33"/>
-      <c r="T61" s="33"/>
-      <c r="U61" s="33"/>
-      <c r="V61" s="33"/>
-      <c r="W61" s="33"/>
-      <c r="X61" s="33" t="s">
+      <c r="R61" s="35"/>
+      <c r="S61" s="35"/>
+      <c r="T61" s="35"/>
+      <c r="U61" s="35"/>
+      <c r="V61" s="35"/>
+      <c r="W61" s="35"/>
+      <c r="X61" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="Y61" s="33"/>
-      <c r="Z61" s="33"/>
-      <c r="AA61" s="33"/>
-      <c r="AB61" s="33"/>
-      <c r="AC61" s="33"/>
-      <c r="AD61" s="33"/>
+      <c r="Y61" s="35"/>
+      <c r="Z61" s="35"/>
+      <c r="AA61" s="35"/>
+      <c r="AB61" s="35"/>
+      <c r="AC61" s="35"/>
+      <c r="AD61" s="35"/>
       <c r="AI61" s="25"/>
       <c r="AJ61" s="25"/>
       <c r="AK61" s="25"/>
@@ -5473,70 +7811,70 @@
       <c r="B62" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="Q62" s="33" t="s">
+      <c r="Q62" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="R62" s="33"/>
-      <c r="S62" s="33"/>
-      <c r="T62" s="33"/>
-      <c r="U62" s="33"/>
-      <c r="V62" s="33"/>
-      <c r="W62" s="33"/>
-      <c r="X62" s="33" t="s">
+      <c r="R62" s="35"/>
+      <c r="S62" s="35"/>
+      <c r="T62" s="35"/>
+      <c r="U62" s="35"/>
+      <c r="V62" s="35"/>
+      <c r="W62" s="35"/>
+      <c r="X62" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="Y62" s="33"/>
-      <c r="Z62" s="33"/>
-      <c r="AA62" s="33"/>
-      <c r="AB62" s="33"/>
-      <c r="AC62" s="33"/>
-      <c r="AD62" s="33"/>
+      <c r="Y62" s="35"/>
+      <c r="Z62" s="35"/>
+      <c r="AA62" s="35"/>
+      <c r="AB62" s="35"/>
+      <c r="AC62" s="35"/>
+      <c r="AD62" s="35"/>
     </row>
     <row r="63" spans="1:49" ht="14.25" customHeight="1">
       <c r="B63" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="Q63" s="33" t="s">
+      <c r="Q63" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="R63" s="33"/>
-      <c r="S63" s="33"/>
-      <c r="T63" s="33"/>
-      <c r="U63" s="33"/>
-      <c r="V63" s="33"/>
-      <c r="W63" s="33"/>
-      <c r="X63" s="33" t="s">
+      <c r="R63" s="35"/>
+      <c r="S63" s="35"/>
+      <c r="T63" s="35"/>
+      <c r="U63" s="35"/>
+      <c r="V63" s="35"/>
+      <c r="W63" s="35"/>
+      <c r="X63" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="Y63" s="33"/>
-      <c r="Z63" s="33"/>
-      <c r="AA63" s="33"/>
-      <c r="AB63" s="33"/>
-      <c r="AC63" s="33"/>
-      <c r="AD63" s="33"/>
+      <c r="Y63" s="35"/>
+      <c r="Z63" s="35"/>
+      <c r="AA63" s="35"/>
+      <c r="AB63" s="35"/>
+      <c r="AC63" s="35"/>
+      <c r="AD63" s="35"/>
     </row>
     <row r="64" spans="1:49" ht="18.75" customHeight="1">
       <c r="B64" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="Q64" s="33" t="s">
+      <c r="Q64" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="R64" s="33"/>
-      <c r="S64" s="33"/>
-      <c r="T64" s="33"/>
-      <c r="U64" s="33"/>
-      <c r="V64" s="33"/>
-      <c r="W64" s="33"/>
-      <c r="X64" s="33" t="s">
+      <c r="R64" s="35"/>
+      <c r="S64" s="35"/>
+      <c r="T64" s="35"/>
+      <c r="U64" s="35"/>
+      <c r="V64" s="35"/>
+      <c r="W64" s="35"/>
+      <c r="X64" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="Y64" s="33"/>
-      <c r="Z64" s="33"/>
-      <c r="AA64" s="33"/>
-      <c r="AB64" s="33"/>
-      <c r="AC64" s="33"/>
-      <c r="AD64" s="33"/>
+      <c r="Y64" s="35"/>
+      <c r="Z64" s="35"/>
+      <c r="AA64" s="35"/>
+      <c r="AB64" s="35"/>
+      <c r="AC64" s="35"/>
+      <c r="AD64" s="35"/>
     </row>
     <row r="65" spans="1:57">
       <c r="B65" s="11" t="s">
@@ -9615,10 +11953,10 @@
       <c r="AQ518" s="19"/>
     </row>
     <row r="519" spans="1:43" ht="15">
-      <c r="A519" s="36" t="s">
+      <c r="A519" s="34" t="s">
         <v>775</v>
       </c>
-      <c r="AI519" s="36" t="s">
+      <c r="AI519" s="34" t="s">
         <v>856</v>
       </c>
     </row>
@@ -10810,18 +13148,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="Q64:W64"/>
+    <mergeCell ref="Q59:W59"/>
+    <mergeCell ref="Q60:W60"/>
+    <mergeCell ref="Q61:W61"/>
+    <mergeCell ref="Q62:W62"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="X63:AD63"/>
     <mergeCell ref="X64:AD64"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="X61:AD61"/>
     <mergeCell ref="X62:AD62"/>
-    <mergeCell ref="Q64:W64"/>
-    <mergeCell ref="Q59:W59"/>
-    <mergeCell ref="Q60:W60"/>
-    <mergeCell ref="Q61:W61"/>
-    <mergeCell ref="Q62:W62"/>
-    <mergeCell ref="Q63:W63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -10830,10 +13168,2397 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:BW195"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="16384" width="3.125" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:75" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A1" s="14" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="2" spans="1:75">
+      <c r="A2" s="33" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="3" spans="1:75">
+      <c r="B3" s="11" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="4" spans="1:75" ht="15" thickBot="1"/>
+    <row r="5" spans="1:75" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A5" s="14" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="6" spans="1:75" ht="15">
+      <c r="A6" s="18" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="U6" s="18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
+      <c r="AI6" s="19"/>
+      <c r="AJ6" s="19"/>
+      <c r="AK6" s="19"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AP6" s="18" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AQ6" s="19"/>
+      <c r="AR6" s="19"/>
+      <c r="AS6" s="19"/>
+      <c r="AT6" s="19"/>
+      <c r="AU6" s="19"/>
+      <c r="AV6" s="19"/>
+      <c r="AW6" s="19"/>
+      <c r="AX6" s="19"/>
+      <c r="AY6" s="19"/>
+      <c r="AZ6" s="19"/>
+      <c r="BA6" s="19"/>
+      <c r="BB6" s="19"/>
+      <c r="BC6" s="19"/>
+      <c r="BD6" s="19"/>
+      <c r="BE6" s="19"/>
+      <c r="BF6" s="19"/>
+      <c r="BG6" s="19"/>
+      <c r="BH6" s="19"/>
+      <c r="BI6" s="19"/>
+      <c r="BM6" s="18" t="s">
+        <v>1059</v>
+      </c>
+      <c r="BN6" s="19"/>
+      <c r="BO6" s="19"/>
+      <c r="BP6" s="19"/>
+      <c r="BQ6" s="19"/>
+      <c r="BR6" s="19"/>
+      <c r="BS6" s="19"/>
+      <c r="BT6" s="19"/>
+      <c r="BU6" s="19"/>
+      <c r="BV6" s="19"/>
+      <c r="BW6" s="19"/>
+    </row>
+    <row r="7" spans="1:75" ht="15">
+      <c r="A7" s="45" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="U7" s="45" t="s">
+        <v>1012</v>
+      </c>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="AP7" s="45" t="s">
+        <v>1012</v>
+      </c>
+      <c r="AQ7" s="21"/>
+      <c r="AR7" s="21"/>
+      <c r="BM7" s="45" t="s">
+        <v>1012</v>
+      </c>
+      <c r="BN7" s="21"/>
+      <c r="BO7" s="21"/>
+    </row>
+    <row r="8" spans="1:75">
+      <c r="A8" s="12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="U8" s="12" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AP8" s="12" t="s">
+        <v>1048</v>
+      </c>
+      <c r="BM8" s="12" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="9" spans="1:75">
+      <c r="A9" s="12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="U9" s="23" t="s">
+        <v>1394</v>
+      </c>
+      <c r="AP9" s="23" t="s">
+        <v>1395</v>
+      </c>
+      <c r="BM9" s="12" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="10" spans="1:75">
+      <c r="A10" s="23" t="s">
+        <v>1393</v>
+      </c>
+      <c r="U10" s="23" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AP10" s="23" t="s">
+        <v>1049</v>
+      </c>
+      <c r="BM10" s="12" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="12" spans="1:75" ht="15">
+      <c r="A12" s="45" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="U12" s="45" t="s">
+        <v>1030</v>
+      </c>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="AP12" s="45" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AQ12" s="21"/>
+      <c r="AR12" s="21"/>
+      <c r="AS12" s="21"/>
+      <c r="BM12" s="45" t="s">
+        <v>1015</v>
+      </c>
+      <c r="BN12" s="21"/>
+      <c r="BO12" s="21"/>
+      <c r="BP12" s="21"/>
+      <c r="BQ12" s="21"/>
+    </row>
+    <row r="13" spans="1:75" ht="15">
+      <c r="A13" s="8" t="s">
+        <v>1362</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>1369</v>
+      </c>
+      <c r="AP13" s="8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="BM13" s="8" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="14" spans="1:75" ht="15">
+      <c r="A14" s="8" t="s">
+        <v>1363</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="AP14" s="8" t="s">
+        <v>1375</v>
+      </c>
+      <c r="BM14" s="8" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:75" ht="15">
+      <c r="A15" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>1371</v>
+      </c>
+      <c r="AP15" s="8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="BM15" s="8" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="16" spans="1:75" ht="15">
+      <c r="A16" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>1372</v>
+      </c>
+      <c r="BM16" s="8" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68" ht="15">
+      <c r="U17" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="AP17" s="45" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AQ17" s="21"/>
+      <c r="AR17" s="21"/>
+      <c r="AS17" s="21"/>
+      <c r="AT17" s="21"/>
+      <c r="AU17" s="21"/>
+    </row>
+    <row r="18" spans="1:68" ht="15">
+      <c r="A18" s="45" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="AQ18" s="11" t="s">
+        <v>1051</v>
+      </c>
+      <c r="BM18" s="45" t="s">
+        <v>1063</v>
+      </c>
+      <c r="BN18" s="21"/>
+      <c r="BO18" s="21"/>
+      <c r="BP18" s="21"/>
+    </row>
+    <row r="19" spans="1:68" ht="15">
+      <c r="B19" s="11" t="s">
+        <v>1017</v>
+      </c>
+      <c r="U19" s="45" t="s">
+        <v>1031</v>
+      </c>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="21"/>
+      <c r="AQ19" s="11" t="s">
+        <v>1052</v>
+      </c>
+      <c r="BN19" s="11" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="B20" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AQ20" s="11" t="s">
+        <v>1053</v>
+      </c>
+      <c r="BN20" s="11" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="B21" s="11" t="s">
+        <v>1018</v>
+      </c>
+      <c r="BN21" s="11" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68" ht="15">
+      <c r="B22" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="U22" s="45" t="s">
+        <v>1033</v>
+      </c>
+      <c r="V22" s="21"/>
+      <c r="W22" s="21"/>
+      <c r="X22" s="21"/>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="21"/>
+      <c r="AB22" s="21"/>
+      <c r="AP22" s="42" t="s">
+        <v>1054</v>
+      </c>
+      <c r="AQ22" s="22"/>
+      <c r="AR22" s="22"/>
+      <c r="AS22" s="22"/>
+    </row>
+    <row r="23" spans="1:68" ht="15">
+      <c r="B23" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AP23" s="39" t="s">
+        <v>1396</v>
+      </c>
+      <c r="AQ23" s="22"/>
+      <c r="AR23" s="22"/>
+      <c r="AS23" s="22"/>
+    </row>
+    <row r="24" spans="1:68" ht="15">
+      <c r="B24" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="V24" s="11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AP24" s="39" t="s">
+        <v>1401</v>
+      </c>
+      <c r="AQ24" s="22"/>
+      <c r="AR24" s="22"/>
+      <c r="AS24" s="22"/>
+    </row>
+    <row r="25" spans="1:68" ht="15">
+      <c r="B25" s="11" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AP25" s="39"/>
+      <c r="AQ25" s="22" t="s">
+        <v>1402</v>
+      </c>
+      <c r="AR25" s="22"/>
+      <c r="AS25" s="22"/>
+    </row>
+    <row r="26" spans="1:68" ht="15">
+      <c r="B26" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="U26" s="13"/>
+      <c r="V26" s="11" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AP26" s="39" t="s">
+        <v>1397</v>
+      </c>
+      <c r="AQ26" s="22"/>
+      <c r="AR26" s="22"/>
+      <c r="AS26" s="22"/>
+    </row>
+    <row r="27" spans="1:68" ht="15">
+      <c r="B27" s="13"/>
+      <c r="V27" s="11" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AP27" s="39"/>
+      <c r="AQ27" s="22" t="s">
+        <v>1406</v>
+      </c>
+      <c r="AR27" s="22"/>
+      <c r="AS27" s="22"/>
+    </row>
+    <row r="28" spans="1:68" ht="15">
+      <c r="B28" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="V28" s="11" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AP28" s="39"/>
+      <c r="AQ28" s="22" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AR28" s="22"/>
+      <c r="AS28" s="22"/>
+    </row>
+    <row r="29" spans="1:68" ht="15">
+      <c r="B29" s="11" t="s">
+        <v>1021</v>
+      </c>
+      <c r="V29" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AP29" s="39" t="s">
+        <v>1404</v>
+      </c>
+      <c r="AQ29" s="22"/>
+      <c r="AR29" s="22"/>
+      <c r="AS29" s="22"/>
+      <c r="AX29" s="41"/>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="B30" s="11" t="s">
+        <v>1022</v>
+      </c>
+      <c r="V30" s="11" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AP30" s="22"/>
+      <c r="AQ30" s="43" t="s">
+        <v>1403</v>
+      </c>
+      <c r="AR30" s="22"/>
+      <c r="AS30" s="22"/>
+    </row>
+    <row r="31" spans="1:68" ht="15">
+      <c r="B31" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="V31" s="11" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AP31" s="22"/>
+      <c r="AQ31" s="43" t="s">
+        <v>1407</v>
+      </c>
+      <c r="AR31" s="22"/>
+      <c r="AS31" s="22"/>
+    </row>
+    <row r="32" spans="1:68" ht="15">
+      <c r="B32" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="V32" s="11" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AP32" s="39" t="s">
+        <v>1398</v>
+      </c>
+      <c r="AQ32" s="22"/>
+      <c r="AR32" s="22"/>
+      <c r="AS32" s="22"/>
+    </row>
+    <row r="33" spans="1:59" ht="15">
+      <c r="V33" s="11" t="s">
+        <v>1043</v>
+      </c>
+      <c r="AP33" s="39"/>
+      <c r="AQ33" s="42" t="s">
+        <v>1408</v>
+      </c>
+      <c r="AR33" s="22"/>
+      <c r="AS33" s="22"/>
+    </row>
+    <row r="34" spans="1:59" ht="15">
+      <c r="A34" s="45" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="V34" s="11" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AP34" s="39"/>
+      <c r="AQ34" s="42" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AR34" s="22"/>
+      <c r="AS34" s="22"/>
+    </row>
+    <row r="35" spans="1:59" ht="15">
+      <c r="B35" s="11" t="s">
+        <v>1024</v>
+      </c>
+      <c r="V35" s="11" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AP35" s="39"/>
+      <c r="AQ35" s="23" t="s">
+        <v>1409</v>
+      </c>
+      <c r="AR35" s="22"/>
+      <c r="AS35" s="22"/>
+    </row>
+    <row r="36" spans="1:59" ht="15">
+      <c r="B36" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="V36" s="11" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AP36" s="40" t="s">
+        <v>1399</v>
+      </c>
+      <c r="AQ36" s="22"/>
+      <c r="AR36" s="22"/>
+      <c r="AS36" s="22"/>
+    </row>
+    <row r="37" spans="1:59">
+      <c r="B37" s="11" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AP37" s="22"/>
+      <c r="AQ37" s="44" t="s">
+        <v>1410</v>
+      </c>
+      <c r="AR37" s="22"/>
+      <c r="AS37" s="22"/>
+    </row>
+    <row r="38" spans="1:59">
+      <c r="AP38" s="22"/>
+      <c r="AQ38" s="44" t="s">
+        <v>1411</v>
+      </c>
+      <c r="AR38" s="22"/>
+      <c r="AS38" s="22"/>
+    </row>
+    <row r="39" spans="1:59">
+      <c r="AP39" s="22"/>
+      <c r="AQ39" s="44" t="s">
+        <v>1412</v>
+      </c>
+      <c r="AR39" s="22"/>
+      <c r="AS39" s="22"/>
+    </row>
+    <row r="40" spans="1:59" ht="15">
+      <c r="A40" s="45" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="AP40" s="22"/>
+      <c r="AQ40" s="44" t="s">
+        <v>1413</v>
+      </c>
+      <c r="AR40" s="22"/>
+      <c r="AS40" s="22"/>
+    </row>
+    <row r="41" spans="1:59">
+      <c r="A41" s="12" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="42" spans="1:59" ht="15">
+      <c r="A42" s="38" t="s">
+        <v>1367</v>
+      </c>
+      <c r="AP42" s="7" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="43" spans="1:59">
+      <c r="A43" s="38" t="s">
+        <v>1368</v>
+      </c>
+      <c r="AQ43" s="11" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="44" spans="1:59">
+      <c r="AQ44" s="11" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="45" spans="1:59">
+      <c r="AQ45" s="11" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="46" spans="1:59" ht="15" thickBot="1"/>
+    <row r="47" spans="1:59" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A47" s="14" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="48" spans="1:59" ht="15">
+      <c r="A48" s="18" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="S48" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="T48" s="19"/>
+      <c r="U48" s="19"/>
+      <c r="V48" s="19"/>
+      <c r="W48" s="19"/>
+      <c r="X48" s="19"/>
+      <c r="Y48" s="19"/>
+      <c r="AI48" s="18" t="s">
+        <v>1129</v>
+      </c>
+      <c r="AJ48" s="19"/>
+      <c r="AK48" s="19"/>
+      <c r="AL48" s="19"/>
+      <c r="AM48" s="19"/>
+      <c r="AN48" s="19"/>
+      <c r="AO48" s="19"/>
+      <c r="AP48" s="19"/>
+      <c r="BA48" s="18" t="s">
+        <v>1148</v>
+      </c>
+      <c r="BB48" s="19"/>
+      <c r="BC48" s="19"/>
+      <c r="BD48" s="19"/>
+      <c r="BE48" s="19"/>
+      <c r="BF48" s="19"/>
+      <c r="BG48" s="19"/>
+    </row>
+    <row r="49" spans="1:54" ht="15">
+      <c r="A49" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AI49" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="BA49" s="7" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:54">
+      <c r="B50" s="11" t="s">
+        <v>1070</v>
+      </c>
+      <c r="T50" s="11" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AI50" s="12" t="s">
+        <v>1131</v>
+      </c>
+      <c r="BB50" s="11" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:54">
+      <c r="AI51" s="12" t="s">
+        <v>1132</v>
+      </c>
+      <c r="BB51" s="12" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:54">
+      <c r="A52" s="33" t="s">
+        <v>1071</v>
+      </c>
+      <c r="S52" s="12" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AI52" s="12" t="s">
+        <v>1133</v>
+      </c>
+      <c r="BB52" s="12" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:54">
+      <c r="A53" s="12" t="s">
+        <v>1072</v>
+      </c>
+      <c r="S53" s="12" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="54" spans="1:54" ht="15">
+      <c r="A54" s="12" t="s">
+        <v>1073</v>
+      </c>
+      <c r="S54" s="12" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AI54" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="BA54" s="7" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="55" spans="1:54">
+      <c r="A55" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="S55" s="12" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AJ55" s="11" t="s">
+        <v>1135</v>
+      </c>
+      <c r="BB55" s="11" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:54">
+      <c r="A56" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AJ56" s="11" t="s">
+        <v>1136</v>
+      </c>
+      <c r="BB56" s="33" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:54">
+      <c r="AJ57" s="11" t="s">
+        <v>1137</v>
+      </c>
+      <c r="BB57" s="38" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="58" spans="1:54" ht="15">
+      <c r="A58" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="S58" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="BB58" s="12" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:54" ht="15">
+      <c r="B59" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="T59" s="11" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AI59" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="BB59" s="38" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="60" spans="1:54">
+      <c r="AJ60" s="11" t="s">
+        <v>1139</v>
+      </c>
+      <c r="BB60" s="38" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="61" spans="1:54">
+      <c r="A61" s="33" t="s">
+        <v>1078</v>
+      </c>
+      <c r="S61" s="33" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AJ61" s="11" t="s">
+        <v>1140</v>
+      </c>
+      <c r="BB61" s="12" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="62" spans="1:54">
+      <c r="A62" s="12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="S62" s="12" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="63" spans="1:54" ht="15">
+      <c r="A63" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="S63" s="12" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AI63" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="BA63" s="7" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:54">
+      <c r="A64" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="S64" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AJ64" s="11" t="s">
+        <v>1142</v>
+      </c>
+      <c r="BB64" s="11" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:54">
+      <c r="AJ65" s="11" t="s">
+        <v>1143</v>
+      </c>
+      <c r="BB65" s="46" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:54" ht="15">
+      <c r="A66" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="S66" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AJ66" s="11" t="s">
+        <v>1144</v>
+      </c>
+      <c r="BB66" s="38" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="67" spans="1:54">
+      <c r="B67" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="T67" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AJ67" s="11" t="s">
+        <v>1145</v>
+      </c>
+      <c r="BB67" s="38" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="68" spans="1:54">
+      <c r="B68" s="13"/>
+      <c r="AJ68" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="BB68" s="12" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="69" spans="1:54">
+      <c r="B69" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="S69" s="33" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AJ69" s="11" t="s">
+        <v>1147</v>
+      </c>
+      <c r="BB69" s="12" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="70" spans="1:54">
+      <c r="B70" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="S70" s="12" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="71" spans="1:54" ht="15">
+      <c r="B71" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="S71" s="12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="BA71" s="7" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:54">
+      <c r="B72" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="S72" s="12" t="s">
+        <v>1111</v>
+      </c>
+      <c r="BB72" s="11" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:54">
+      <c r="B73" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="S73" s="12" t="s">
+        <v>1112</v>
+      </c>
+      <c r="BB73" s="12" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="74" spans="1:54">
+      <c r="B74" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB74" s="12" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="75" spans="1:54" ht="15">
+      <c r="S75" s="7" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:54" ht="15">
+      <c r="A76" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="T76" s="11" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="77" spans="1:54">
+      <c r="B77" s="11" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="78" spans="1:54">
+      <c r="B78" s="11" t="s">
+        <v>1089</v>
+      </c>
+      <c r="S78" s="33" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="79" spans="1:54">
+      <c r="B79" s="11" t="s">
+        <v>1090</v>
+      </c>
+      <c r="S79" s="12" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="80" spans="1:54">
+      <c r="B80" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="S80" s="12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="81" spans="2:20">
+      <c r="B81" s="11" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S81" s="12" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="82" spans="2:20">
+      <c r="S82" s="12" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="84" spans="2:20" ht="15">
+      <c r="S84" s="7" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="85" spans="2:20">
+      <c r="T85" s="11" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="87" spans="2:20">
+      <c r="S87" s="33" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="88" spans="2:20">
+      <c r="S88" s="12" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="89" spans="2:20">
+      <c r="S89" s="12" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="91" spans="2:20" ht="15">
+      <c r="S91" s="7" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="92" spans="2:20">
+      <c r="T92" s="11" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="93" spans="2:20">
+      <c r="S93" s="12"/>
+    </row>
+    <row r="94" spans="2:20">
+      <c r="S94" s="12" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="95" spans="2:20">
+      <c r="S95" s="12" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="96" spans="2:20" ht="15" thickBot="1"/>
+    <row r="97" spans="1:59" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A97" s="14" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:59" ht="15">
+      <c r="A98" s="18" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B98" s="19"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="19"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="19"/>
+      <c r="P98" s="18" t="s">
+        <v>1187</v>
+      </c>
+      <c r="Q98" s="19"/>
+      <c r="R98" s="19"/>
+      <c r="S98" s="19"/>
+      <c r="T98" s="19"/>
+      <c r="U98" s="19"/>
+      <c r="V98" s="19"/>
+      <c r="AE98" s="18" t="s">
+        <v>1218</v>
+      </c>
+      <c r="AF98" s="19"/>
+      <c r="AG98" s="19"/>
+      <c r="AH98" s="19"/>
+      <c r="AI98" s="19"/>
+      <c r="AJ98" s="19"/>
+      <c r="AK98" s="19"/>
+      <c r="AL98" s="19"/>
+      <c r="BA98" s="18" t="s">
+        <v>1256</v>
+      </c>
+      <c r="BB98" s="19"/>
+      <c r="BC98" s="19"/>
+      <c r="BD98" s="19"/>
+      <c r="BE98" s="19"/>
+      <c r="BF98" s="19"/>
+      <c r="BG98" s="19"/>
+    </row>
+    <row r="99" spans="1:59" ht="15">
+      <c r="A99" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="P99" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="AE99" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="BA99" s="7" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="100" spans="1:59">
+      <c r="A100" s="12" t="s">
+        <v>1173</v>
+      </c>
+      <c r="P100" s="12" t="s">
+        <v>1188</v>
+      </c>
+      <c r="AE100" s="12" t="s">
+        <v>1219</v>
+      </c>
+      <c r="BA100" s="12" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="101" spans="1:59">
+      <c r="A101" s="12" t="s">
+        <v>1174</v>
+      </c>
+      <c r="P101" s="12" t="s">
+        <v>1189</v>
+      </c>
+      <c r="AE101" s="12" t="s">
+        <v>1220</v>
+      </c>
+      <c r="BA101" s="12" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="102" spans="1:59">
+      <c r="A102" s="12" t="s">
+        <v>1175</v>
+      </c>
+      <c r="P102" s="12" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AE102" s="12" t="s">
+        <v>1221</v>
+      </c>
+      <c r="BA102" s="12" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="103" spans="1:59">
+      <c r="A103" s="12" t="s">
+        <v>1176</v>
+      </c>
+      <c r="P103" s="12" t="s">
+        <v>1190</v>
+      </c>
+      <c r="AE103" s="12" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="104" spans="1:59" ht="15">
+      <c r="BA104" s="7" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="105" spans="1:59" ht="15">
+      <c r="A105" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="P105" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="BA105" s="8" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="106" spans="1:59" ht="15">
+      <c r="B106" s="11" t="s">
+        <v>1178</v>
+      </c>
+      <c r="Q106" s="11" t="s">
+        <v>1192</v>
+      </c>
+      <c r="AE106" s="7" t="s">
+        <v>1223</v>
+      </c>
+      <c r="BA106" s="8" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="107" spans="1:59" ht="15">
+      <c r="B107" s="11" t="s">
+        <v>1179</v>
+      </c>
+      <c r="Q107" s="11" t="s">
+        <v>1193</v>
+      </c>
+      <c r="AF107" s="11" t="s">
+        <v>1224</v>
+      </c>
+      <c r="BA107" s="8" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="108" spans="1:59">
+      <c r="B108" s="11" t="s">
+        <v>1180</v>
+      </c>
+      <c r="Q108" s="11" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AF108" s="11" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="109" spans="1:59" ht="15">
+      <c r="B109" s="13"/>
+      <c r="Q109" s="13"/>
+      <c r="AF109" s="13"/>
+      <c r="BA109" s="7" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="110" spans="1:59">
+      <c r="B110" s="11" t="s">
+        <v>1181</v>
+      </c>
+      <c r="Q110" s="11" t="s">
+        <v>1195</v>
+      </c>
+      <c r="AF110" s="11" t="s">
+        <v>1226</v>
+      </c>
+      <c r="BA110" s="11" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="111" spans="1:59">
+      <c r="B111" s="11" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Q111" s="11" t="s">
+        <v>1196</v>
+      </c>
+      <c r="AF111" s="11" t="s">
+        <v>1227</v>
+      </c>
+      <c r="BA111" s="11" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="112" spans="1:59">
+      <c r="B112" s="13"/>
+      <c r="Q112" s="13"/>
+      <c r="AF112" s="13"/>
+      <c r="BA112" s="11" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="113" spans="2:53">
+      <c r="B113" s="11" t="s">
+        <v>1183</v>
+      </c>
+      <c r="Q113" s="11" t="s">
+        <v>1197</v>
+      </c>
+      <c r="AF113" s="11" t="s">
+        <v>1228</v>
+      </c>
+      <c r="BA113" s="13"/>
+    </row>
+    <row r="114" spans="2:53">
+      <c r="B114" s="11" t="s">
+        <v>1184</v>
+      </c>
+      <c r="Q114" s="11" t="s">
+        <v>1198</v>
+      </c>
+      <c r="AF114" s="11" t="s">
+        <v>1198</v>
+      </c>
+      <c r="BA114" s="11" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="115" spans="2:53">
+      <c r="B115" s="11" t="s">
+        <v>1185</v>
+      </c>
+      <c r="Q115" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF115" s="13"/>
+      <c r="BA115" s="13"/>
+    </row>
+    <row r="116" spans="2:53">
+      <c r="Q116" s="11" t="s">
+        <v>1199</v>
+      </c>
+      <c r="AF116" s="11" t="s">
+        <v>1229</v>
+      </c>
+      <c r="BA116" s="11" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="117" spans="2:53">
+      <c r="AF117" s="11" t="s">
+        <v>1230</v>
+      </c>
+      <c r="BA117" s="11" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="118" spans="2:53" ht="15">
+      <c r="P118" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="BA118" s="11" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="119" spans="2:53" ht="15">
+      <c r="Q119" s="11" t="s">
+        <v>1201</v>
+      </c>
+      <c r="AE119" s="7" t="s">
+        <v>1231</v>
+      </c>
+      <c r="BA119" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="120" spans="2:53" ht="15">
+      <c r="Q120" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="AG120" s="48" t="s">
+        <v>1232</v>
+      </c>
+      <c r="AH120" s="49"/>
+      <c r="AI120" s="49"/>
+      <c r="AJ120" s="49"/>
+      <c r="AK120" s="50"/>
+      <c r="AL120" s="48" t="s">
+        <v>1233</v>
+      </c>
+      <c r="AM120" s="49"/>
+      <c r="AN120" s="49"/>
+      <c r="AO120" s="49"/>
+      <c r="AP120" s="50"/>
+      <c r="AQ120" s="48" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AR120" s="49"/>
+      <c r="AS120" s="49"/>
+      <c r="AT120" s="49"/>
+      <c r="AU120" s="49"/>
+      <c r="AV120" s="49"/>
+      <c r="AW120" s="50"/>
+      <c r="BA120" s="13"/>
+    </row>
+    <row r="121" spans="2:53">
+      <c r="Q121" s="11" t="s">
+        <v>1203</v>
+      </c>
+      <c r="AG121" s="51" t="s">
+        <v>1235</v>
+      </c>
+      <c r="AH121" s="52"/>
+      <c r="AI121" s="52"/>
+      <c r="AJ121" s="52"/>
+      <c r="AK121" s="53"/>
+      <c r="AL121" s="54" t="s">
+        <v>1236</v>
+      </c>
+      <c r="AM121" s="55"/>
+      <c r="AN121" s="55"/>
+      <c r="AO121" s="55"/>
+      <c r="AP121" s="56"/>
+      <c r="AQ121" s="54" t="s">
+        <v>1237</v>
+      </c>
+      <c r="AR121" s="55"/>
+      <c r="AS121" s="55"/>
+      <c r="AT121" s="55"/>
+      <c r="AU121" s="55"/>
+      <c r="AV121" s="55"/>
+      <c r="AW121" s="56"/>
+      <c r="BA121" s="11" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="122" spans="2:53">
+      <c r="Q122" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG122" s="51" t="s">
+        <v>1238</v>
+      </c>
+      <c r="AH122" s="52"/>
+      <c r="AI122" s="52"/>
+      <c r="AJ122" s="52"/>
+      <c r="AK122" s="53"/>
+      <c r="AL122" s="51" t="s">
+        <v>1239</v>
+      </c>
+      <c r="AM122" s="52"/>
+      <c r="AN122" s="52"/>
+      <c r="AO122" s="52"/>
+      <c r="AP122" s="53"/>
+      <c r="AQ122" s="51" t="s">
+        <v>1240</v>
+      </c>
+      <c r="AR122" s="52"/>
+      <c r="AS122" s="52"/>
+      <c r="AT122" s="52"/>
+      <c r="AU122" s="52"/>
+      <c r="AV122" s="52"/>
+      <c r="AW122" s="53"/>
+      <c r="BA122" s="11" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="123" spans="2:53">
+      <c r="Q123" s="13"/>
+      <c r="AG123" s="51" t="s">
+        <v>1241</v>
+      </c>
+      <c r="AH123" s="52"/>
+      <c r="AI123" s="52"/>
+      <c r="AJ123" s="52"/>
+      <c r="AK123" s="53"/>
+      <c r="AL123" s="51" t="s">
+        <v>1242</v>
+      </c>
+      <c r="AM123" s="52"/>
+      <c r="AN123" s="52"/>
+      <c r="AO123" s="52"/>
+      <c r="AP123" s="53"/>
+      <c r="AQ123" s="51" t="s">
+        <v>1243</v>
+      </c>
+      <c r="AR123" s="52"/>
+      <c r="AS123" s="52"/>
+      <c r="AT123" s="52"/>
+      <c r="AU123" s="52"/>
+      <c r="AV123" s="52"/>
+      <c r="AW123" s="53"/>
+      <c r="BA123" s="13"/>
+    </row>
+    <row r="124" spans="2:53">
+      <c r="Q124" s="11" t="s">
+        <v>1204</v>
+      </c>
+      <c r="AG124" s="51" t="s">
+        <v>1244</v>
+      </c>
+      <c r="AH124" s="52"/>
+      <c r="AI124" s="52"/>
+      <c r="AJ124" s="52"/>
+      <c r="AK124" s="53"/>
+      <c r="AL124" s="51" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AM124" s="52"/>
+      <c r="AN124" s="52"/>
+      <c r="AO124" s="52"/>
+      <c r="AP124" s="53"/>
+      <c r="AQ124" s="51" t="s">
+        <v>1246</v>
+      </c>
+      <c r="AR124" s="52"/>
+      <c r="AS124" s="52"/>
+      <c r="AT124" s="52"/>
+      <c r="AU124" s="52"/>
+      <c r="AV124" s="52"/>
+      <c r="AW124" s="53"/>
+      <c r="BA124" s="11" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="125" spans="2:53">
+      <c r="Q125" s="11" t="s">
+        <v>1205</v>
+      </c>
+      <c r="AG125" s="51" t="s">
+        <v>1247</v>
+      </c>
+      <c r="AH125" s="52"/>
+      <c r="AI125" s="52"/>
+      <c r="AJ125" s="52"/>
+      <c r="AK125" s="53"/>
+      <c r="AL125" s="51" t="s">
+        <v>1248</v>
+      </c>
+      <c r="AM125" s="52"/>
+      <c r="AN125" s="52"/>
+      <c r="AO125" s="52"/>
+      <c r="AP125" s="53"/>
+      <c r="AQ125" s="51" t="s">
+        <v>1249</v>
+      </c>
+      <c r="AR125" s="52"/>
+      <c r="AS125" s="52"/>
+      <c r="AT125" s="52"/>
+      <c r="AU125" s="52"/>
+      <c r="AV125" s="52"/>
+      <c r="AW125" s="53"/>
+      <c r="BA125" s="11" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="126" spans="2:53">
+      <c r="Q126" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG126" s="51" t="s">
+        <v>1250</v>
+      </c>
+      <c r="AH126" s="52"/>
+      <c r="AI126" s="52"/>
+      <c r="AJ126" s="52"/>
+      <c r="AK126" s="53"/>
+      <c r="AL126" s="51" t="s">
+        <v>1251</v>
+      </c>
+      <c r="AM126" s="52"/>
+      <c r="AN126" s="52"/>
+      <c r="AO126" s="52"/>
+      <c r="AP126" s="53"/>
+      <c r="AQ126" s="51" t="s">
+        <v>1252</v>
+      </c>
+      <c r="AR126" s="52"/>
+      <c r="AS126" s="52"/>
+      <c r="AT126" s="52"/>
+      <c r="AU126" s="52"/>
+      <c r="AV126" s="52"/>
+      <c r="AW126" s="53"/>
+      <c r="BA126" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="127" spans="2:53">
+      <c r="Q127" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG127" s="51" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AH127" s="52"/>
+      <c r="AI127" s="52"/>
+      <c r="AJ127" s="52"/>
+      <c r="AK127" s="53"/>
+      <c r="AL127" s="51" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AM127" s="52"/>
+      <c r="AN127" s="52"/>
+      <c r="AO127" s="52"/>
+      <c r="AP127" s="53"/>
+      <c r="AQ127" s="51" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AR127" s="52"/>
+      <c r="AS127" s="52"/>
+      <c r="AT127" s="52"/>
+      <c r="AU127" s="52"/>
+      <c r="AV127" s="52"/>
+      <c r="AW127" s="53"/>
+    </row>
+    <row r="128" spans="2:53" ht="15">
+      <c r="Q128" s="13"/>
+      <c r="BA128" s="7" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="129" spans="17:54" ht="15">
+      <c r="Q129" s="11" t="s">
+        <v>1206</v>
+      </c>
+      <c r="AE129" s="42" t="s">
+        <v>1417</v>
+      </c>
+      <c r="AF129" s="22"/>
+      <c r="BB129" s="11" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="130" spans="17:54" ht="15">
+      <c r="Q130" s="11" t="s">
+        <v>1207</v>
+      </c>
+      <c r="AE130" s="23" t="s">
+        <v>1414</v>
+      </c>
+      <c r="AF130" s="22"/>
+      <c r="BB130" s="11" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="131" spans="17:54">
+      <c r="Q131" s="11" t="s">
+        <v>1208</v>
+      </c>
+      <c r="AE131" s="23" t="s">
+        <v>1415</v>
+      </c>
+      <c r="AF131" s="22"/>
+      <c r="BB131" s="11" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="132" spans="17:54" ht="15">
+      <c r="Q132" s="13"/>
+      <c r="AE132" s="23" t="s">
+        <v>1416</v>
+      </c>
+      <c r="AF132" s="22"/>
+    </row>
+    <row r="133" spans="17:54" ht="15">
+      <c r="Q133" s="11" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AE133" s="5"/>
+      <c r="BA133" s="7" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="134" spans="17:54" ht="15">
+      <c r="Q134" s="11" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AA134" s="57" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AB134" s="58"/>
+      <c r="AC134" s="58"/>
+      <c r="AD134" s="58"/>
+      <c r="AE134" s="58"/>
+      <c r="AF134" s="58"/>
+      <c r="AG134" s="58"/>
+      <c r="AH134" s="58"/>
+      <c r="AI134" s="58"/>
+      <c r="AJ134" s="58"/>
+      <c r="AK134" s="58"/>
+      <c r="AL134" s="58"/>
+      <c r="AM134" s="58"/>
+      <c r="AN134" s="58"/>
+      <c r="AO134" s="58"/>
+      <c r="AP134" s="58"/>
+      <c r="AQ134" s="58"/>
+      <c r="AR134" s="58"/>
+      <c r="AS134" s="58"/>
+      <c r="AT134" s="58"/>
+      <c r="AU134" s="58"/>
+      <c r="AV134" s="58"/>
+      <c r="AW134" s="58"/>
+      <c r="AX134" s="58"/>
+      <c r="AY134" s="58"/>
+      <c r="AZ134" s="58"/>
+      <c r="BA134" s="12"/>
+      <c r="BB134" s="38" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="135" spans="17:54" ht="15">
+      <c r="Q135" s="13"/>
+      <c r="AA135" s="59" t="s">
+        <v>1418</v>
+      </c>
+      <c r="AB135" s="58"/>
+      <c r="AC135" s="58"/>
+      <c r="AD135" s="58"/>
+      <c r="AE135" s="58"/>
+      <c r="AF135" s="58"/>
+      <c r="AG135" s="58"/>
+      <c r="AH135" s="58"/>
+      <c r="AI135" s="58"/>
+      <c r="AJ135" s="58"/>
+      <c r="AK135" s="58"/>
+      <c r="AL135" s="58"/>
+      <c r="AM135" s="58"/>
+      <c r="AN135" s="58"/>
+      <c r="AO135" s="58"/>
+      <c r="AP135" s="58"/>
+      <c r="AQ135" s="58"/>
+      <c r="AR135" s="58"/>
+      <c r="AS135" s="58"/>
+      <c r="AT135" s="58"/>
+      <c r="AU135" s="58"/>
+      <c r="AV135" s="58"/>
+      <c r="AW135" s="58"/>
+      <c r="AX135" s="58"/>
+      <c r="AY135" s="58"/>
+      <c r="AZ135" s="58"/>
+      <c r="BB135" s="38" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="136" spans="17:54" ht="15">
+      <c r="Q136" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA136" s="59" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AB136" s="58"/>
+      <c r="AC136" s="58"/>
+      <c r="AD136" s="58"/>
+      <c r="AE136" s="58"/>
+      <c r="AF136" s="58"/>
+      <c r="AG136" s="58"/>
+      <c r="AH136" s="58"/>
+      <c r="AI136" s="58"/>
+      <c r="AJ136" s="58"/>
+      <c r="AK136" s="58"/>
+      <c r="AL136" s="58"/>
+      <c r="AM136" s="58"/>
+      <c r="AN136" s="58"/>
+      <c r="AO136" s="58"/>
+      <c r="AP136" s="58"/>
+      <c r="AQ136" s="58"/>
+      <c r="AR136" s="58"/>
+      <c r="AS136" s="58"/>
+      <c r="AT136" s="58"/>
+      <c r="AU136" s="58"/>
+      <c r="AV136" s="58"/>
+      <c r="AW136" s="58"/>
+      <c r="AX136" s="58"/>
+      <c r="AY136" s="58"/>
+      <c r="AZ136" s="58"/>
+      <c r="BB136" s="38" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="137" spans="17:54">
+      <c r="Q137" s="13"/>
+      <c r="BB137" s="38" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="138" spans="17:54">
+      <c r="Q138" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="BB138" s="38" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="139" spans="17:54">
+      <c r="Q139" s="11" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="140" spans="17:54" ht="15" customHeight="1">
+      <c r="Q140" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="141" spans="17:54" ht="14.25" customHeight="1">
+      <c r="Q141" s="13"/>
+    </row>
+    <row r="142" spans="17:54" ht="14.25" customHeight="1">
+      <c r="Q142" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="17:54" ht="14.25" customHeight="1">
+      <c r="Q143" s="11" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="144" spans="17:54" ht="14.25" customHeight="1">
+      <c r="Q144" s="11" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="145" spans="1:57" ht="14.25" customHeight="1">
+      <c r="Q145" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="146" spans="1:57" ht="14.25" customHeight="1">
+      <c r="Q146" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="147" spans="1:57" ht="14.25" customHeight="1"/>
+    <row r="148" spans="1:57" ht="15">
+      <c r="P148" s="7" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="149" spans="1:57">
+      <c r="Q149" s="11" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="150" spans="1:57">
+      <c r="Q150" s="11" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="151" spans="1:57">
+      <c r="Q151" s="11" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="152" spans="1:57" ht="15" thickBot="1"/>
+    <row r="153" spans="1:57" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A153" s="14" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="154" spans="1:57" ht="15">
+      <c r="A154" s="18" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B154" s="19"/>
+      <c r="C154" s="19"/>
+      <c r="D154" s="19"/>
+      <c r="E154" s="19"/>
+      <c r="F154" s="19"/>
+      <c r="G154" s="19"/>
+      <c r="M154" s="18" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N154" s="19"/>
+      <c r="O154" s="19"/>
+      <c r="P154" s="19"/>
+      <c r="Q154" s="19"/>
+      <c r="R154" s="19"/>
+      <c r="S154" s="19"/>
+      <c r="Y154" s="18" t="s">
+        <v>1288</v>
+      </c>
+      <c r="Z154" s="19"/>
+      <c r="AA154" s="19"/>
+      <c r="AB154" s="19"/>
+      <c r="AC154" s="19"/>
+      <c r="AD154" s="19"/>
+      <c r="AE154" s="19"/>
+      <c r="AL154" s="18" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AM154" s="19"/>
+      <c r="AN154" s="19"/>
+      <c r="AO154" s="19"/>
+      <c r="AP154" s="19"/>
+      <c r="AQ154" s="19"/>
+      <c r="AR154" s="19"/>
+      <c r="AS154" s="19"/>
+      <c r="AT154" s="19"/>
+      <c r="AU154" s="19"/>
+      <c r="AV154" s="19"/>
+      <c r="AY154" s="18" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AZ154" s="19"/>
+      <c r="BA154" s="19"/>
+      <c r="BB154" s="19"/>
+      <c r="BC154" s="19"/>
+      <c r="BD154" s="19"/>
+      <c r="BE154" s="19"/>
+    </row>
+    <row r="155" spans="1:57">
+      <c r="B155" s="11" t="s">
+        <v>1280</v>
+      </c>
+      <c r="N155" s="11" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Y155" s="11" t="s">
+        <v>1289</v>
+      </c>
+      <c r="AL155" s="11" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AY155" s="11" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="156" spans="1:57">
+      <c r="B156" s="11" t="s">
+        <v>1186</v>
+      </c>
+      <c r="N156" s="11" t="s">
+        <v>1285</v>
+      </c>
+      <c r="Y156" s="11" t="s">
+        <v>1290</v>
+      </c>
+      <c r="AL156" s="11" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AY156" s="11" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="157" spans="1:57">
+      <c r="B157" s="11" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N157" s="13"/>
+      <c r="Y157" s="13"/>
+      <c r="AL157" s="13"/>
+      <c r="AY157" s="11" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="158" spans="1:57">
+      <c r="B158" s="13"/>
+      <c r="N158" s="11" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Y158" s="11" t="s">
+        <v>1291</v>
+      </c>
+      <c r="AL158" s="11" t="s">
+        <v>1296</v>
+      </c>
+      <c r="AY158" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="159" spans="1:57">
+      <c r="B159" s="11" t="s">
+        <v>1282</v>
+      </c>
+      <c r="N159" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="Y159" s="11" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AL159" s="11" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="160" spans="1:57">
+      <c r="B160" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="161" spans="1:44">
+      <c r="B161" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="162" spans="1:44">
+      <c r="B162" s="11" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="163" spans="1:44">
+      <c r="B163" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="164" spans="1:44" ht="15" thickBot="1"/>
+    <row r="165" spans="1:44" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A165" s="47" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="166" spans="1:44" ht="15">
+      <c r="A166" s="18" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B166" s="19"/>
+      <c r="C166" s="19"/>
+      <c r="D166" s="19"/>
+      <c r="E166" s="19"/>
+      <c r="F166" s="19"/>
+      <c r="G166" s="19"/>
+      <c r="H166" s="19"/>
+      <c r="I166" s="19"/>
+      <c r="J166" s="19"/>
+      <c r="Q166" s="18" t="s">
+        <v>1316</v>
+      </c>
+      <c r="R166" s="19"/>
+      <c r="S166" s="19"/>
+      <c r="T166" s="19"/>
+      <c r="U166" s="19"/>
+      <c r="V166" s="19"/>
+      <c r="W166" s="19"/>
+      <c r="AJ166" s="18" t="s">
+        <v>1334</v>
+      </c>
+      <c r="AK166" s="19"/>
+      <c r="AL166" s="19"/>
+      <c r="AM166" s="19"/>
+      <c r="AN166" s="19"/>
+      <c r="AO166" s="19"/>
+      <c r="AP166" s="19"/>
+      <c r="AQ166" s="19"/>
+      <c r="AR166" s="19"/>
+    </row>
+    <row r="167" spans="1:44">
+      <c r="B167" s="11" t="s">
+        <v>1304</v>
+      </c>
+      <c r="R167" s="11" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AK167" s="11" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="168" spans="1:44">
+      <c r="B168" s="11" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R168" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="AK168" s="11" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="169" spans="1:44">
+      <c r="B169" s="11" t="s">
+        <v>1306</v>
+      </c>
+      <c r="R169" s="13"/>
+      <c r="AK169" s="13"/>
+    </row>
+    <row r="170" spans="1:44">
+      <c r="B170" s="11" t="s">
+        <v>1307</v>
+      </c>
+      <c r="R170" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="AK170" s="11" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="171" spans="1:44">
+      <c r="B171" s="11" t="s">
+        <v>1308</v>
+      </c>
+      <c r="R171" s="11" t="s">
+        <v>1320</v>
+      </c>
+      <c r="AK171" s="11" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="172" spans="1:44">
+      <c r="B172" s="13"/>
+      <c r="R172" s="11" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="173" spans="1:44" ht="15">
+      <c r="B173" s="11" t="s">
+        <v>1309</v>
+      </c>
+      <c r="R173" s="11" t="s">
+        <v>1322</v>
+      </c>
+      <c r="AJ173" s="18" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AK173" s="19"/>
+      <c r="AL173" s="19"/>
+      <c r="AM173" s="19"/>
+      <c r="AN173" s="19"/>
+      <c r="AO173" s="19"/>
+      <c r="AP173" s="19"/>
+      <c r="AQ173" s="19"/>
+    </row>
+    <row r="174" spans="1:44">
+      <c r="B174" s="11" t="s">
+        <v>1310</v>
+      </c>
+      <c r="R174" s="13"/>
+      <c r="AK174" s="11" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="175" spans="1:44">
+      <c r="B175" s="13"/>
+      <c r="R175" s="11" t="s">
+        <v>1323</v>
+      </c>
+      <c r="AK175" s="11" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="176" spans="1:44">
+      <c r="B176" s="11" t="s">
+        <v>1311</v>
+      </c>
+      <c r="R176" s="11" t="s">
+        <v>1324</v>
+      </c>
+      <c r="AK176" s="13"/>
+    </row>
+    <row r="177" spans="1:37">
+      <c r="B177" s="11" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R177" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="AK177" s="11" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="178" spans="1:37">
+      <c r="B178" s="13"/>
+      <c r="R178" s="11" t="s">
+        <v>1326</v>
+      </c>
+      <c r="AK178" s="11" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="179" spans="1:37">
+      <c r="B179" s="11" t="s">
+        <v>1313</v>
+      </c>
+      <c r="R179" s="11" t="s">
+        <v>1327</v>
+      </c>
+      <c r="AK179" s="13"/>
+    </row>
+    <row r="180" spans="1:37">
+      <c r="B180" s="11" t="s">
+        <v>1314</v>
+      </c>
+      <c r="R180" s="11" t="s">
+        <v>1328</v>
+      </c>
+      <c r="AK180" s="11" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="181" spans="1:37">
+      <c r="B181" s="13"/>
+      <c r="R181" s="11" t="s">
+        <v>1329</v>
+      </c>
+      <c r="AK181" s="11" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="182" spans="1:37">
+      <c r="B182" s="11" t="s">
+        <v>1315</v>
+      </c>
+      <c r="R182" s="11" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="183" spans="1:37">
+      <c r="R183" s="11" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="184" spans="1:37">
+      <c r="R184" s="11" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="185" spans="1:37">
+      <c r="R185" s="11" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="186" spans="1:37" ht="15" thickBot="1">
+      <c r="R186" s="11" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="187" spans="1:37" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A187" s="14" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="188" spans="1:37" ht="15">
+      <c r="A188" s="18" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B188" s="19"/>
+      <c r="C188" s="19"/>
+      <c r="D188" s="19"/>
+      <c r="E188" s="19"/>
+      <c r="F188" s="19"/>
+      <c r="G188" s="19"/>
+      <c r="H188" s="19"/>
+      <c r="I188" s="19"/>
+      <c r="N188" s="18" t="s">
+        <v>1350</v>
+      </c>
+      <c r="O188" s="19"/>
+      <c r="P188" s="19"/>
+      <c r="Q188" s="19"/>
+      <c r="R188" s="19"/>
+      <c r="S188" s="19"/>
+      <c r="T188" s="19"/>
+      <c r="Z188" s="18" t="s">
+        <v>1357</v>
+      </c>
+      <c r="AA188" s="19"/>
+      <c r="AB188" s="19"/>
+      <c r="AC188" s="19"/>
+      <c r="AD188" s="19"/>
+      <c r="AE188" s="19"/>
+      <c r="AF188" s="19"/>
+      <c r="AG188" s="19"/>
+      <c r="AH188" s="19"/>
+    </row>
+    <row r="189" spans="1:37">
+      <c r="A189" s="12" t="s">
+        <v>1391</v>
+      </c>
+      <c r="N189" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="O189" s="22"/>
+      <c r="P189" s="22"/>
+      <c r="Q189" s="22"/>
+      <c r="R189" s="22"/>
+      <c r="S189" s="22"/>
+      <c r="T189" s="22"/>
+      <c r="U189" s="22"/>
+      <c r="V189" s="22"/>
+      <c r="W189" s="22"/>
+      <c r="X189" s="22"/>
+      <c r="Y189" s="22"/>
+      <c r="Z189" s="12" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="190" spans="1:37">
+      <c r="A190" s="12" t="s">
+        <v>1348</v>
+      </c>
+      <c r="N190" s="16" t="s">
+        <v>1351</v>
+      </c>
+      <c r="O190" s="22"/>
+      <c r="P190" s="22"/>
+      <c r="Q190" s="22"/>
+      <c r="R190" s="22"/>
+      <c r="S190" s="22"/>
+      <c r="T190" s="22"/>
+      <c r="U190" s="22"/>
+      <c r="V190" s="22"/>
+      <c r="W190" s="22"/>
+      <c r="X190" s="22"/>
+      <c r="Y190" s="22"/>
+      <c r="Z190" s="12" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="191" spans="1:37">
+      <c r="A191" s="12" t="s">
+        <v>1392</v>
+      </c>
+      <c r="N191" s="16" t="s">
+        <v>1352</v>
+      </c>
+      <c r="O191" s="22"/>
+      <c r="P191" s="22"/>
+      <c r="Q191" s="22"/>
+      <c r="R191" s="22"/>
+      <c r="S191" s="22"/>
+      <c r="T191" s="22"/>
+      <c r="U191" s="22"/>
+      <c r="V191" s="22"/>
+      <c r="W191" s="22"/>
+      <c r="X191" s="22"/>
+      <c r="Y191" s="22"/>
+      <c r="Z191" s="12" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="192" spans="1:37">
+      <c r="A192" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="N192" s="16" t="s">
+        <v>1353</v>
+      </c>
+      <c r="O192" s="22"/>
+      <c r="P192" s="22"/>
+      <c r="Q192" s="22"/>
+      <c r="R192" s="22"/>
+      <c r="S192" s="22"/>
+      <c r="T192" s="22"/>
+      <c r="U192" s="22"/>
+      <c r="V192" s="22"/>
+      <c r="W192" s="22"/>
+      <c r="X192" s="22"/>
+      <c r="Y192" s="22"/>
+      <c r="Z192" s="12" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="193" spans="14:25">
+      <c r="N193" s="16" t="s">
+        <v>1354</v>
+      </c>
+      <c r="O193" s="22"/>
+      <c r="P193" s="22"/>
+      <c r="Q193" s="22"/>
+      <c r="R193" s="22"/>
+      <c r="S193" s="22"/>
+      <c r="T193" s="22"/>
+      <c r="U193" s="22"/>
+      <c r="V193" s="22"/>
+      <c r="W193" s="22"/>
+      <c r="X193" s="22"/>
+      <c r="Y193" s="22"/>
+    </row>
+    <row r="194" spans="14:25">
+      <c r="N194" s="16" t="s">
+        <v>1355</v>
+      </c>
+      <c r="O194" s="22"/>
+      <c r="P194" s="22"/>
+      <c r="Q194" s="22"/>
+      <c r="R194" s="22"/>
+      <c r="S194" s="22"/>
+      <c r="T194" s="22"/>
+      <c r="U194" s="22"/>
+      <c r="V194" s="22"/>
+      <c r="W194" s="22"/>
+      <c r="X194" s="22"/>
+      <c r="Y194" s="22"/>
+    </row>
+    <row r="195" spans="14:25">
+      <c r="N195" s="16" t="s">
+        <v>1356</v>
+      </c>
+      <c r="O195" s="22"/>
+      <c r="P195" s="22"/>
+      <c r="Q195" s="22"/>
+      <c r="R195" s="22"/>
+      <c r="S195" s="22"/>
+      <c r="T195" s="22"/>
+      <c r="U195" s="22"/>
+      <c r="V195" s="22"/>
+      <c r="W195" s="22"/>
+      <c r="X195" s="22"/>
+      <c r="Y195" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="AL126:AP126"/>
+    <mergeCell ref="AL127:AP127"/>
+    <mergeCell ref="AQ120:AW120"/>
+    <mergeCell ref="AQ121:AW121"/>
+    <mergeCell ref="AQ122:AW122"/>
+    <mergeCell ref="AQ123:AW123"/>
+    <mergeCell ref="AQ124:AW124"/>
+    <mergeCell ref="AQ125:AW125"/>
+    <mergeCell ref="AQ126:AW126"/>
+    <mergeCell ref="AQ127:AW127"/>
+    <mergeCell ref="AL120:AP120"/>
+    <mergeCell ref="AL121:AP121"/>
+    <mergeCell ref="AL122:AP122"/>
+    <mergeCell ref="AL123:AP123"/>
+    <mergeCell ref="AL124:AP124"/>
+    <mergeCell ref="AL125:AP125"/>
+    <mergeCell ref="AG120:AK120"/>
+    <mergeCell ref="AG121:AK121"/>
+    <mergeCell ref="AG122:AK122"/>
+    <mergeCell ref="AG123:AK123"/>
+    <mergeCell ref="AG124:AK124"/>
+    <mergeCell ref="AG125:AK125"/>
+    <mergeCell ref="AG126:AK126"/>
+    <mergeCell ref="AG127:AK127"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Kỹ Thuật lập trình/C/05. PREPROCESSOR & COMPILATION.xlsx
+++ b/Kỹ Thuật lập trình/C/05. PREPROCESSOR & COMPILATION.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mục Lục" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="2014">
   <si>
     <t>🔄 PREPROCESSOR &amp; COMPILATION</t>
   </si>
@@ -6093,12 +6093,1791 @@
   <si>
     <t xml:space="preserve">Nói về rebuild ở đây là quá trình linking là chính xác nhất, </t>
   </si>
+  <si>
+    <t>1. Header File Design</t>
+  </si>
+  <si>
+    <t>1.1 Khái niệm cơ bản</t>
+  </si>
+  <si>
+    <t>Header file (.h) là file chứa các khai báo (declarations) được sử dụng bởi nhiều source file khác nhau. Chúng giúp:</t>
+  </si>
+  <si>
+    <t>Tái sử dụng code</t>
+  </si>
+  <si>
+    <t>Tổ chức code rõ ràng</t>
+  </si>
+  <si>
+    <t>Chia sẻ interface giữa các module</t>
+  </si>
+  <si>
+    <t>1.2 Cấu trúc cơ bản của một header file</t>
+  </si>
+  <si>
+    <t>// math_utils.h</t>
+  </si>
+  <si>
+    <t>#ifndef MATH_UTILS_H</t>
+  </si>
+  <si>
+    <t>#define MATH_UTILS_H</t>
+  </si>
+  <si>
+    <t>// Include các thư viện cần thiết</t>
+  </si>
+  <si>
+    <t>// Macro definitions</t>
+  </si>
+  <si>
+    <t>#define MAX(a,b) ((a) &gt; (b) ? (a) : (b))</t>
+  </si>
+  <si>
+    <t>// Type definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double x, y;</t>
+  </si>
+  <si>
+    <t>} Point;</t>
+  </si>
+  <si>
+    <t>// Function declarations</t>
+  </si>
+  <si>
+    <t>double calculate_distance(Point p1, Point p2);</t>
+  </si>
+  <si>
+    <t>double calculate_area_circle(double radius);</t>
+  </si>
+  <si>
+    <t>// External variable declarations</t>
+  </si>
+  <si>
+    <t>extern int global_counter;</t>
+  </si>
+  <si>
+    <t>#endif // MATH_UTILS_H</t>
+  </si>
+  <si>
+    <t>1.3 Nguyên tắc thiết kế header file</t>
+  </si>
+  <si>
+    <t>DO:</t>
+  </si>
+  <si>
+    <t>Chỉ chứa declarations, không chứa definitions</t>
+  </si>
+  <si>
+    <t>Sử dụng header guards</t>
+  </si>
+  <si>
+    <t>Include đầy đủ dependencies</t>
+  </si>
+  <si>
+    <t>Sử dụng tên rõ ràng, có ý nghĩa</t>
+  </si>
+  <si>
+    <t>DON'T:</t>
+  </si>
+  <si>
+    <t>Không định nghĩa variables (trừ const)</t>
+  </si>
+  <si>
+    <t>Không include các header không cần thiết</t>
+  </si>
+  <si>
+    <t>Không sử dụng using namespace trong C++</t>
+  </si>
+  <si>
+    <t>2. Header Guards</t>
+  </si>
+  <si>
+    <t>2.1 Traditional Header Guards (#ifndef)</t>
+  </si>
+  <si>
+    <t>// Example: string_utils.h</t>
+  </si>
+  <si>
+    <t>#ifndef STRING_UTILS_H</t>
+  </si>
+  <si>
+    <t>#define STRING_UTILS_H</t>
+  </si>
+  <si>
+    <t>// Content của header file</t>
+  </si>
+  <si>
+    <t>char* string_duplicate(const char* src);</t>
+  </si>
+  <si>
+    <t>int string_length(const char* str);</t>
+  </si>
+  <si>
+    <t>void string_reverse(char* str);</t>
+  </si>
+  <si>
+    <t>#endif // STRING_UTILS_H</t>
+  </si>
+  <si>
+    <t>2.2 Pragma Once (Compiler-specific)</t>
+  </si>
+  <si>
+    <t>// Alternative (không phải standard C)</t>
+  </si>
+  <si>
+    <t>2.3 Tại sao cần header guards?</t>
+  </si>
+  <si>
+    <t>Vấn đề:</t>
+  </si>
+  <si>
+    <t>// file1.h</t>
+  </si>
+  <si>
+    <t>struct Data {</t>
+  </si>
+  <si>
+    <t>// file2.h</t>
+  </si>
+  <si>
+    <t>#include "file1.h"</t>
+  </si>
+  <si>
+    <t>struct MoreData {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    struct Data data;</t>
+  </si>
+  <si>
+    <t>#include "file1.h"  // Định nghĩa struct Data lần 1</t>
+  </si>
+  <si>
+    <t>#include "file2.h"  // Định nghĩa struct Data lần 2 (ERROR!)</t>
+  </si>
+  <si>
+    <t>Giải pháp với header guards:</t>
+  </si>
+  <si>
+    <t>#ifndef FILE1_H</t>
+  </si>
+  <si>
+    <t>#define FILE1_H</t>
+  </si>
+  <si>
+    <t>#endif // FILE1_H</t>
+  </si>
+  <si>
+    <t>2.4 Naming Convention cho Header Guards</t>
+  </si>
+  <si>
+    <t>// Tốt</t>
+  </si>
+  <si>
+    <t>#ifndef PROJECT_MODULE_H</t>
+  </si>
+  <si>
+    <t>#define PROJECT_MODULE_H</t>
+  </si>
+  <si>
+    <t>// Rất tốt (với timestamp/UUID)</t>
+  </si>
+  <si>
+    <t>#ifndef PROJECT_MODULE_H_INCLUDED_20240101</t>
+  </si>
+  <si>
+    <t>#define PROJECT_MODULE_H_INCLUDED_20240101</t>
+  </si>
+  <si>
+    <t>3. Function Declarations</t>
+  </si>
+  <si>
+    <t>3.1 Cú pháp cơ bản</t>
+  </si>
+  <si>
+    <t>// math_operations.h</t>
+  </si>
+  <si>
+    <t>#ifndef MATH_OPERATIONS_H</t>
+  </si>
+  <si>
+    <t>#define MATH_OPERATIONS_H</t>
+  </si>
+  <si>
+    <t>// Basic function declarations</t>
+  </si>
+  <si>
+    <t>int add(int a, int b);</t>
+  </si>
+  <si>
+    <t>double divide(double a, double b);</t>
+  </si>
+  <si>
+    <t>void print_result(int result);</t>
+  </si>
+  <si>
+    <t>// Function với default parameters (C99+)</t>
+  </si>
+  <si>
+    <t>double power(double base, double exponent /* = 2.0 */);</t>
+  </si>
+  <si>
+    <t>// Function pointers</t>
+  </si>
+  <si>
+    <t>typedef int (*comparison_func_t)(const void* a, const void* b);</t>
+  </si>
+  <si>
+    <t>void sort_array(void* array, size_t count, size_t size, comparison_func_t compare);</t>
+  </si>
+  <si>
+    <t>3.2 Variadic Functions</t>
+  </si>
+  <si>
+    <t>// logger.h</t>
+  </si>
+  <si>
+    <t>#include &lt;stdarg.h&gt;</t>
+  </si>
+  <si>
+    <t>// Variadic function declaration</t>
+  </si>
+  <si>
+    <t>void log_message(const char* level, const char* format, ...);</t>
+  </si>
+  <si>
+    <t>void log_info(const char* format, ...);</t>
+  </si>
+  <si>
+    <t>void log_error(const char* format, ...);</t>
+  </si>
+  <si>
+    <t>3.3 Inline Functions (C99+)</t>
+  </si>
+  <si>
+    <t>// utilities.h</t>
+  </si>
+  <si>
+    <t>#ifndef UTILITIES_H</t>
+  </si>
+  <si>
+    <t>#define UTILITIES_H</t>
+  </si>
+  <si>
+    <t>// Inline function definitions trong header</t>
+  </si>
+  <si>
+    <t>static inline int min(int a, int b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return (a &lt; b) ? a : b;</t>
+  </si>
+  <si>
+    <t>static inline int max(int a, int b) {</t>
+  </si>
+  <si>
+    <t>4. Type Definitions</t>
+  </si>
+  <si>
+    <t>4.1 Struct Definitions</t>
+  </si>
+  <si>
+    <t>// data_structures.h</t>
+  </si>
+  <si>
+    <t>#ifndef DATA_STRUCTURES_H</t>
+  </si>
+  <si>
+    <t>#define DATA_STRUCTURES_H</t>
+  </si>
+  <si>
+    <t>// Simple struct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x, y;</t>
+  </si>
+  <si>
+    <t>} Point2D;</t>
+  </si>
+  <si>
+    <t>// Named struct (có thể self-reference)</t>
+  </si>
+  <si>
+    <t>typedef struct Node {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int data;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    struct Node* next;</t>
+  </si>
+  <si>
+    <t>} Node;</t>
+  </si>
+  <si>
+    <t>// Forward declarations</t>
+  </si>
+  <si>
+    <t>typedef struct LinkedList LinkedList;</t>
+  </si>
+  <si>
+    <t>typedef struct TreeNode TreeNode;</t>
+  </si>
+  <si>
+    <t>// Complete definitions</t>
+  </si>
+  <si>
+    <t>struct LinkedList {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Node* head;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Node* tail;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    size_t size;</t>
+  </si>
+  <si>
+    <t>struct TreeNode {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TreeNode* left;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TreeNode* right;</t>
+  </si>
+  <si>
+    <t>4.2 Enum Definitions</t>
+  </si>
+  <si>
+    <t>// enums.h</t>
+  </si>
+  <si>
+    <t>#ifndef ENUMS_H</t>
+  </si>
+  <si>
+    <t>#define ENUMS_H</t>
+  </si>
+  <si>
+    <t>// Simple enum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    STATUS_SUCCESS = 0,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    STATUS_ERROR = -1,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    STATUS_WARNING = 1</t>
+  </si>
+  <si>
+    <t>} Status;</t>
+  </si>
+  <si>
+    <t>// Enum với explicit values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    COLOR_RED   = 0xFF0000,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    COLOR_GREEN = 0x00FF00,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    COLOR_BLUE  = 0x0000FF</t>
+  </si>
+  <si>
+    <t>} Color;</t>
+  </si>
+  <si>
+    <t>// Bit flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PERMISSION_READ    = 1 &lt;&lt; 0,  // 0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PERMISSION_WRITE   = 1 &lt;&lt; 1,  // 0010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PERMISSION_EXECUTE = 1 &lt;&lt; 2   // 0100</t>
+  </si>
+  <si>
+    <t>} Permission;</t>
+  </si>
+  <si>
+    <t>4.3 Union Definitions</t>
+  </si>
+  <si>
+    <t>// unions.h</t>
+  </si>
+  <si>
+    <t>#ifndef UNIONS_H</t>
+  </si>
+  <si>
+    <t>#define UNIONS_H</t>
+  </si>
+  <si>
+    <t>// Tagged union</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TYPE_INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TYPE_FLOAT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TYPE_STRING</t>
+  </si>
+  <si>
+    <t>} ValueType;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ValueType type;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    union {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        int int_value;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        float float_value;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        char* string_value;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    } data;</t>
+  </si>
+  <si>
+    <t>} Value;</t>
+  </si>
+  <si>
+    <t>4.4 Function Pointer Types</t>
+  </si>
+  <si>
+    <t>// callbacks.h</t>
+  </si>
+  <si>
+    <t>#ifndef CALLBACKS_H</t>
+  </si>
+  <si>
+    <t>#define CALLBACKS_H</t>
+  </si>
+  <si>
+    <t>// Callback function types</t>
+  </si>
+  <si>
+    <t>typedef void (*event_callback_t)(int event_id, void* data);</t>
+  </si>
+  <si>
+    <t>typedef int (*comparator_t)(const void* a, const void* b);</t>
+  </si>
+  <si>
+    <t>typedef void (*destructor_t)(void* object);</t>
+  </si>
+  <si>
+    <t>// Callback registry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    event_callback_t callback;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void* user_data;</t>
+  </si>
+  <si>
+    <t>} EventHandler;</t>
+  </si>
+  <si>
+    <t>5. Constant Definitions</t>
+  </si>
+  <si>
+    <t>5.1 Macro Constants</t>
+  </si>
+  <si>
+    <t>// constants.h</t>
+  </si>
+  <si>
+    <t>#ifndef CONSTANTS_H</t>
+  </si>
+  <si>
+    <t>#define CONSTANTS_H</t>
+  </si>
+  <si>
+    <t>// Mathematical constants</t>
+  </si>
+  <si>
+    <t>#define PI 3.14159265358979323846</t>
+  </si>
+  <si>
+    <t>#define E  2.71828182845904523536</t>
+  </si>
+  <si>
+    <t>// Configuration constants</t>
+  </si>
+  <si>
+    <t>#define MAX_BUFFER_SIZE 1024</t>
+  </si>
+  <si>
+    <t>#define MAX_FILENAME_LENGTH 256</t>
+  </si>
+  <si>
+    <t>#define DEFAULT_TIMEOUT 30</t>
+  </si>
+  <si>
+    <t>// String constants</t>
+  </si>
+  <si>
+    <t>#define ERROR_MESSAGE "An error occurred"</t>
+  </si>
+  <si>
+    <t>#define SUCCESS_MESSAGE "Operation completed successfully"</t>
+  </si>
+  <si>
+    <t>// Bit manipulation</t>
+  </si>
+  <si>
+    <t>#define BIT_SET(value, bit)   ((value) |= (1 &lt;&lt; (bit)))</t>
+  </si>
+  <si>
+    <t>#define BIT_CLEAR(value, bit) ((value) &amp;= ~(1 &lt;&lt; (bit)))</t>
+  </si>
+  <si>
+    <t>#define BIT_CHECK(value, bit) ((value) &amp; (1 &lt;&lt; (bit)))</t>
+  </si>
+  <si>
+    <t>5.2 Const Variables (C99+)</t>
+  </si>
+  <si>
+    <t>// Global constants</t>
+  </si>
+  <si>
+    <t>extern const double GRAVITY;</t>
+  </si>
+  <si>
+    <t>extern const int MAX_CONNECTIONS;</t>
+  </si>
+  <si>
+    <t>extern const char* const DEFAULT_CONFIG_FILE;</t>
+  </si>
+  <si>
+    <t>// Array constants</t>
+  </si>
+  <si>
+    <t>extern const int FIBONACCI_SEQUENCE[];</t>
+  </si>
+  <si>
+    <t>extern const size_t FIBONACCI_SEQUENCE_SIZE;</t>
+  </si>
+  <si>
+    <t>// constants.c</t>
+  </si>
+  <si>
+    <t>#include "constants.h"</t>
+  </si>
+  <si>
+    <t>const double GRAVITY = 9.81;</t>
+  </si>
+  <si>
+    <t>const int MAX_CONNECTIONS = 100;</t>
+  </si>
+  <si>
+    <t>const char* const DEFAULT_CONFIG_FILE = "/etc/myapp.conf";</t>
+  </si>
+  <si>
+    <t>const int FIBONACCI_SEQUENCE[] = {0, 1, 1, 2, 3, 5, 8, 13, 21, 34};</t>
+  </si>
+  <si>
+    <t>const size_t FIBONACCI_SEQUENCE_SIZE = sizeof(FIBONACCI_SEQUENCE) / sizeof(FIBONACCI_SEQUENCE[0]);</t>
+  </si>
+  <si>
+    <t>6. Library Creation</t>
+  </si>
+  <si>
+    <t>6.1 Static Library Creation</t>
+  </si>
+  <si>
+    <t>Bước 1: Tạo source files</t>
+  </si>
+  <si>
+    <t>// math_lib.h</t>
+  </si>
+  <si>
+    <t>#ifndef MATH_LIB_H</t>
+  </si>
+  <si>
+    <t>#define MATH_LIB_H</t>
+  </si>
+  <si>
+    <t>double add(double a, double b);</t>
+  </si>
+  <si>
+    <t>double subtract(double a, double b);</t>
+  </si>
+  <si>
+    <t>double multiply(double a, double b);</t>
+  </si>
+  <si>
+    <t>// math_lib.c</t>
+  </si>
+  <si>
+    <t>#include "math_lib.h"</t>
+  </si>
+  <si>
+    <t>double add(double a, double b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return a + b;</t>
+  </si>
+  <si>
+    <t>double subtract(double a, double b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return a - b;</t>
+  </si>
+  <si>
+    <t>double multiply(double a, double b) {</t>
+  </si>
+  <si>
+    <t>double divide(double a, double b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (b != 0) return a / b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return 0; // Error handling</t>
+  </si>
+  <si>
+    <t>Bước 2: Compile và tạo static library</t>
+  </si>
+  <si>
+    <t>gcc -c math_lib.c -o math_lib.o</t>
+  </si>
+  <si>
+    <t>ar rcs libmath.a math_lib.o</t>
+  </si>
+  <si>
+    <t># Link với static library</t>
+  </si>
+  <si>
+    <t>gcc main.c -L. -lmath -o main</t>
+  </si>
+  <si>
+    <t>6.2 Dynamic Library Creation</t>
+  </si>
+  <si>
+    <t>Linux/Unix (.so files):</t>
+  </si>
+  <si>
+    <t># Compile với position-independent code</t>
+  </si>
+  <si>
+    <t>gcc -fPIC -c math_lib.c -o math_lib.o</t>
+  </si>
+  <si>
+    <t>gcc -shared -o libmath.so math_lib.o</t>
+  </si>
+  <si>
+    <t># Link với dynamic library</t>
+  </si>
+  <si>
+    <t># Run với library path</t>
+  </si>
+  <si>
+    <t>LD_LIBRARY_PATH=. ./main</t>
+  </si>
+  <si>
+    <t>Windows (.dll files):</t>
+  </si>
+  <si>
+    <t># Với MinGW</t>
+  </si>
+  <si>
+    <t>gcc -shared -o math.dll math_lib.c</t>
+  </si>
+  <si>
+    <t># Hoặc với MSVC</t>
+  </si>
+  <si>
+    <t>cl /LD math_lib.c /Fe:math.dll</t>
+  </si>
+  <si>
+    <t>6.3 Advanced Library Features</t>
+  </si>
+  <si>
+    <t>Version Symbols:</t>
+  </si>
+  <si>
+    <t>// versioned_lib.h</t>
+  </si>
+  <si>
+    <t>#ifndef VERSIONED_LIB_H</t>
+  </si>
+  <si>
+    <t>#define VERSIONED_LIB_H</t>
+  </si>
+  <si>
+    <t>#define LIB_VERSION_MAJOR 1</t>
+  </si>
+  <si>
+    <t>#define LIB_VERSION_MINOR 2</t>
+  </si>
+  <si>
+    <t>#define LIB_VERSION_PATCH 3</t>
+  </si>
+  <si>
+    <t>// Version check function</t>
+  </si>
+  <si>
+    <t>int lib_version_check(int major, int minor, int patch);</t>
+  </si>
+  <si>
+    <t>// Deprecated function warning</t>
+  </si>
+  <si>
+    <t>#define DEPRECATED __attribute__((deprecated))</t>
+  </si>
+  <si>
+    <t>#define DEPRECATED</t>
+  </si>
+  <si>
+    <t>DEPRECATED void old_function(void);</t>
+  </si>
+  <si>
+    <t>void new_function(void);</t>
+  </si>
+  <si>
+    <t>Library Initialization:</t>
+  </si>
+  <si>
+    <t>// lib_init.h</t>
+  </si>
+  <si>
+    <t>#ifndef LIB_INIT_H</t>
+  </si>
+  <si>
+    <t>#define LIB_INIT_H</t>
+  </si>
+  <si>
+    <t>// Constructor/Destructor attributes (GCC)</t>
+  </si>
+  <si>
+    <t>#define LIB_CONSTRUCTOR __attribute__((constructor))</t>
+  </si>
+  <si>
+    <t>#define LIB_DESTRUCTOR __attribute__((destructor))</t>
+  </si>
+  <si>
+    <t>#define LIB_CONSTRUCTOR</t>
+  </si>
+  <si>
+    <t>#define LIB_DESTRUCTOR</t>
+  </si>
+  <si>
+    <t>// Library lifecycle functions</t>
+  </si>
+  <si>
+    <t>LIB_CONSTRUCTOR void lib_init(void);</t>
+  </si>
+  <si>
+    <t>LIB_DESTRUCTOR void lib_cleanup(void);</t>
+  </si>
+  <si>
+    <t>// Manual initialization</t>
+  </si>
+  <si>
+    <t>int lib_initialize(void);</t>
+  </si>
+  <si>
+    <t>void lib_finalize(void);</t>
+  </si>
+  <si>
+    <t>7. Library Versioning</t>
+  </si>
+  <si>
+    <t>7.1 Semantic Versioning</t>
+  </si>
+  <si>
+    <t>// version.h</t>
+  </si>
+  <si>
+    <t>#ifndef VERSION_H</t>
+  </si>
+  <si>
+    <t>#define VERSION_H</t>
+  </si>
+  <si>
+    <t>// Semantic versioning: MAJOR.MINOR.PATCH</t>
+  </si>
+  <si>
+    <t>#define VERSION_PATCH 0</t>
+  </si>
+  <si>
+    <t>// Version string</t>
+  </si>
+  <si>
+    <t>#define VERSION_STRING "2.1.0"</t>
+  </si>
+  <si>
+    <t>// Version as single number</t>
+  </si>
+  <si>
+    <t>#define VERSION_NUMBER (VERSION_MAJOR * 10000 + VERSION_MINOR * 100 + VERSION_PATCH)</t>
+  </si>
+  <si>
+    <t>// Version comparison</t>
+  </si>
+  <si>
+    <t>#define VERSION_AT_LEAST(major, minor, patch) \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (VERSION_NUMBER &gt;= ((major) * 10000 + (minor) * 100 + (patch)))</t>
+  </si>
+  <si>
+    <t>// API compatibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int major;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int minor;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int patch;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const char* string;</t>
+  </si>
+  <si>
+    <t>} Version;</t>
+  </si>
+  <si>
+    <t>extern const Version LIBRARY_VERSION;</t>
+  </si>
+  <si>
+    <t>// Runtime version checking</t>
+  </si>
+  <si>
+    <t>int is_version_compatible(int required_major, int required_minor);</t>
+  </si>
+  <si>
+    <t>7.2 ABI (Application Binary Interface) Compatibility</t>
+  </si>
+  <si>
+    <t>// abi_compat.h</t>
+  </si>
+  <si>
+    <t>#ifndef ABI_COMPAT_H</t>
+  </si>
+  <si>
+    <t>#define ABI_COMPAT_H</t>
+  </si>
+  <si>
+    <t>// Forward compatibility</t>
+  </si>
+  <si>
+    <t>typedef struct LibraryContext_v1 {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int version;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // v1 fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int field1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    char field2[64];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Reserved space for future expansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void* reserved[8];</t>
+  </si>
+  <si>
+    <t>} LibraryContext;</t>
+  </si>
+  <si>
+    <t>// Opaque pointer design cho forward compatibility</t>
+  </si>
+  <si>
+    <t>typedef struct LibraryHandle LibraryHandle;</t>
+  </si>
+  <si>
+    <t>LibraryHandle* lib_create(void);</t>
+  </si>
+  <si>
+    <t>void lib_destroy(LibraryHandle* handle);</t>
+  </si>
+  <si>
+    <t>int lib_set_option(LibraryHandle* handle, int option, const void* value);</t>
+  </si>
+  <si>
+    <t>8. API Design Principles</t>
+  </si>
+  <si>
+    <t>8.1 Consistent Naming Conventions</t>
+  </si>
+  <si>
+    <t>// good_api.h</t>
+  </si>
+  <si>
+    <t>#ifndef GOOD_API_H</t>
+  </si>
+  <si>
+    <t>#define GOOD_API_H</t>
+  </si>
+  <si>
+    <t>// Consistent prefix</t>
+  </si>
+  <si>
+    <t>typedef struct database_connection database_connection_t;</t>
+  </si>
+  <si>
+    <t>typedef enum database_error database_error_t;</t>
+  </si>
+  <si>
+    <t>// CRUD operations với consistent naming</t>
+  </si>
+  <si>
+    <t>database_connection_t* database_connection_create(const char* url);</t>
+  </si>
+  <si>
+    <t>database_error_t database_connection_connect(database_connection_t* conn);</t>
+  </si>
+  <si>
+    <t>database_error_t database_connection_execute(database_connection_t* conn, const char* query);</t>
+  </si>
+  <si>
+    <t>void database_connection_destroy(database_connection_t* conn);</t>
+  </si>
+  <si>
+    <t>// Error handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DATABASE_ERROR_NONE = 0,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DATABASE_ERROR_CONNECTION_FAILED,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DATABASE_ERROR_QUERY_FAILED,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DATABASE_ERROR_OUT_OF_MEMORY</t>
+  </si>
+  <si>
+    <t>} database_error_t;</t>
+  </si>
+  <si>
+    <t>const char* database_error_string(database_error_t error);</t>
+  </si>
+  <si>
+    <t>8.2 Resource Management Patterns</t>
+  </si>
+  <si>
+    <t>// resource_mgmt.h</t>
+  </si>
+  <si>
+    <t>#ifndef RESOURCE_MGMT_H</t>
+  </si>
+  <si>
+    <t>#define RESOURCE_MGMT_H</t>
+  </si>
+  <si>
+    <t>// RAII-style resource management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void* data;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void (*destructor)(void*);</t>
+  </si>
+  <si>
+    <t>} Resource;</t>
+  </si>
+  <si>
+    <t>// Resource creation/destruction</t>
+  </si>
+  <si>
+    <t>Resource* resource_create(size_t size);</t>
+  </si>
+  <si>
+    <t>void resource_destroy(Resource* resource);</t>
+  </si>
+  <si>
+    <t>// Automatic cleanup với compiler attributes</t>
+  </si>
+  <si>
+    <t>#define CLEANUP_RESOURCE __attribute__((cleanup(cleanup_resource)))</t>
+  </si>
+  <si>
+    <t>void cleanup_resource(Resource** resource);</t>
+  </si>
+  <si>
+    <t>// Smart pointer pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void* ptr;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int* ref_count;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void (*deleter)(void*);</t>
+  </si>
+  <si>
+    <t>} SharedPtr;</t>
+  </si>
+  <si>
+    <t>SharedPtr shared_ptr_create(void* ptr, void (*deleter)(void*));</t>
+  </si>
+  <si>
+    <t>SharedPtr shared_ptr_copy(const SharedPtr* src);</t>
+  </si>
+  <si>
+    <t>void shared_ptr_destroy(SharedPtr* ptr);</t>
+  </si>
+  <si>
+    <t>8.3 Error Handling Strategies</t>
+  </si>
+  <si>
+    <t>// error_handling.h</t>
+  </si>
+  <si>
+    <t>#ifndef ERROR_HANDLING_H</t>
+  </si>
+  <si>
+    <t>#define ERROR_HANDLING_H</t>
+  </si>
+  <si>
+    <t>#include &lt;errno.h&gt;</t>
+  </si>
+  <si>
+    <t>// Error codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    API_SUCCESS = 0,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    API_ERROR_INVALID_PARAM = -1,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    API_ERROR_OUT_OF_MEMORY = -2,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    API_ERROR_IO_FAILED = -3,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    API_ERROR_TIMEOUT = -4</t>
+  </si>
+  <si>
+    <t>} ApiError;</t>
+  </si>
+  <si>
+    <t>// Error context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ApiError code;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const char* message;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    const char* file;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int line;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int system_errno;</t>
+  </si>
+  <si>
+    <t>} ErrorContext;</t>
+  </si>
+  <si>
+    <t>// Error reporting macros</t>
+  </si>
+  <si>
+    <t>#define SET_ERROR(ctx, err_code, msg) do { \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (ctx)-&gt;code = (err_code); \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (ctx)-&gt;message = (msg); \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (ctx)-&gt;file = __FILE__; \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (ctx)-&gt;line = __LINE__; \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (ctx)-&gt;system_errno = errno; \</t>
+  </si>
+  <si>
+    <t>// Functions với error context</t>
+  </si>
+  <si>
+    <t>ApiError file_read(const char* filename, char** buffer, size_t* size, ErrorContext* error);</t>
+  </si>
+  <si>
+    <t>ApiError network_send(int socket, const void* data, size_t size, ErrorContext* error);</t>
+  </si>
+  <si>
+    <t>8.4 Thread Safety</t>
+  </si>
+  <si>
+    <t>// thread_safe_api.h</t>
+  </si>
+  <si>
+    <t>#ifndef THREAD_SAFE_API_H</t>
+  </si>
+  <si>
+    <t>#define THREAD_SAFE_API_H</t>
+  </si>
+  <si>
+    <t>// Thread-safe data structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    pthread_mutex_t mutex;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int initialized;</t>
+  </si>
+  <si>
+    <t>} ThreadSafeContainer;</t>
+  </si>
+  <si>
+    <t>// Thread-safe operations</t>
+  </si>
+  <si>
+    <t>ThreadSafeContainer* container_create(void);</t>
+  </si>
+  <si>
+    <t>int container_set(ThreadSafeContainer* container, const void* data, size_t size);</t>
+  </si>
+  <si>
+    <t>int container_get(ThreadSafeContainer* container, void* data, size_t size);</t>
+  </si>
+  <si>
+    <t>void container_destroy(ThreadSafeContainer* container);</t>
+  </si>
+  <si>
+    <t>// Lock-free alternatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    volatile int value;</t>
+  </si>
+  <si>
+    <t>} AtomicInt;</t>
+  </si>
+  <si>
+    <t>void atomic_int_init(AtomicInt* atomic, int value);</t>
+  </si>
+  <si>
+    <t>int atomic_int_get(const AtomicInt* atomic);</t>
+  </si>
+  <si>
+    <t>void atomic_int_set(AtomicInt* atomic, int value);</t>
+  </si>
+  <si>
+    <t>int atomic_int_compare_and_swap(AtomicInt* atomic, int expected, int desired);</t>
+  </si>
+  <si>
+    <t>9. Bẫy Thường Gặp và Cách Tránh</t>
+  </si>
+  <si>
+    <t>9.1 Multiple Definition Errors</t>
+  </si>
+  <si>
+    <t>❌ Sai:</t>
+  </si>
+  <si>
+    <t>int global_variable = 42;  // Định nghĩa trong header!</t>
+  </si>
+  <si>
+    <t>void function() {          // Định nghĩa function trong header!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Hello\n");</t>
+  </si>
+  <si>
+    <t>✅ Đúng:</t>
+  </si>
+  <si>
+    <t>extern int global_variable;  // Chỉ declaration</t>
+  </si>
+  <si>
+    <t>void function(void);         // Chỉ declaration</t>
+  </si>
+  <si>
+    <t>// utils.c</t>
+  </si>
+  <si>
+    <t>#include "utils.h"</t>
+  </si>
+  <si>
+    <t>int global_variable = 42;    // Definition trong source file</t>
+  </si>
+  <si>
+    <t>void function(void) {        // Definition trong source file</t>
+  </si>
+  <si>
+    <t>9.2 Circular Dependencies</t>
+  </si>
+  <si>
+    <t>❌ Vấn đề:</t>
+  </si>
+  <si>
+    <t>// a.h</t>
+  </si>
+  <si>
+    <t>#include "b.h"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    B* b_instance;</t>
+  </si>
+  <si>
+    <t>} A;</t>
+  </si>
+  <si>
+    <t>// b.h</t>
+  </si>
+  <si>
+    <t>#include "a.h"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    A* a_instance;</t>
+  </si>
+  <si>
+    <t>} B;</t>
+  </si>
+  <si>
+    <t>✅ Giải pháp:</t>
+  </si>
+  <si>
+    <t>#ifndef A_H</t>
+  </si>
+  <si>
+    <t>#define A_H</t>
+  </si>
+  <si>
+    <t>typedef struct B B;</t>
+  </si>
+  <si>
+    <t>typedef struct A {</t>
+  </si>
+  <si>
+    <t>#ifndef B_H</t>
+  </si>
+  <si>
+    <t>#define B_H</t>
+  </si>
+  <si>
+    <t>typedef struct A A;</t>
+  </si>
+  <si>
+    <t>typedef struct B {</t>
+  </si>
+  <si>
+    <t>9.3 Header Guard Naming Conflicts</t>
+  </si>
+  <si>
+    <t>❌ Nguy hiểm:</t>
+  </si>
+  <si>
+    <t>// Nhiều files có thể có cùng guard name</t>
+  </si>
+  <si>
+    <t>#ifndef UTILS_H  // Too generic!</t>
+  </si>
+  <si>
+    <t>✅ An toàn:</t>
+  </si>
+  <si>
+    <t>// Unique guard names</t>
+  </si>
+  <si>
+    <t>#ifndef PROJECT_MODULE_UTILS_H_INCLUDED</t>
+  </si>
+  <si>
+    <t>#define PROJECT_MODULE_UTILS_H_INCLUDED</t>
+  </si>
+  <si>
+    <t>9.4 Macro Side Effects</t>
+  </si>
+  <si>
+    <t>int x = 5;</t>
+  </si>
+  <si>
+    <t>int result = MAX(++x, 10);  // x có thể được tăng 2 lần!</t>
+  </si>
+  <si>
+    <t>✅ An toàn hơn:</t>
+  </si>
+  <si>
+    <t>// C99+ với typeof (GCC extension)</t>
+  </si>
+  <si>
+    <t>#define MAX(a, b) ({ \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    __typeof__(a) _a = (a); \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    __typeof__(b) _b = (b); \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (_a) &gt; (_b) ? (_a) : (_b); \</t>
+  </si>
+  <si>
+    <t>})</t>
+  </si>
+  <si>
+    <t>// Hoặc sử dụng inline functions</t>
+  </si>
+  <si>
+    <t>10. Ứng Dụng Thực Tế</t>
+  </si>
+  <si>
+    <t>10.1 Game Engine Module</t>
+  </si>
+  <si>
+    <t>// game_engine.h</t>
+  </si>
+  <si>
+    <t>#ifndef GAME_ENGINE_H</t>
+  </si>
+  <si>
+    <t>#define GAME_ENGINE_H</t>
+  </si>
+  <si>
+    <t>#include &lt;stdint.h&gt;</t>
+  </si>
+  <si>
+    <t>#include &lt;stdbool.h&gt;</t>
+  </si>
+  <si>
+    <t>// Core types</t>
+  </si>
+  <si>
+    <t>typedef struct Vector2 { float x, y; } Vector2;</t>
+  </si>
+  <si>
+    <t>typedef struct Color { uint8_t r, g, b, a; } Color;</t>
+  </si>
+  <si>
+    <t>typedef struct Texture Texture;</t>
+  </si>
+  <si>
+    <t>typedef struct Sprite Sprite;</t>
+  </si>
+  <si>
+    <t>// Engine subsystems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    bool (*init)(int width, int height);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void (*shutdown)(void);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void (*clear)(Color color);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void (*present)(void);</t>
+  </si>
+  <si>
+    <t>} RenderSystem;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    bool (*init)(void);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void (*update)(float delta_time);</t>
+  </si>
+  <si>
+    <t>} AudioSystem;</t>
+  </si>
+  <si>
+    <t>// Game object system</t>
+  </si>
+  <si>
+    <t>typedef struct GameObject {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    uint32_t id;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Vector2 position;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Vector2 velocity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float rotation;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void (*update)(struct GameObject* self, float delta_time);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void (*render)(struct GameObject* self);</t>
+  </si>
+  <si>
+    <t>} GameObject;</t>
+  </si>
+  <si>
+    <t>// Engine interface</t>
+  </si>
+  <si>
+    <t>extern const RenderSystem* render_system;</t>
+  </si>
+  <si>
+    <t>extern const AudioSystem* audio_system;</t>
+  </si>
+  <si>
+    <t>bool engine_init(int width, int height);</t>
+  </si>
+  <si>
+    <t>void engine_shutdown(void);</t>
+  </si>
+  <si>
+    <t>void engine_run(void);</t>
+  </si>
+  <si>
+    <t>GameObject* game_object_create(void);</t>
+  </si>
+  <si>
+    <t>void game_object_destroy(GameObject* obj);</t>
+  </si>
+  <si>
+    <t>10.2 Database Abstraction Layer</t>
+  </si>
+  <si>
+    <t>// database.h</t>
+  </si>
+  <si>
+    <t>#ifndef DATABASE_H</t>
+  </si>
+  <si>
+    <t>#define DATABASE_H</t>
+  </si>
+  <si>
+    <t>#include &lt;stddef.h&gt;</t>
+  </si>
+  <si>
+    <t>typedef struct Database Database;</t>
+  </si>
+  <si>
+    <t>typedef struct Statement Statement;</t>
+  </si>
+  <si>
+    <t>typedef struct ResultSet ResultSet;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DB_SUCCESS = 0,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DB_ERROR_CONNECTION_FAILED,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DB_ERROR_QUERY_FAILED,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DB_ERROR_NO_MORE_ROWS,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DB_ERROR_INVALID_COLUMN</t>
+  </si>
+  <si>
+    <t>} DatabaseError;</t>
+  </si>
+  <si>
+    <t>// Database interface</t>
+  </si>
+  <si>
+    <t>Database* db_connect(const char* connection_string);</t>
+  </si>
+  <si>
+    <t>void db_disconnect(Database* db);</t>
+  </si>
+  <si>
+    <t>DatabaseError db_execute(Database* db, const char* sql);</t>
+  </si>
+  <si>
+    <t>// Prepared statements</t>
+  </si>
+  <si>
+    <t>Statement* db_prepare(Database* db, const char* sql);</t>
+  </si>
+  <si>
+    <t>DatabaseError stmt_bind_int(Statement* stmt, int index, int value);</t>
+  </si>
+  <si>
+    <t>DatabaseError stmt_bind_string(Statement* stmt, int index, const char* value);</t>
+  </si>
+  <si>
+    <t>ResultSet* stmt_execute(Statement* stmt);</t>
+  </si>
+  <si>
+    <t>void stmt_destroy(Statement* stmt);</t>
+  </si>
+  <si>
+    <t>// Result set handling</t>
+  </si>
+  <si>
+    <t>bool result_next(ResultSet* rs);</t>
+  </si>
+  <si>
+    <t>int result_get_int(ResultSet* rs, int column);</t>
+  </si>
+  <si>
+    <t>const char* result_get_string(ResultSet* rs, int column);</t>
+  </si>
+  <si>
+    <t>void result_destroy(ResultSet* rs);</t>
+  </si>
+  <si>
+    <t>10.3 Cross-Platform File I/O</t>
+  </si>
+  <si>
+    <t>// file_io.h</t>
+  </si>
+  <si>
+    <t>#ifndef FILE_IO_H</t>
+  </si>
+  <si>
+    <t>#define FILE_IO_H</t>
+  </si>
+  <si>
+    <t>// Platform abstraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    typedef void* FileHandle;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #define INVALID_FILE_HANDLE NULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    typedef int FileHandle;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #define INVALID_FILE_HANDLE -1</t>
+  </si>
+  <si>
+    <t>// File operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FILE_MODE_READ,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FILE_MODE_WRITE,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FILE_MODE_APPEND,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FILE_MODE_READ_WRITE</t>
+  </si>
+  <si>
+    <t>} FileMode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FILE_SEEK_BEGIN,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FILE_SEEK_CURRENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FILE_SEEK_END</t>
+  </si>
+  <si>
+    <t>} FileSeekOrigin;</t>
+  </si>
+  <si>
+    <t>// File API</t>
+  </si>
+  <si>
+    <t>FileHandle file_open(const char* path, FileMode mode);</t>
+  </si>
+  <si>
+    <t>void file_close(FileHandle handle);</t>
+  </si>
+  <si>
+    <t>size_t file_read(FileHandle handle, void* buffer, size_t size);</t>
+  </si>
+  <si>
+    <t>size_t file_write(FileHandle handle, const void* buffer, size_t size);</t>
+  </si>
+  <si>
+    <t>bool file_seek(FileHandle handle, int64_t offset, FileSeekOrigin origin);</t>
+  </si>
+  <si>
+    <t>int64_t file_tell(FileHandle handle);</t>
+  </si>
+  <si>
+    <t>bool file_exists(const char* path);</t>
+  </si>
+  <si>
+    <t>int64_t file_size(const char* path);</t>
+  </si>
+  <si>
+    <t>// Directory operations</t>
+  </si>
+  <si>
+    <t>bool dir_create(const char* path);</t>
+  </si>
+  <si>
+    <t>bool dir_remove(const char* path);</t>
+  </si>
+  <si>
+    <t>bool dir_exists(const char* path);</t>
+  </si>
+  <si>
+    <t>// Path utilities</t>
+  </si>
+  <si>
+    <t>char* path_combine(const char* path1, const char* path2);</t>
+  </si>
+  <si>
+    <t>char* path_get_directory(const char* path);</t>
+  </si>
+  <si>
+    <t>char* path_get_filename(const char* path);</t>
+  </si>
+  <si>
+    <t>char* path_get_extension(const char* path);</t>
+  </si>
+  <si>
+    <t>11. Best Practices Tổng Hợp</t>
+  </si>
+  <si>
+    <t>11.1 Header Organization</t>
+  </si>
+  <si>
+    <t>// Thứ tự include chuẩn</t>
+  </si>
+  <si>
+    <t>#ifndef MY_MODULE_H</t>
+  </si>
+  <si>
+    <t>#define MY_MODULE_H</t>
+  </si>
+  <si>
+    <t>// 1. System headers</t>
+  </si>
+  <si>
+    <t>// 2. Third-party headers</t>
+  </si>
+  <si>
+    <t>#include &lt;curl/curl.h&gt;</t>
+  </si>
+  <si>
+    <t>// 3. Project headers</t>
+  </si>
+  <si>
+    <t>#include "common/types.h"</t>
+  </si>
+  <si>
+    <t>#include "utils/memory.h"</t>
+  </si>
+  <si>
+    <t>// 4. Local declarations</t>
+  </si>
+  <si>
+    <t>// ... nội dung header</t>
+  </si>
+  <si>
+    <t>11.2 Documentation Standards</t>
+  </si>
+  <si>
+    <t>/**</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @file network.h</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @brief Network communication utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @author Your Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @date 2024-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @version 1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> */</t>
+  </si>
+  <si>
+    <t>#ifndef NETWORK_H</t>
+  </si>
+  <si>
+    <t>#define NETWORK_H</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @brief Connects to a remote server</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @param hostname Server hostname or IP address</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @param port Server port number (1-65535)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @param timeout_ms Connection timeout in milliseconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @return Connection handle on success, NULL on failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @note The returned handle must be freed with network_disconnect()</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @warning This function is not thread-safe</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * @example</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * ```c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * NetworkHandle* conn = network_connect("example.com", 80, 5000);</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * if (conn) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *     // Use connection</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *     network_disconnect(conn);</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * }</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * ```</t>
+  </si>
+  <si>
+    <t>NetworkHandle* network_connect(const char* hostname, int port, int timeout_ms);</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6219,13 +7998,6 @@
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
       <charset val="163"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -6381,7 +8153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6461,13 +8233,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -6492,14 +8258,17 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6510,6 +8279,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6518,11 +8296,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7690,20 +9463,20 @@
       <c r="AW58" s="25"/>
     </row>
     <row r="59" spans="1:49">
-      <c r="Q59" s="36"/>
-      <c r="R59" s="36"/>
-      <c r="S59" s="36"/>
-      <c r="T59" s="36"/>
-      <c r="U59" s="36"/>
-      <c r="V59" s="36"/>
-      <c r="W59" s="36"/>
-      <c r="X59" s="36"/>
-      <c r="Y59" s="36"/>
-      <c r="Z59" s="36"/>
-      <c r="AA59" s="36"/>
-      <c r="AB59" s="36"/>
-      <c r="AC59" s="36"/>
-      <c r="AD59" s="36"/>
+      <c r="Q59" s="50"/>
+      <c r="R59" s="50"/>
+      <c r="S59" s="50"/>
+      <c r="T59" s="50"/>
+      <c r="U59" s="50"/>
+      <c r="V59" s="50"/>
+      <c r="W59" s="50"/>
+      <c r="X59" s="50"/>
+      <c r="Y59" s="50"/>
+      <c r="Z59" s="50"/>
+      <c r="AA59" s="50"/>
+      <c r="AB59" s="50"/>
+      <c r="AC59" s="50"/>
+      <c r="AD59" s="50"/>
       <c r="AI59" s="26"/>
       <c r="AJ59" s="25"/>
       <c r="AK59" s="25"/>
@@ -7735,24 +9508,24 @@
       <c r="J60" s="19"/>
       <c r="K60" s="19"/>
       <c r="L60" s="19"/>
-      <c r="Q60" s="37" t="s">
+      <c r="Q60" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="R60" s="37"/>
-      <c r="S60" s="37"/>
-      <c r="T60" s="37"/>
-      <c r="U60" s="37"/>
-      <c r="V60" s="37"/>
-      <c r="W60" s="37"/>
-      <c r="X60" s="37" t="s">
+      <c r="R60" s="51"/>
+      <c r="S60" s="51"/>
+      <c r="T60" s="51"/>
+      <c r="U60" s="51"/>
+      <c r="V60" s="51"/>
+      <c r="W60" s="51"/>
+      <c r="X60" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="Y60" s="37"/>
-      <c r="Z60" s="37"/>
-      <c r="AA60" s="37"/>
-      <c r="AB60" s="37"/>
-      <c r="AC60" s="37"/>
-      <c r="AD60" s="37"/>
+      <c r="Y60" s="51"/>
+      <c r="Z60" s="51"/>
+      <c r="AA60" s="51"/>
+      <c r="AB60" s="51"/>
+      <c r="AC60" s="51"/>
+      <c r="AD60" s="51"/>
       <c r="AI60" s="26"/>
       <c r="AJ60" s="25"/>
       <c r="AK60" s="25"/>
@@ -7773,24 +9546,24 @@
       <c r="B61" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="Q61" s="35" t="s">
+      <c r="Q61" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="R61" s="35"/>
-      <c r="S61" s="35"/>
-      <c r="T61" s="35"/>
-      <c r="U61" s="35"/>
-      <c r="V61" s="35"/>
-      <c r="W61" s="35"/>
-      <c r="X61" s="35" t="s">
+      <c r="R61" s="49"/>
+      <c r="S61" s="49"/>
+      <c r="T61" s="49"/>
+      <c r="U61" s="49"/>
+      <c r="V61" s="49"/>
+      <c r="W61" s="49"/>
+      <c r="X61" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="Y61" s="35"/>
-      <c r="Z61" s="35"/>
-      <c r="AA61" s="35"/>
-      <c r="AB61" s="35"/>
-      <c r="AC61" s="35"/>
-      <c r="AD61" s="35"/>
+      <c r="Y61" s="49"/>
+      <c r="Z61" s="49"/>
+      <c r="AA61" s="49"/>
+      <c r="AB61" s="49"/>
+      <c r="AC61" s="49"/>
+      <c r="AD61" s="49"/>
       <c r="AI61" s="25"/>
       <c r="AJ61" s="25"/>
       <c r="AK61" s="25"/>
@@ -7811,70 +9584,70 @@
       <c r="B62" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="Q62" s="35" t="s">
+      <c r="Q62" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="R62" s="35"/>
-      <c r="S62" s="35"/>
-      <c r="T62" s="35"/>
-      <c r="U62" s="35"/>
-      <c r="V62" s="35"/>
-      <c r="W62" s="35"/>
-      <c r="X62" s="35" t="s">
+      <c r="R62" s="49"/>
+      <c r="S62" s="49"/>
+      <c r="T62" s="49"/>
+      <c r="U62" s="49"/>
+      <c r="V62" s="49"/>
+      <c r="W62" s="49"/>
+      <c r="X62" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="Y62" s="35"/>
-      <c r="Z62" s="35"/>
-      <c r="AA62" s="35"/>
-      <c r="AB62" s="35"/>
-      <c r="AC62" s="35"/>
-      <c r="AD62" s="35"/>
+      <c r="Y62" s="49"/>
+      <c r="Z62" s="49"/>
+      <c r="AA62" s="49"/>
+      <c r="AB62" s="49"/>
+      <c r="AC62" s="49"/>
+      <c r="AD62" s="49"/>
     </row>
     <row r="63" spans="1:49" ht="14.25" customHeight="1">
       <c r="B63" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="Q63" s="35" t="s">
+      <c r="Q63" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="R63" s="35"/>
-      <c r="S63" s="35"/>
-      <c r="T63" s="35"/>
-      <c r="U63" s="35"/>
-      <c r="V63" s="35"/>
-      <c r="W63" s="35"/>
-      <c r="X63" s="35" t="s">
+      <c r="R63" s="49"/>
+      <c r="S63" s="49"/>
+      <c r="T63" s="49"/>
+      <c r="U63" s="49"/>
+      <c r="V63" s="49"/>
+      <c r="W63" s="49"/>
+      <c r="X63" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="Y63" s="35"/>
-      <c r="Z63" s="35"/>
-      <c r="AA63" s="35"/>
-      <c r="AB63" s="35"/>
-      <c r="AC63" s="35"/>
-      <c r="AD63" s="35"/>
+      <c r="Y63" s="49"/>
+      <c r="Z63" s="49"/>
+      <c r="AA63" s="49"/>
+      <c r="AB63" s="49"/>
+      <c r="AC63" s="49"/>
+      <c r="AD63" s="49"/>
     </row>
     <row r="64" spans="1:49" ht="18.75" customHeight="1">
       <c r="B64" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="Q64" s="35" t="s">
+      <c r="Q64" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="R64" s="35"/>
-      <c r="S64" s="35"/>
-      <c r="T64" s="35"/>
-      <c r="U64" s="35"/>
-      <c r="V64" s="35"/>
-      <c r="W64" s="35"/>
-      <c r="X64" s="35" t="s">
+      <c r="R64" s="49"/>
+      <c r="S64" s="49"/>
+      <c r="T64" s="49"/>
+      <c r="U64" s="49"/>
+      <c r="V64" s="49"/>
+      <c r="W64" s="49"/>
+      <c r="X64" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="Y64" s="35"/>
-      <c r="Z64" s="35"/>
-      <c r="AA64" s="35"/>
-      <c r="AB64" s="35"/>
-      <c r="AC64" s="35"/>
-      <c r="AD64" s="35"/>
+      <c r="Y64" s="49"/>
+      <c r="Z64" s="49"/>
+      <c r="AA64" s="49"/>
+      <c r="AB64" s="49"/>
+      <c r="AC64" s="49"/>
+      <c r="AD64" s="49"/>
     </row>
     <row r="65" spans="1:57">
       <c r="B65" s="11" t="s">
@@ -13148,18 +14921,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="X63:AD63"/>
+    <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="X59:AD59"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="X61:AD61"/>
+    <mergeCell ref="X62:AD62"/>
     <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q59:W59"/>
     <mergeCell ref="Q60:W60"/>
     <mergeCell ref="Q61:W61"/>
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="Q63:W63"/>
-    <mergeCell ref="X63:AD63"/>
-    <mergeCell ref="X64:AD64"/>
-    <mergeCell ref="X59:AD59"/>
-    <mergeCell ref="X60:AD60"/>
-    <mergeCell ref="X61:AD61"/>
-    <mergeCell ref="X62:AD62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13270,23 +15043,23 @@
       <c r="BW6" s="19"/>
     </row>
     <row r="7" spans="1:75" ht="15">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="43" t="s">
         <v>1012</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
-      <c r="U7" s="45" t="s">
+      <c r="U7" s="43" t="s">
         <v>1012</v>
       </c>
       <c r="V7" s="21"/>
       <c r="W7" s="21"/>
       <c r="X7" s="21"/>
-      <c r="AP7" s="45" t="s">
+      <c r="AP7" s="43" t="s">
         <v>1012</v>
       </c>
       <c r="AQ7" s="21"/>
       <c r="AR7" s="21"/>
-      <c r="BM7" s="45" t="s">
+      <c r="BM7" s="43" t="s">
         <v>1012</v>
       </c>
       <c r="BN7" s="21"/>
@@ -13335,26 +15108,26 @@
       </c>
     </row>
     <row r="12" spans="1:75" ht="15">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="43" t="s">
         <v>1015</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21"/>
-      <c r="U12" s="45" t="s">
+      <c r="U12" s="43" t="s">
         <v>1030</v>
       </c>
       <c r="V12" s="21"/>
       <c r="W12" s="21"/>
       <c r="X12" s="21"/>
-      <c r="AP12" s="45" t="s">
+      <c r="AP12" s="43" t="s">
         <v>1030</v>
       </c>
       <c r="AQ12" s="21"/>
       <c r="AR12" s="21"/>
       <c r="AS12" s="21"/>
-      <c r="BM12" s="45" t="s">
+      <c r="BM12" s="43" t="s">
         <v>1015</v>
       </c>
       <c r="BN12" s="21"/>
@@ -13419,7 +15192,7 @@
       <c r="U17" s="8" t="s">
         <v>1373</v>
       </c>
-      <c r="AP17" s="45" t="s">
+      <c r="AP17" s="43" t="s">
         <v>1050</v>
       </c>
       <c r="AQ17" s="21"/>
@@ -13429,7 +15202,7 @@
       <c r="AU17" s="21"/>
     </row>
     <row r="18" spans="1:68" ht="15">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="43" t="s">
         <v>1016</v>
       </c>
       <c r="B18" s="21"/>
@@ -13438,7 +15211,7 @@
       <c r="AQ18" s="11" t="s">
         <v>1051</v>
       </c>
-      <c r="BM18" s="45" t="s">
+      <c r="BM18" s="43" t="s">
         <v>1063</v>
       </c>
       <c r="BN18" s="21"/>
@@ -13449,7 +15222,7 @@
       <c r="B19" s="11" t="s">
         <v>1017</v>
       </c>
-      <c r="U19" s="45" t="s">
+      <c r="U19" s="43" t="s">
         <v>1031</v>
       </c>
       <c r="V19" s="21"/>
@@ -13491,7 +15264,7 @@
       <c r="B22" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="U22" s="45" t="s">
+      <c r="U22" s="43" t="s">
         <v>1033</v>
       </c>
       <c r="V22" s="21"/>
@@ -13501,7 +15274,7 @@
       <c r="Z22" s="21"/>
       <c r="AA22" s="21"/>
       <c r="AB22" s="21"/>
-      <c r="AP22" s="42" t="s">
+      <c r="AP22" s="40" t="s">
         <v>1054</v>
       </c>
       <c r="AQ22" s="22"/>
@@ -13515,7 +15288,7 @@
       <c r="V23" s="11" t="s">
         <v>1034</v>
       </c>
-      <c r="AP23" s="39" t="s">
+      <c r="AP23" s="37" t="s">
         <v>1396</v>
       </c>
       <c r="AQ23" s="22"/>
@@ -13529,7 +15302,7 @@
       <c r="V24" s="11" t="s">
         <v>1035</v>
       </c>
-      <c r="AP24" s="39" t="s">
+      <c r="AP24" s="37" t="s">
         <v>1401</v>
       </c>
       <c r="AQ24" s="22"/>
@@ -13540,7 +15313,7 @@
       <c r="B25" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="AP25" s="39"/>
+      <c r="AP25" s="37"/>
       <c r="AQ25" s="22" t="s">
         <v>1402</v>
       </c>
@@ -13555,7 +15328,7 @@
       <c r="V26" s="11" t="s">
         <v>1036</v>
       </c>
-      <c r="AP26" s="39" t="s">
+      <c r="AP26" s="37" t="s">
         <v>1397</v>
       </c>
       <c r="AQ26" s="22"/>
@@ -13567,7 +15340,7 @@
       <c r="V27" s="11" t="s">
         <v>1037</v>
       </c>
-      <c r="AP27" s="39"/>
+      <c r="AP27" s="37"/>
       <c r="AQ27" s="22" t="s">
         <v>1406</v>
       </c>
@@ -13581,7 +15354,7 @@
       <c r="V28" s="11" t="s">
         <v>1038</v>
       </c>
-      <c r="AP28" s="39"/>
+      <c r="AP28" s="37"/>
       <c r="AQ28" s="22" t="s">
         <v>1400</v>
       </c>
@@ -13595,13 +15368,13 @@
       <c r="V29" s="11" t="s">
         <v>1039</v>
       </c>
-      <c r="AP29" s="39" t="s">
+      <c r="AP29" s="37" t="s">
         <v>1404</v>
       </c>
       <c r="AQ29" s="22"/>
       <c r="AR29" s="22"/>
       <c r="AS29" s="22"/>
-      <c r="AX29" s="41"/>
+      <c r="AX29" s="39"/>
     </row>
     <row r="30" spans="1:68">
       <c r="B30" s="11" t="s">
@@ -13611,7 +15384,7 @@
         <v>1040</v>
       </c>
       <c r="AP30" s="22"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="41" t="s">
         <v>1403</v>
       </c>
       <c r="AR30" s="22"/>
@@ -13625,7 +15398,7 @@
         <v>1041</v>
       </c>
       <c r="AP31" s="22"/>
-      <c r="AQ31" s="43" t="s">
+      <c r="AQ31" s="41" t="s">
         <v>1407</v>
       </c>
       <c r="AR31" s="22"/>
@@ -13638,7 +15411,7 @@
       <c r="V32" s="11" t="s">
         <v>1042</v>
       </c>
-      <c r="AP32" s="39" t="s">
+      <c r="AP32" s="37" t="s">
         <v>1398</v>
       </c>
       <c r="AQ32" s="22"/>
@@ -13649,15 +15422,15 @@
       <c r="V33" s="11" t="s">
         <v>1043</v>
       </c>
-      <c r="AP33" s="39"/>
-      <c r="AQ33" s="42" t="s">
+      <c r="AP33" s="37"/>
+      <c r="AQ33" s="40" t="s">
         <v>1408</v>
       </c>
       <c r="AR33" s="22"/>
       <c r="AS33" s="22"/>
     </row>
     <row r="34" spans="1:59" ht="15">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="43" t="s">
         <v>1023</v>
       </c>
       <c r="B34" s="21"/>
@@ -13672,8 +15445,8 @@
       <c r="V34" s="11" t="s">
         <v>1044</v>
       </c>
-      <c r="AP34" s="39"/>
-      <c r="AQ34" s="42" t="s">
+      <c r="AP34" s="37"/>
+      <c r="AQ34" s="40" t="s">
         <v>1405</v>
       </c>
       <c r="AR34" s="22"/>
@@ -13686,7 +15459,7 @@
       <c r="V35" s="11" t="s">
         <v>1045</v>
       </c>
-      <c r="AP35" s="39"/>
+      <c r="AP35" s="37"/>
       <c r="AQ35" s="23" t="s">
         <v>1409</v>
       </c>
@@ -13700,7 +15473,7 @@
       <c r="V36" s="11" t="s">
         <v>1046</v>
       </c>
-      <c r="AP36" s="40" t="s">
+      <c r="AP36" s="38" t="s">
         <v>1399</v>
       </c>
       <c r="AQ36" s="22"/>
@@ -13712,7 +15485,7 @@
         <v>1025</v>
       </c>
       <c r="AP37" s="22"/>
-      <c r="AQ37" s="44" t="s">
+      <c r="AQ37" s="42" t="s">
         <v>1410</v>
       </c>
       <c r="AR37" s="22"/>
@@ -13720,7 +15493,7 @@
     </row>
     <row r="38" spans="1:59">
       <c r="AP38" s="22"/>
-      <c r="AQ38" s="44" t="s">
+      <c r="AQ38" s="42" t="s">
         <v>1411</v>
       </c>
       <c r="AR38" s="22"/>
@@ -13728,14 +15501,14 @@
     </row>
     <row r="39" spans="1:59">
       <c r="AP39" s="22"/>
-      <c r="AQ39" s="44" t="s">
+      <c r="AQ39" s="42" t="s">
         <v>1412</v>
       </c>
       <c r="AR39" s="22"/>
       <c r="AS39" s="22"/>
     </row>
     <row r="40" spans="1:59" ht="15">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="43" t="s">
         <v>1026</v>
       </c>
       <c r="B40" s="21"/>
@@ -13746,7 +15519,7 @@
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
       <c r="AP40" s="22"/>
-      <c r="AQ40" s="44" t="s">
+      <c r="AQ40" s="42" t="s">
         <v>1413</v>
       </c>
       <c r="AR40" s="22"/>
@@ -13758,7 +15531,7 @@
       </c>
     </row>
     <row r="42" spans="1:59" ht="15">
-      <c r="A42" s="38" t="s">
+      <c r="A42" s="36" t="s">
         <v>1367</v>
       </c>
       <c r="AP42" s="7" t="s">
@@ -13766,7 +15539,7 @@
       </c>
     </row>
     <row r="43" spans="1:59">
-      <c r="A43" s="38" t="s">
+      <c r="A43" s="36" t="s">
         <v>1368</v>
       </c>
       <c r="AQ43" s="11" t="s">
@@ -13927,7 +15700,7 @@
       <c r="AJ57" s="11" t="s">
         <v>1137</v>
       </c>
-      <c r="BB57" s="38" t="s">
+      <c r="BB57" s="36" t="s">
         <v>1381</v>
       </c>
     </row>
@@ -13952,7 +15725,7 @@
       <c r="AI59" s="7" t="s">
         <v>1138</v>
       </c>
-      <c r="BB59" s="38" t="s">
+      <c r="BB59" s="36" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -13960,7 +15733,7 @@
       <c r="AJ60" s="11" t="s">
         <v>1139</v>
       </c>
-      <c r="BB60" s="38" t="s">
+      <c r="BB60" s="36" t="s">
         <v>1382</v>
       </c>
     </row>
@@ -14018,7 +15791,7 @@
       <c r="AJ65" s="11" t="s">
         <v>1143</v>
       </c>
-      <c r="BB65" s="46" t="s">
+      <c r="BB65" s="44" t="s">
         <v>1161</v>
       </c>
     </row>
@@ -14032,7 +15805,7 @@
       <c r="AJ66" s="11" t="s">
         <v>1144</v>
       </c>
-      <c r="BB66" s="38" t="s">
+      <c r="BB66" s="36" t="s">
         <v>1162</v>
       </c>
     </row>
@@ -14046,7 +15819,7 @@
       <c r="AJ67" s="11" t="s">
         <v>1145</v>
       </c>
-      <c r="BB67" s="38" t="s">
+      <c r="BB67" s="36" t="s">
         <v>1163</v>
       </c>
     </row>
@@ -14513,58 +16286,58 @@
       <c r="Q120" s="11" t="s">
         <v>1202</v>
       </c>
-      <c r="AG120" s="48" t="s">
+      <c r="AG120" s="55" t="s">
         <v>1232</v>
       </c>
-      <c r="AH120" s="49"/>
-      <c r="AI120" s="49"/>
-      <c r="AJ120" s="49"/>
-      <c r="AK120" s="50"/>
-      <c r="AL120" s="48" t="s">
+      <c r="AH120" s="56"/>
+      <c r="AI120" s="56"/>
+      <c r="AJ120" s="56"/>
+      <c r="AK120" s="57"/>
+      <c r="AL120" s="55" t="s">
         <v>1233</v>
       </c>
-      <c r="AM120" s="49"/>
-      <c r="AN120" s="49"/>
-      <c r="AO120" s="49"/>
-      <c r="AP120" s="50"/>
-      <c r="AQ120" s="48" t="s">
+      <c r="AM120" s="56"/>
+      <c r="AN120" s="56"/>
+      <c r="AO120" s="56"/>
+      <c r="AP120" s="57"/>
+      <c r="AQ120" s="55" t="s">
         <v>1234</v>
       </c>
-      <c r="AR120" s="49"/>
-      <c r="AS120" s="49"/>
-      <c r="AT120" s="49"/>
-      <c r="AU120" s="49"/>
-      <c r="AV120" s="49"/>
-      <c r="AW120" s="50"/>
+      <c r="AR120" s="56"/>
+      <c r="AS120" s="56"/>
+      <c r="AT120" s="56"/>
+      <c r="AU120" s="56"/>
+      <c r="AV120" s="56"/>
+      <c r="AW120" s="57"/>
       <c r="BA120" s="13"/>
     </row>
     <row r="121" spans="2:53">
       <c r="Q121" s="11" t="s">
         <v>1203</v>
       </c>
-      <c r="AG121" s="51" t="s">
+      <c r="AG121" s="52" t="s">
         <v>1235</v>
       </c>
-      <c r="AH121" s="52"/>
-      <c r="AI121" s="52"/>
-      <c r="AJ121" s="52"/>
-      <c r="AK121" s="53"/>
-      <c r="AL121" s="54" t="s">
+      <c r="AH121" s="53"/>
+      <c r="AI121" s="53"/>
+      <c r="AJ121" s="53"/>
+      <c r="AK121" s="54"/>
+      <c r="AL121" s="58" t="s">
         <v>1236</v>
       </c>
-      <c r="AM121" s="55"/>
-      <c r="AN121" s="55"/>
-      <c r="AO121" s="55"/>
-      <c r="AP121" s="56"/>
-      <c r="AQ121" s="54" t="s">
+      <c r="AM121" s="59"/>
+      <c r="AN121" s="59"/>
+      <c r="AO121" s="59"/>
+      <c r="AP121" s="60"/>
+      <c r="AQ121" s="58" t="s">
         <v>1237</v>
       </c>
-      <c r="AR121" s="55"/>
-      <c r="AS121" s="55"/>
-      <c r="AT121" s="55"/>
-      <c r="AU121" s="55"/>
-      <c r="AV121" s="55"/>
-      <c r="AW121" s="56"/>
+      <c r="AR121" s="59"/>
+      <c r="AS121" s="59"/>
+      <c r="AT121" s="59"/>
+      <c r="AU121" s="59"/>
+      <c r="AV121" s="59"/>
+      <c r="AW121" s="60"/>
       <c r="BA121" s="11" t="s">
         <v>1269</v>
       </c>
@@ -14573,87 +16346,87 @@
       <c r="Q122" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="AG122" s="51" t="s">
+      <c r="AG122" s="52" t="s">
         <v>1238</v>
       </c>
-      <c r="AH122" s="52"/>
-      <c r="AI122" s="52"/>
-      <c r="AJ122" s="52"/>
-      <c r="AK122" s="53"/>
-      <c r="AL122" s="51" t="s">
+      <c r="AH122" s="53"/>
+      <c r="AI122" s="53"/>
+      <c r="AJ122" s="53"/>
+      <c r="AK122" s="54"/>
+      <c r="AL122" s="52" t="s">
         <v>1239</v>
       </c>
-      <c r="AM122" s="52"/>
-      <c r="AN122" s="52"/>
-      <c r="AO122" s="52"/>
-      <c r="AP122" s="53"/>
-      <c r="AQ122" s="51" t="s">
+      <c r="AM122" s="53"/>
+      <c r="AN122" s="53"/>
+      <c r="AO122" s="53"/>
+      <c r="AP122" s="54"/>
+      <c r="AQ122" s="52" t="s">
         <v>1240</v>
       </c>
-      <c r="AR122" s="52"/>
-      <c r="AS122" s="52"/>
-      <c r="AT122" s="52"/>
-      <c r="AU122" s="52"/>
-      <c r="AV122" s="52"/>
-      <c r="AW122" s="53"/>
+      <c r="AR122" s="53"/>
+      <c r="AS122" s="53"/>
+      <c r="AT122" s="53"/>
+      <c r="AU122" s="53"/>
+      <c r="AV122" s="53"/>
+      <c r="AW122" s="54"/>
       <c r="BA122" s="11" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="123" spans="2:53">
       <c r="Q123" s="13"/>
-      <c r="AG123" s="51" t="s">
+      <c r="AG123" s="52" t="s">
         <v>1241</v>
       </c>
-      <c r="AH123" s="52"/>
-      <c r="AI123" s="52"/>
-      <c r="AJ123" s="52"/>
-      <c r="AK123" s="53"/>
-      <c r="AL123" s="51" t="s">
+      <c r="AH123" s="53"/>
+      <c r="AI123" s="53"/>
+      <c r="AJ123" s="53"/>
+      <c r="AK123" s="54"/>
+      <c r="AL123" s="52" t="s">
         <v>1242</v>
       </c>
-      <c r="AM123" s="52"/>
-      <c r="AN123" s="52"/>
-      <c r="AO123" s="52"/>
-      <c r="AP123" s="53"/>
-      <c r="AQ123" s="51" t="s">
+      <c r="AM123" s="53"/>
+      <c r="AN123" s="53"/>
+      <c r="AO123" s="53"/>
+      <c r="AP123" s="54"/>
+      <c r="AQ123" s="52" t="s">
         <v>1243</v>
       </c>
-      <c r="AR123" s="52"/>
-      <c r="AS123" s="52"/>
-      <c r="AT123" s="52"/>
-      <c r="AU123" s="52"/>
-      <c r="AV123" s="52"/>
-      <c r="AW123" s="53"/>
+      <c r="AR123" s="53"/>
+      <c r="AS123" s="53"/>
+      <c r="AT123" s="53"/>
+      <c r="AU123" s="53"/>
+      <c r="AV123" s="53"/>
+      <c r="AW123" s="54"/>
       <c r="BA123" s="13"/>
     </row>
     <row r="124" spans="2:53">
       <c r="Q124" s="11" t="s">
         <v>1204</v>
       </c>
-      <c r="AG124" s="51" t="s">
+      <c r="AG124" s="52" t="s">
         <v>1244</v>
       </c>
-      <c r="AH124" s="52"/>
-      <c r="AI124" s="52"/>
-      <c r="AJ124" s="52"/>
-      <c r="AK124" s="53"/>
-      <c r="AL124" s="51" t="s">
+      <c r="AH124" s="53"/>
+      <c r="AI124" s="53"/>
+      <c r="AJ124" s="53"/>
+      <c r="AK124" s="54"/>
+      <c r="AL124" s="52" t="s">
         <v>1245</v>
       </c>
-      <c r="AM124" s="52"/>
-      <c r="AN124" s="52"/>
-      <c r="AO124" s="52"/>
-      <c r="AP124" s="53"/>
-      <c r="AQ124" s="51" t="s">
+      <c r="AM124" s="53"/>
+      <c r="AN124" s="53"/>
+      <c r="AO124" s="53"/>
+      <c r="AP124" s="54"/>
+      <c r="AQ124" s="52" t="s">
         <v>1246</v>
       </c>
-      <c r="AR124" s="52"/>
-      <c r="AS124" s="52"/>
-      <c r="AT124" s="52"/>
-      <c r="AU124" s="52"/>
-      <c r="AV124" s="52"/>
-      <c r="AW124" s="53"/>
+      <c r="AR124" s="53"/>
+      <c r="AS124" s="53"/>
+      <c r="AT124" s="53"/>
+      <c r="AU124" s="53"/>
+      <c r="AV124" s="53"/>
+      <c r="AW124" s="54"/>
       <c r="BA124" s="11" t="s">
         <v>1271</v>
       </c>
@@ -14662,29 +16435,29 @@
       <c r="Q125" s="11" t="s">
         <v>1205</v>
       </c>
-      <c r="AG125" s="51" t="s">
+      <c r="AG125" s="52" t="s">
         <v>1247</v>
       </c>
-      <c r="AH125" s="52"/>
-      <c r="AI125" s="52"/>
-      <c r="AJ125" s="52"/>
-      <c r="AK125" s="53"/>
-      <c r="AL125" s="51" t="s">
+      <c r="AH125" s="53"/>
+      <c r="AI125" s="53"/>
+      <c r="AJ125" s="53"/>
+      <c r="AK125" s="54"/>
+      <c r="AL125" s="52" t="s">
         <v>1248</v>
       </c>
-      <c r="AM125" s="52"/>
-      <c r="AN125" s="52"/>
-      <c r="AO125" s="52"/>
-      <c r="AP125" s="53"/>
-      <c r="AQ125" s="51" t="s">
+      <c r="AM125" s="53"/>
+      <c r="AN125" s="53"/>
+      <c r="AO125" s="53"/>
+      <c r="AP125" s="54"/>
+      <c r="AQ125" s="52" t="s">
         <v>1249</v>
       </c>
-      <c r="AR125" s="52"/>
-      <c r="AS125" s="52"/>
-      <c r="AT125" s="52"/>
-      <c r="AU125" s="52"/>
-      <c r="AV125" s="52"/>
-      <c r="AW125" s="53"/>
+      <c r="AR125" s="53"/>
+      <c r="AS125" s="53"/>
+      <c r="AT125" s="53"/>
+      <c r="AU125" s="53"/>
+      <c r="AV125" s="53"/>
+      <c r="AW125" s="54"/>
       <c r="BA125" s="11" t="s">
         <v>1272</v>
       </c>
@@ -14693,29 +16466,29 @@
       <c r="Q126" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="AG126" s="51" t="s">
+      <c r="AG126" s="52" t="s">
         <v>1250</v>
       </c>
-      <c r="AH126" s="52"/>
-      <c r="AI126" s="52"/>
-      <c r="AJ126" s="52"/>
-      <c r="AK126" s="53"/>
-      <c r="AL126" s="51" t="s">
+      <c r="AH126" s="53"/>
+      <c r="AI126" s="53"/>
+      <c r="AJ126" s="53"/>
+      <c r="AK126" s="54"/>
+      <c r="AL126" s="52" t="s">
         <v>1251</v>
       </c>
-      <c r="AM126" s="52"/>
-      <c r="AN126" s="52"/>
-      <c r="AO126" s="52"/>
-      <c r="AP126" s="53"/>
-      <c r="AQ126" s="51" t="s">
+      <c r="AM126" s="53"/>
+      <c r="AN126" s="53"/>
+      <c r="AO126" s="53"/>
+      <c r="AP126" s="54"/>
+      <c r="AQ126" s="52" t="s">
         <v>1252</v>
       </c>
-      <c r="AR126" s="52"/>
-      <c r="AS126" s="52"/>
-      <c r="AT126" s="52"/>
-      <c r="AU126" s="52"/>
-      <c r="AV126" s="52"/>
-      <c r="AW126" s="53"/>
+      <c r="AR126" s="53"/>
+      <c r="AS126" s="53"/>
+      <c r="AT126" s="53"/>
+      <c r="AU126" s="53"/>
+      <c r="AV126" s="53"/>
+      <c r="AW126" s="54"/>
       <c r="BA126" s="11" t="s">
         <v>112</v>
       </c>
@@ -14724,29 +16497,29 @@
       <c r="Q127" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="AG127" s="51" t="s">
+      <c r="AG127" s="52" t="s">
         <v>1253</v>
       </c>
-      <c r="AH127" s="52"/>
-      <c r="AI127" s="52"/>
-      <c r="AJ127" s="52"/>
-      <c r="AK127" s="53"/>
-      <c r="AL127" s="51" t="s">
+      <c r="AH127" s="53"/>
+      <c r="AI127" s="53"/>
+      <c r="AJ127" s="53"/>
+      <c r="AK127" s="54"/>
+      <c r="AL127" s="52" t="s">
         <v>1254</v>
       </c>
-      <c r="AM127" s="52"/>
-      <c r="AN127" s="52"/>
-      <c r="AO127" s="52"/>
-      <c r="AP127" s="53"/>
-      <c r="AQ127" s="51" t="s">
+      <c r="AM127" s="53"/>
+      <c r="AN127" s="53"/>
+      <c r="AO127" s="53"/>
+      <c r="AP127" s="54"/>
+      <c r="AQ127" s="52" t="s">
         <v>1255</v>
       </c>
-      <c r="AR127" s="52"/>
-      <c r="AS127" s="52"/>
-      <c r="AT127" s="52"/>
-      <c r="AU127" s="52"/>
-      <c r="AV127" s="52"/>
-      <c r="AW127" s="53"/>
+      <c r="AR127" s="53"/>
+      <c r="AS127" s="53"/>
+      <c r="AT127" s="53"/>
+      <c r="AU127" s="53"/>
+      <c r="AV127" s="53"/>
+      <c r="AW127" s="54"/>
     </row>
     <row r="128" spans="2:53" ht="15">
       <c r="Q128" s="13"/>
@@ -14758,7 +16531,7 @@
       <c r="Q129" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="AE129" s="42" t="s">
+      <c r="AE129" s="40" t="s">
         <v>1417</v>
       </c>
       <c r="AF129" s="22"/>
@@ -14810,70 +16583,70 @@
       <c r="Q134" s="11" t="s">
         <v>1210</v>
       </c>
-      <c r="AA134" s="57" t="s">
+      <c r="AA134" s="46" t="s">
         <v>1420</v>
       </c>
-      <c r="AB134" s="58"/>
-      <c r="AC134" s="58"/>
-      <c r="AD134" s="58"/>
-      <c r="AE134" s="58"/>
-      <c r="AF134" s="58"/>
-      <c r="AG134" s="58"/>
-      <c r="AH134" s="58"/>
-      <c r="AI134" s="58"/>
-      <c r="AJ134" s="58"/>
-      <c r="AK134" s="58"/>
-      <c r="AL134" s="58"/>
-      <c r="AM134" s="58"/>
-      <c r="AN134" s="58"/>
-      <c r="AO134" s="58"/>
-      <c r="AP134" s="58"/>
-      <c r="AQ134" s="58"/>
-      <c r="AR134" s="58"/>
-      <c r="AS134" s="58"/>
-      <c r="AT134" s="58"/>
-      <c r="AU134" s="58"/>
-      <c r="AV134" s="58"/>
-      <c r="AW134" s="58"/>
-      <c r="AX134" s="58"/>
-      <c r="AY134" s="58"/>
-      <c r="AZ134" s="58"/>
+      <c r="AB134" s="47"/>
+      <c r="AC134" s="47"/>
+      <c r="AD134" s="47"/>
+      <c r="AE134" s="47"/>
+      <c r="AF134" s="47"/>
+      <c r="AG134" s="47"/>
+      <c r="AH134" s="47"/>
+      <c r="AI134" s="47"/>
+      <c r="AJ134" s="47"/>
+      <c r="AK134" s="47"/>
+      <c r="AL134" s="47"/>
+      <c r="AM134" s="47"/>
+      <c r="AN134" s="47"/>
+      <c r="AO134" s="47"/>
+      <c r="AP134" s="47"/>
+      <c r="AQ134" s="47"/>
+      <c r="AR134" s="47"/>
+      <c r="AS134" s="47"/>
+      <c r="AT134" s="47"/>
+      <c r="AU134" s="47"/>
+      <c r="AV134" s="47"/>
+      <c r="AW134" s="47"/>
+      <c r="AX134" s="47"/>
+      <c r="AY134" s="47"/>
+      <c r="AZ134" s="47"/>
       <c r="BA134" s="12"/>
-      <c r="BB134" s="38" t="s">
+      <c r="BB134" s="36" t="s">
         <v>1386</v>
       </c>
     </row>
     <row r="135" spans="17:54" ht="15">
       <c r="Q135" s="13"/>
-      <c r="AA135" s="59" t="s">
+      <c r="AA135" s="48" t="s">
         <v>1418</v>
       </c>
-      <c r="AB135" s="58"/>
-      <c r="AC135" s="58"/>
-      <c r="AD135" s="58"/>
-      <c r="AE135" s="58"/>
-      <c r="AF135" s="58"/>
-      <c r="AG135" s="58"/>
-      <c r="AH135" s="58"/>
-      <c r="AI135" s="58"/>
-      <c r="AJ135" s="58"/>
-      <c r="AK135" s="58"/>
-      <c r="AL135" s="58"/>
-      <c r="AM135" s="58"/>
-      <c r="AN135" s="58"/>
-      <c r="AO135" s="58"/>
-      <c r="AP135" s="58"/>
-      <c r="AQ135" s="58"/>
-      <c r="AR135" s="58"/>
-      <c r="AS135" s="58"/>
-      <c r="AT135" s="58"/>
-      <c r="AU135" s="58"/>
-      <c r="AV135" s="58"/>
-      <c r="AW135" s="58"/>
-      <c r="AX135" s="58"/>
-      <c r="AY135" s="58"/>
-      <c r="AZ135" s="58"/>
-      <c r="BB135" s="38" t="s">
+      <c r="AB135" s="47"/>
+      <c r="AC135" s="47"/>
+      <c r="AD135" s="47"/>
+      <c r="AE135" s="47"/>
+      <c r="AF135" s="47"/>
+      <c r="AG135" s="47"/>
+      <c r="AH135" s="47"/>
+      <c r="AI135" s="47"/>
+      <c r="AJ135" s="47"/>
+      <c r="AK135" s="47"/>
+      <c r="AL135" s="47"/>
+      <c r="AM135" s="47"/>
+      <c r="AN135" s="47"/>
+      <c r="AO135" s="47"/>
+      <c r="AP135" s="47"/>
+      <c r="AQ135" s="47"/>
+      <c r="AR135" s="47"/>
+      <c r="AS135" s="47"/>
+      <c r="AT135" s="47"/>
+      <c r="AU135" s="47"/>
+      <c r="AV135" s="47"/>
+      <c r="AW135" s="47"/>
+      <c r="AX135" s="47"/>
+      <c r="AY135" s="47"/>
+      <c r="AZ135" s="47"/>
+      <c r="BB135" s="36" t="s">
         <v>1387</v>
       </c>
     </row>
@@ -14881,41 +16654,41 @@
       <c r="Q136" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="AA136" s="59" t="s">
+      <c r="AA136" s="48" t="s">
         <v>1419</v>
       </c>
-      <c r="AB136" s="58"/>
-      <c r="AC136" s="58"/>
-      <c r="AD136" s="58"/>
-      <c r="AE136" s="58"/>
-      <c r="AF136" s="58"/>
-      <c r="AG136" s="58"/>
-      <c r="AH136" s="58"/>
-      <c r="AI136" s="58"/>
-      <c r="AJ136" s="58"/>
-      <c r="AK136" s="58"/>
-      <c r="AL136" s="58"/>
-      <c r="AM136" s="58"/>
-      <c r="AN136" s="58"/>
-      <c r="AO136" s="58"/>
-      <c r="AP136" s="58"/>
-      <c r="AQ136" s="58"/>
-      <c r="AR136" s="58"/>
-      <c r="AS136" s="58"/>
-      <c r="AT136" s="58"/>
-      <c r="AU136" s="58"/>
-      <c r="AV136" s="58"/>
-      <c r="AW136" s="58"/>
-      <c r="AX136" s="58"/>
-      <c r="AY136" s="58"/>
-      <c r="AZ136" s="58"/>
-      <c r="BB136" s="38" t="s">
+      <c r="AB136" s="47"/>
+      <c r="AC136" s="47"/>
+      <c r="AD136" s="47"/>
+      <c r="AE136" s="47"/>
+      <c r="AF136" s="47"/>
+      <c r="AG136" s="47"/>
+      <c r="AH136" s="47"/>
+      <c r="AI136" s="47"/>
+      <c r="AJ136" s="47"/>
+      <c r="AK136" s="47"/>
+      <c r="AL136" s="47"/>
+      <c r="AM136" s="47"/>
+      <c r="AN136" s="47"/>
+      <c r="AO136" s="47"/>
+      <c r="AP136" s="47"/>
+      <c r="AQ136" s="47"/>
+      <c r="AR136" s="47"/>
+      <c r="AS136" s="47"/>
+      <c r="AT136" s="47"/>
+      <c r="AU136" s="47"/>
+      <c r="AV136" s="47"/>
+      <c r="AW136" s="47"/>
+      <c r="AX136" s="47"/>
+      <c r="AY136" s="47"/>
+      <c r="AZ136" s="47"/>
+      <c r="BB136" s="36" t="s">
         <v>1388</v>
       </c>
     </row>
     <row r="137" spans="17:54">
       <c r="Q137" s="13"/>
-      <c r="BB137" s="38" t="s">
+      <c r="BB137" s="36" t="s">
         <v>1389</v>
       </c>
     </row>
@@ -14923,7 +16696,7 @@
       <c r="Q138" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="BB138" s="38" t="s">
+      <c r="BB138" s="36" t="s">
         <v>1390</v>
       </c>
     </row>
@@ -15139,7 +16912,7 @@
     </row>
     <row r="164" spans="1:44" ht="15" thickBot="1"/>
     <row r="165" spans="1:44" s="15" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A165" s="47" t="s">
+      <c r="A165" s="45" t="s">
         <v>1302</v>
       </c>
     </row>
@@ -15532,6 +17305,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="AG125:AK125"/>
+    <mergeCell ref="AG126:AK126"/>
+    <mergeCell ref="AG127:AK127"/>
+    <mergeCell ref="AG120:AK120"/>
+    <mergeCell ref="AG121:AK121"/>
+    <mergeCell ref="AG122:AK122"/>
+    <mergeCell ref="AG123:AK123"/>
+    <mergeCell ref="AG124:AK124"/>
     <mergeCell ref="AL126:AP126"/>
     <mergeCell ref="AL127:AP127"/>
     <mergeCell ref="AQ120:AW120"/>
@@ -15548,14 +17329,6 @@
     <mergeCell ref="AL123:AP123"/>
     <mergeCell ref="AL124:AP124"/>
     <mergeCell ref="AL125:AP125"/>
-    <mergeCell ref="AG120:AK120"/>
-    <mergeCell ref="AG121:AK121"/>
-    <mergeCell ref="AG122:AK122"/>
-    <mergeCell ref="AG123:AK123"/>
-    <mergeCell ref="AG124:AK124"/>
-    <mergeCell ref="AG125:AK125"/>
-    <mergeCell ref="AG126:AK126"/>
-    <mergeCell ref="AG127:AK127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -15564,9 +17337,3405 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:BY385"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="16384" width="3.125" style="35"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:58" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A1" s="14" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="2" spans="1:58" ht="15">
+      <c r="A2" s="18" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="AF2" s="18" t="s">
+        <v>1427</v>
+      </c>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="19"/>
+      <c r="AP2" s="19"/>
+      <c r="AQ2" s="19"/>
+      <c r="AW2" s="18" t="s">
+        <v>1443</v>
+      </c>
+      <c r="AX2" s="19"/>
+      <c r="AY2" s="19"/>
+      <c r="AZ2" s="19"/>
+      <c r="BA2" s="19"/>
+      <c r="BB2" s="19"/>
+      <c r="BC2" s="19"/>
+      <c r="BD2" s="19"/>
+      <c r="BE2" s="19"/>
+      <c r="BF2" s="19"/>
+    </row>
+    <row r="3" spans="1:58" ht="15">
+      <c r="A3" s="35" t="s">
+        <v>1423</v>
+      </c>
+      <c r="AG3" s="11" t="s">
+        <v>1428</v>
+      </c>
+      <c r="AW3" s="40" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58">
+      <c r="A4" s="12" t="s">
+        <v>1424</v>
+      </c>
+      <c r="AG4" s="11" t="s">
+        <v>1429</v>
+      </c>
+      <c r="AW4" s="23" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="5" spans="1:58">
+      <c r="A5" s="12" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AG5" s="11" t="s">
+        <v>1430</v>
+      </c>
+      <c r="AW5" s="23" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
+      <c r="A6" s="12" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AG6" s="13"/>
+      <c r="AW6" s="23" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58">
+      <c r="AG7" s="11" t="s">
+        <v>1431</v>
+      </c>
+      <c r="AW7" s="23" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="8" spans="1:58">
+      <c r="AG8" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="AW8" s="22"/>
+    </row>
+    <row r="9" spans="1:58" ht="15">
+      <c r="AG9" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW9" s="40" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:58">
+      <c r="AG10" s="13"/>
+      <c r="AW10" s="23" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58">
+      <c r="AG11" s="11" t="s">
+        <v>1432</v>
+      </c>
+      <c r="AW11" s="23" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58">
+      <c r="AG12" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="AW12" s="23" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
+      <c r="AG13" s="11" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58">
+      <c r="AG14" s="13"/>
+    </row>
+    <row r="15" spans="1:58">
+      <c r="AG15" s="11" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58">
+      <c r="AG16" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:49">
+      <c r="AG17" s="11" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="18" spans="1:49">
+      <c r="AG18" s="11" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="19" spans="1:49">
+      <c r="AG19" s="13"/>
+    </row>
+    <row r="20" spans="1:49">
+      <c r="AG20" s="11" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49">
+      <c r="AG21" s="11" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49">
+      <c r="AG22" s="11" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49">
+      <c r="AG23" s="13"/>
+    </row>
+    <row r="24" spans="1:49">
+      <c r="AG24" s="11" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49">
+      <c r="AG25" s="11" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49">
+      <c r="AG26" s="13"/>
+    </row>
+    <row r="27" spans="1:49" ht="15" thickBot="1">
+      <c r="AG27" s="11" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A28" s="14" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49" ht="15">
+      <c r="A29" s="18" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="S29" s="18" t="s">
+        <v>1465</v>
+      </c>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="19"/>
+      <c r="Z29" s="19"/>
+      <c r="AA29" s="19"/>
+      <c r="AK29" s="18" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AL29" s="19"/>
+      <c r="AM29" s="19"/>
+      <c r="AN29" s="19"/>
+      <c r="AO29" s="19"/>
+      <c r="AP29" s="19"/>
+      <c r="AQ29" s="19"/>
+      <c r="AR29" s="19"/>
+      <c r="AS29" s="19"/>
+      <c r="AT29" s="19"/>
+      <c r="AU29" s="19"/>
+      <c r="AV29" s="19"/>
+      <c r="AW29" s="19"/>
+    </row>
+    <row r="30" spans="1:49" ht="15">
+      <c r="A30" s="11" t="s">
+        <v>1455</v>
+      </c>
+      <c r="S30" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="AK30" s="11" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49">
+      <c r="A31" s="11" t="s">
+        <v>1456</v>
+      </c>
+      <c r="T31" s="11" t="s">
+        <v>1467</v>
+      </c>
+      <c r="AK31" s="11" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="32" spans="1:49">
+      <c r="A32" s="11" t="s">
+        <v>1457</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>1468</v>
+      </c>
+      <c r="AK32" s="11" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37">
+      <c r="A33" s="13"/>
+      <c r="T33" s="11" t="s">
+        <v>939</v>
+      </c>
+      <c r="AK33" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37">
+      <c r="A34" s="11" t="s">
+        <v>1458</v>
+      </c>
+      <c r="T34" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="AK34" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37">
+      <c r="A35" s="11" t="s">
+        <v>1459</v>
+      </c>
+      <c r="T35" s="13"/>
+      <c r="AK35" s="13"/>
+    </row>
+    <row r="36" spans="1:37">
+      <c r="A36" s="11" t="s">
+        <v>1460</v>
+      </c>
+      <c r="T36" s="11" t="s">
+        <v>1469</v>
+      </c>
+      <c r="AK36" s="11" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37">
+      <c r="A37" s="11" t="s">
+        <v>1461</v>
+      </c>
+      <c r="T37" s="11" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK37" s="11" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37">
+      <c r="A38" s="13"/>
+      <c r="T38" s="11" t="s">
+        <v>1471</v>
+      </c>
+      <c r="AK38" s="11" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37">
+      <c r="A39" s="11" t="s">
+        <v>1462</v>
+      </c>
+      <c r="T39" s="11" t="s">
+        <v>1472</v>
+      </c>
+      <c r="AK39" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37">
+      <c r="T40" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="AK40" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" ht="15">
+      <c r="A41" s="9" t="s">
+        <v>1463</v>
+      </c>
+      <c r="T41" s="13"/>
+    </row>
+    <row r="42" spans="1:37">
+      <c r="A42" s="11" t="s">
+        <v>1464</v>
+      </c>
+      <c r="T42" s="11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37">
+      <c r="A43" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="T43" s="11" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37">
+      <c r="A44" s="13"/>
+      <c r="T44" s="11" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="45" spans="1:37">
+      <c r="A45" s="11" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37" ht="15">
+      <c r="S46" s="7" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37">
+      <c r="T47" s="11" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="48" spans="1:37">
+      <c r="T48" s="11" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="49" spans="1:55">
+      <c r="T49" s="11" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="50" spans="1:55">
+      <c r="T50" s="13"/>
+    </row>
+    <row r="51" spans="1:55">
+      <c r="T51" s="11" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="52" spans="1:55">
+      <c r="T52" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="53" spans="1:55">
+      <c r="T53" s="11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:55" ht="15" thickBot="1">
+      <c r="T54" s="11" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="55" spans="1:55" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A55" s="14" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="56" spans="1:55" ht="15">
+      <c r="A56" s="18" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="AB56" s="18" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AC56" s="19"/>
+      <c r="AD56" s="19"/>
+      <c r="AE56" s="19"/>
+      <c r="AF56" s="19"/>
+      <c r="AG56" s="19"/>
+      <c r="AH56" s="19"/>
+      <c r="AV56" s="18" t="s">
+        <v>1507</v>
+      </c>
+      <c r="AW56" s="19"/>
+      <c r="AX56" s="19"/>
+      <c r="AY56" s="19"/>
+      <c r="AZ56" s="19"/>
+      <c r="BA56" s="19"/>
+      <c r="BB56" s="19"/>
+      <c r="BC56" s="19"/>
+    </row>
+    <row r="57" spans="1:55">
+      <c r="A57" s="11" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="58" spans="1:55">
+      <c r="A58" s="11" t="s">
+        <v>1489</v>
+      </c>
+      <c r="AB58" s="11" t="s">
+        <v>1501</v>
+      </c>
+      <c r="AV58" s="11" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="59" spans="1:55">
+      <c r="A59" s="11" t="s">
+        <v>1490</v>
+      </c>
+      <c r="AB59" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="AV59" s="11" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="60" spans="1:55">
+      <c r="A60" s="13"/>
+      <c r="AB60" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="AV60" s="11" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="61" spans="1:55">
+      <c r="A61" s="11" t="s">
+        <v>1491</v>
+      </c>
+      <c r="AB61" s="13"/>
+      <c r="AV61" s="13"/>
+    </row>
+    <row r="62" spans="1:55">
+      <c r="A62" s="11" t="s">
+        <v>1492</v>
+      </c>
+      <c r="AB62" s="11" t="s">
+        <v>1502</v>
+      </c>
+      <c r="AV62" s="11" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="63" spans="1:55">
+      <c r="A63" s="11" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AB63" s="13"/>
+      <c r="AV63" s="11" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="64" spans="1:55">
+      <c r="A64" s="11" t="s">
+        <v>1494</v>
+      </c>
+      <c r="AB64" s="11" t="s">
+        <v>1503</v>
+      </c>
+      <c r="AV64" s="11" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="65" spans="1:49">
+      <c r="A65" s="13"/>
+      <c r="AB65" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AV65" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:49">
+      <c r="A66" s="11" t="s">
+        <v>1495</v>
+      </c>
+      <c r="AB66" s="11" t="s">
+        <v>1505</v>
+      </c>
+      <c r="AV66" s="13"/>
+    </row>
+    <row r="67" spans="1:49">
+      <c r="A67" s="11" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AB67" s="11" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AV67" s="11" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="68" spans="1:49">
+      <c r="A68" s="13"/>
+      <c r="AB68" s="13"/>
+      <c r="AV68" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:49">
+      <c r="A69" s="11" t="s">
+        <v>1497</v>
+      </c>
+      <c r="AB69" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV69" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:49">
+      <c r="A70" s="11" t="s">
+        <v>1498</v>
+      </c>
+      <c r="AV70" s="13"/>
+    </row>
+    <row r="71" spans="1:49">
+      <c r="A71" s="11" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AV71" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:49">
+      <c r="A72" s="13"/>
+    </row>
+    <row r="73" spans="1:49" ht="15" thickBot="1">
+      <c r="A73" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:49" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A74" s="14" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="75" spans="1:49" ht="15">
+      <c r="A75" s="18" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19"/>
+      <c r="O75" s="18" t="s">
+        <v>1539</v>
+      </c>
+      <c r="P75" s="19"/>
+      <c r="Q75" s="19"/>
+      <c r="R75" s="19"/>
+      <c r="S75" s="19"/>
+      <c r="T75" s="19"/>
+      <c r="AE75" s="18" t="s">
+        <v>1558</v>
+      </c>
+      <c r="AF75" s="19"/>
+      <c r="AG75" s="19"/>
+      <c r="AH75" s="19"/>
+      <c r="AI75" s="19"/>
+      <c r="AJ75" s="19"/>
+      <c r="AP75" s="18" t="s">
+        <v>1574</v>
+      </c>
+      <c r="AQ75" s="19"/>
+      <c r="AR75" s="19"/>
+      <c r="AS75" s="19"/>
+      <c r="AT75" s="19"/>
+      <c r="AU75" s="19"/>
+      <c r="AV75" s="19"/>
+      <c r="AW75" s="19"/>
+    </row>
+    <row r="76" spans="1:49">
+      <c r="A76" s="11" t="s">
+        <v>1517</v>
+      </c>
+      <c r="O76" s="11" t="s">
+        <v>1540</v>
+      </c>
+      <c r="AE76" s="11" t="s">
+        <v>1559</v>
+      </c>
+      <c r="AP76" s="11" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="77" spans="1:49">
+      <c r="A77" s="11" t="s">
+        <v>1518</v>
+      </c>
+      <c r="O77" s="11" t="s">
+        <v>1541</v>
+      </c>
+      <c r="AE77" s="11" t="s">
+        <v>1560</v>
+      </c>
+      <c r="AP77" s="11" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="78" spans="1:49">
+      <c r="A78" s="11" t="s">
+        <v>1519</v>
+      </c>
+      <c r="O78" s="11" t="s">
+        <v>1542</v>
+      </c>
+      <c r="AE78" s="11" t="s">
+        <v>1561</v>
+      </c>
+      <c r="AP78" s="11" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="79" spans="1:49">
+      <c r="A79" s="13"/>
+      <c r="O79" s="13"/>
+      <c r="AE79" s="13"/>
+      <c r="AP79" s="13"/>
+    </row>
+    <row r="80" spans="1:49">
+      <c r="A80" s="11" t="s">
+        <v>1520</v>
+      </c>
+      <c r="O80" s="11" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AE80" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="AP80" s="11" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="81" spans="1:42">
+      <c r="A81" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="O81" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AE81" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AP81" s="11" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="82" spans="1:42">
+      <c r="A82" s="11" t="s">
+        <v>1521</v>
+      </c>
+      <c r="O82" s="11" t="s">
+        <v>1544</v>
+      </c>
+      <c r="AE82" s="11" t="s">
+        <v>1563</v>
+      </c>
+      <c r="AP82" s="11" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="83" spans="1:42">
+      <c r="A83" s="11" t="s">
+        <v>1522</v>
+      </c>
+      <c r="O83" s="11" t="s">
+        <v>1545</v>
+      </c>
+      <c r="AE83" s="11" t="s">
+        <v>1564</v>
+      </c>
+      <c r="AP83" s="11" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="84" spans="1:42">
+      <c r="A84" s="13"/>
+      <c r="O84" s="11" t="s">
+        <v>1546</v>
+      </c>
+      <c r="AE84" s="11" t="s">
+        <v>1565</v>
+      </c>
+      <c r="AP84" s="13"/>
+    </row>
+    <row r="85" spans="1:42">
+      <c r="A85" s="11" t="s">
+        <v>1523</v>
+      </c>
+      <c r="O85" s="11" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AE85" s="11" t="s">
+        <v>1566</v>
+      </c>
+      <c r="AP85" s="11" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="86" spans="1:42">
+      <c r="A86" s="11" t="s">
+        <v>1524</v>
+      </c>
+      <c r="O86" s="13"/>
+      <c r="AE86" s="13"/>
+      <c r="AP86" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:42">
+      <c r="A87" s="11" t="s">
+        <v>1525</v>
+      </c>
+      <c r="O87" s="11" t="s">
+        <v>1548</v>
+      </c>
+      <c r="AE87" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP87" s="11" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="88" spans="1:42">
+      <c r="A88" s="11" t="s">
+        <v>1526</v>
+      </c>
+      <c r="O88" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AE88" s="11" t="s">
+        <v>1567</v>
+      </c>
+      <c r="AP88" s="11" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="89" spans="1:42">
+      <c r="A89" s="11" t="s">
+        <v>1527</v>
+      </c>
+      <c r="O89" s="11" t="s">
+        <v>1549</v>
+      </c>
+      <c r="AE89" s="11" t="s">
+        <v>1568</v>
+      </c>
+      <c r="AP89" s="11" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="90" spans="1:42">
+      <c r="A90" s="13"/>
+      <c r="O90" s="11" t="s">
+        <v>1550</v>
+      </c>
+      <c r="AE90" s="11" t="s">
+        <v>1569</v>
+      </c>
+      <c r="AP90" s="13"/>
+    </row>
+    <row r="91" spans="1:42">
+      <c r="A91" s="11" t="s">
+        <v>1528</v>
+      </c>
+      <c r="O91" s="11" t="s">
+        <v>1551</v>
+      </c>
+      <c r="AE91" s="11" t="s">
+        <v>1570</v>
+      </c>
+      <c r="AP91" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="92" spans="1:42">
+      <c r="A92" s="11" t="s">
+        <v>1529</v>
+      </c>
+      <c r="O92" s="11" t="s">
+        <v>1552</v>
+      </c>
+      <c r="AE92" s="11" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="93" spans="1:42">
+      <c r="A93" s="11" t="s">
+        <v>1530</v>
+      </c>
+      <c r="O93" s="13"/>
+      <c r="AE93" s="11" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="94" spans="1:42">
+      <c r="A94" s="13"/>
+      <c r="O94" s="11" t="s">
+        <v>1553</v>
+      </c>
+      <c r="AE94" s="11" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="95" spans="1:42">
+      <c r="A95" s="11" t="s">
+        <v>1531</v>
+      </c>
+      <c r="O95" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AE95" s="13"/>
+    </row>
+    <row r="96" spans="1:42">
+      <c r="A96" s="11" t="s">
+        <v>1532</v>
+      </c>
+      <c r="O96" s="11" t="s">
+        <v>1554</v>
+      </c>
+      <c r="AE96" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28">
+      <c r="A97" s="11" t="s">
+        <v>1533</v>
+      </c>
+      <c r="O97" s="11" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28">
+      <c r="A98" s="11" t="s">
+        <v>1534</v>
+      </c>
+      <c r="O98" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28">
+      <c r="A99" s="11" t="s">
+        <v>1535</v>
+      </c>
+      <c r="O99" s="11" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28">
+      <c r="A100" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="O100" s="13"/>
+    </row>
+    <row r="101" spans="1:28">
+      <c r="A101" s="13"/>
+      <c r="O101" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28">
+      <c r="A102" s="11" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28">
+      <c r="A103" s="11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28">
+      <c r="A104" s="11" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28">
+      <c r="A105" s="11" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28">
+      <c r="A106" s="11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28">
+      <c r="A107" s="13"/>
+    </row>
+    <row r="108" spans="1:28">
+      <c r="A108" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" ht="15" thickBot="1"/>
+    <row r="110" spans="1:28" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A110" s="14" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" ht="15">
+      <c r="A111" s="18" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B111" s="19"/>
+      <c r="C111" s="19"/>
+      <c r="D111" s="19"/>
+      <c r="E111" s="19"/>
+      <c r="F111" s="19"/>
+      <c r="U111" s="18" t="s">
+        <v>1605</v>
+      </c>
+      <c r="V111" s="19"/>
+      <c r="W111" s="19"/>
+      <c r="X111" s="19"/>
+      <c r="Y111" s="19"/>
+      <c r="Z111" s="19"/>
+      <c r="AA111" s="19"/>
+      <c r="AB111" s="19"/>
+    </row>
+    <row r="112" spans="1:28">
+      <c r="A112" s="11" t="s">
+        <v>1588</v>
+      </c>
+      <c r="U112" s="11" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21">
+      <c r="A113" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="U113" s="11" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21">
+      <c r="A114" s="11" t="s">
+        <v>1590</v>
+      </c>
+      <c r="U114" s="11" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21">
+      <c r="A115" s="13"/>
+      <c r="U115" s="13"/>
+    </row>
+    <row r="116" spans="1:21">
+      <c r="A116" s="11" t="s">
+        <v>1591</v>
+      </c>
+      <c r="U116" s="11" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21">
+      <c r="A117" s="11" t="s">
+        <v>1592</v>
+      </c>
+      <c r="U117" s="11" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21">
+      <c r="A118" s="11" t="s">
+        <v>1593</v>
+      </c>
+      <c r="U118" s="11" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21">
+      <c r="A119" s="13"/>
+      <c r="U119" s="11" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21">
+      <c r="A120" s="11" t="s">
+        <v>1594</v>
+      </c>
+      <c r="U120" s="13"/>
+    </row>
+    <row r="121" spans="1:21">
+      <c r="A121" s="11" t="s">
+        <v>1595</v>
+      </c>
+      <c r="U121" s="11" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21">
+      <c r="A122" s="11" t="s">
+        <v>1596</v>
+      </c>
+      <c r="U122" s="11" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21">
+      <c r="A123" s="11" t="s">
+        <v>1597</v>
+      </c>
+      <c r="U123" s="11" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21">
+      <c r="A124" s="13"/>
+      <c r="U124" s="13"/>
+    </row>
+    <row r="125" spans="1:21">
+      <c r="A125" s="11" t="s">
+        <v>1598</v>
+      </c>
+      <c r="U125" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21">
+      <c r="A126" s="11" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21">
+      <c r="A127" s="11" t="s">
+        <v>1600</v>
+      </c>
+      <c r="U127" s="11" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21">
+      <c r="A128" s="13"/>
+      <c r="U128" s="11" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="129" spans="1:49">
+      <c r="A129" s="11" t="s">
+        <v>1601</v>
+      </c>
+      <c r="U129" s="13"/>
+    </row>
+    <row r="130" spans="1:49">
+      <c r="A130" s="11" t="s">
+        <v>1602</v>
+      </c>
+      <c r="U130" s="11" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="131" spans="1:49">
+      <c r="A131" s="11" t="s">
+        <v>1603</v>
+      </c>
+      <c r="U131" s="11" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="132" spans="1:49">
+      <c r="A132" s="11" t="s">
+        <v>1604</v>
+      </c>
+      <c r="U132" s="11" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="133" spans="1:49">
+      <c r="A133" s="13"/>
+      <c r="U133" s="13"/>
+    </row>
+    <row r="134" spans="1:49">
+      <c r="A134" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="U134" s="11" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="135" spans="1:49">
+      <c r="U135" s="11" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="136" spans="1:49" ht="15" thickBot="1"/>
+    <row r="137" spans="1:49" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A137" s="14" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="138" spans="1:49" ht="15">
+      <c r="A138" s="18" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B138" s="19"/>
+      <c r="C138" s="19"/>
+      <c r="D138" s="19"/>
+      <c r="E138" s="19"/>
+      <c r="F138" s="19"/>
+      <c r="G138" s="19"/>
+      <c r="H138" s="19"/>
+      <c r="O138" s="18" t="s">
+        <v>1644</v>
+      </c>
+      <c r="P138" s="19"/>
+      <c r="Q138" s="19"/>
+      <c r="R138" s="19"/>
+      <c r="S138" s="19"/>
+      <c r="T138" s="19"/>
+      <c r="U138" s="19"/>
+      <c r="V138" s="19"/>
+      <c r="W138" s="19"/>
+      <c r="AC138" s="18" t="s">
+        <v>1657</v>
+      </c>
+      <c r="AD138" s="19"/>
+      <c r="AE138" s="19"/>
+      <c r="AF138" s="19"/>
+      <c r="AG138" s="19"/>
+      <c r="AH138" s="19"/>
+      <c r="AI138" s="19"/>
+      <c r="AJ138" s="19"/>
+      <c r="AK138" s="19"/>
+    </row>
+    <row r="139" spans="1:49" ht="15">
+      <c r="A139" s="43" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B139" s="21"/>
+      <c r="C139" s="21"/>
+      <c r="D139" s="21"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="21"/>
+      <c r="G139" s="21"/>
+      <c r="O139" s="43" t="s">
+        <v>1645</v>
+      </c>
+      <c r="P139" s="21"/>
+      <c r="Q139" s="21"/>
+      <c r="R139" s="21"/>
+      <c r="S139" s="21"/>
+      <c r="T139" s="21"/>
+      <c r="AC139" s="43" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AD139" s="21"/>
+      <c r="AE139" s="21"/>
+      <c r="AF139" s="21"/>
+      <c r="AG139" s="21"/>
+      <c r="AR139" s="43" t="s">
+        <v>1672</v>
+      </c>
+      <c r="AS139" s="21"/>
+      <c r="AT139" s="21"/>
+      <c r="AU139" s="21"/>
+      <c r="AV139" s="21"/>
+      <c r="AW139" s="21"/>
+    </row>
+    <row r="140" spans="1:49">
+      <c r="B140" s="11" t="s">
+        <v>1623</v>
+      </c>
+      <c r="O140" s="11" t="s">
+        <v>1646</v>
+      </c>
+      <c r="AC140" s="11" t="s">
+        <v>1659</v>
+      </c>
+      <c r="AR140" s="11" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="141" spans="1:49">
+      <c r="B141" s="11" t="s">
+        <v>1624</v>
+      </c>
+      <c r="O141" s="11" t="s">
+        <v>1647</v>
+      </c>
+      <c r="AC141" s="11" t="s">
+        <v>1660</v>
+      </c>
+      <c r="AR141" s="11" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:49">
+      <c r="B142" s="11" t="s">
+        <v>1625</v>
+      </c>
+      <c r="O142" s="13"/>
+      <c r="AC142" s="11" t="s">
+        <v>1661</v>
+      </c>
+      <c r="AR142" s="11" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="143" spans="1:49">
+      <c r="B143" s="13"/>
+      <c r="O143" s="11" t="s">
+        <v>1226</v>
+      </c>
+      <c r="AC143" s="13"/>
+      <c r="AR143" s="13"/>
+    </row>
+    <row r="144" spans="1:49">
+      <c r="B144" s="11" t="s">
+        <v>1626</v>
+      </c>
+      <c r="O144" s="11" t="s">
+        <v>1648</v>
+      </c>
+      <c r="AC144" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="AR144" s="11" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="145" spans="2:44">
+      <c r="B145" s="11" t="s">
+        <v>1627</v>
+      </c>
+      <c r="O145" s="13"/>
+      <c r="AC145" s="11" t="s">
+        <v>1662</v>
+      </c>
+      <c r="AR145" s="11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="146" spans="2:44">
+      <c r="B146" s="11" t="s">
+        <v>1628</v>
+      </c>
+      <c r="O146" s="11" t="s">
+        <v>1649</v>
+      </c>
+      <c r="AC146" s="11" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AR146" s="11" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="147" spans="2:44">
+      <c r="B147" s="11" t="s">
+        <v>1493</v>
+      </c>
+      <c r="O147" s="11" t="s">
+        <v>1643</v>
+      </c>
+      <c r="AC147" s="11" t="s">
+        <v>1664</v>
+      </c>
+      <c r="AR147" s="11" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="148" spans="2:44">
+      <c r="B148" s="13"/>
+      <c r="O148" s="13"/>
+      <c r="AC148" s="13"/>
+      <c r="AR148" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="149" spans="2:44">
+      <c r="B149" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="O149" s="11" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AC149" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="AR149" s="11" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="150" spans="2:44">
+      <c r="O150" s="11" t="s">
+        <v>1651</v>
+      </c>
+      <c r="AC150" s="11" t="s">
+        <v>1666</v>
+      </c>
+      <c r="AR150" s="11" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="151" spans="2:44">
+      <c r="B151" s="11" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AC151" s="13"/>
+      <c r="AR151" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="152" spans="2:44" ht="15">
+      <c r="B152" s="11" t="s">
+        <v>1630</v>
+      </c>
+      <c r="O152" s="43" t="s">
+        <v>1652</v>
+      </c>
+      <c r="P152" s="21"/>
+      <c r="Q152" s="21"/>
+      <c r="R152" s="21"/>
+      <c r="S152" s="21"/>
+      <c r="T152" s="21"/>
+      <c r="AC152" s="11" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AR152" s="13"/>
+    </row>
+    <row r="153" spans="2:44">
+      <c r="B153" s="13"/>
+      <c r="AC153" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="AR153" s="11" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="154" spans="2:44">
+      <c r="B154" s="11" t="s">
+        <v>1631</v>
+      </c>
+      <c r="O154" s="11" t="s">
+        <v>1653</v>
+      </c>
+      <c r="AC154" s="11" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AR154" s="11" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="155" spans="2:44">
+      <c r="B155" s="11" t="s">
+        <v>1632</v>
+      </c>
+      <c r="O155" s="11" t="s">
+        <v>1654</v>
+      </c>
+      <c r="AC155" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="AR155" s="11" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="156" spans="2:44">
+      <c r="B156" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="O156" s="13"/>
+      <c r="AC156" s="11" t="s">
+        <v>1669</v>
+      </c>
+      <c r="AR156" s="13"/>
+    </row>
+    <row r="157" spans="2:44">
+      <c r="B157" s="11" t="s">
+        <v>1633</v>
+      </c>
+      <c r="O157" s="11" t="s">
+        <v>1655</v>
+      </c>
+      <c r="AC157" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AR157" s="11" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="158" spans="2:44">
+      <c r="B158" s="11" t="s">
+        <v>1634</v>
+      </c>
+      <c r="O158" s="11" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AC158" s="13"/>
+      <c r="AR158" s="11" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="159" spans="2:44">
+      <c r="B159" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC159" s="11" t="s">
+        <v>1670</v>
+      </c>
+      <c r="AR159" s="11" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="160" spans="2:44">
+      <c r="B160" s="11" t="s">
+        <v>1635</v>
+      </c>
+      <c r="AC160" s="11" t="s">
+        <v>1671</v>
+      </c>
+      <c r="AR160" s="13"/>
+    </row>
+    <row r="161" spans="1:44">
+      <c r="B161" s="11" t="s">
+        <v>1203</v>
+      </c>
+      <c r="AC161" s="13"/>
+      <c r="AR161" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="162" spans="1:44">
+      <c r="B162" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC162" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="163" spans="1:44">
+      <c r="B163" s="11" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="164" spans="1:44">
+      <c r="B164" s="11" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="165" spans="1:44">
+      <c r="B165" s="11" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="166" spans="1:44">
+      <c r="B166" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="168" spans="1:44" ht="15">
+      <c r="A168" s="43" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B168" s="21"/>
+      <c r="C168" s="21"/>
+      <c r="D168" s="21"/>
+      <c r="E168" s="21"/>
+      <c r="F168" s="21"/>
+      <c r="G168" s="21"/>
+      <c r="H168" s="21"/>
+      <c r="I168" s="21"/>
+      <c r="J168" s="21"/>
+      <c r="K168" s="21"/>
+    </row>
+    <row r="169" spans="1:44">
+      <c r="B169" s="11" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="170" spans="1:44">
+      <c r="B170" s="11" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="172" spans="1:44">
+      <c r="A172" s="13"/>
+      <c r="B172" s="11" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="173" spans="1:44">
+      <c r="B173" s="11" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="175" spans="1:44">
+      <c r="A175" s="13"/>
+      <c r="B175" s="11" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="176" spans="1:44" ht="15" thickBot="1">
+      <c r="B176" s="11" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="177" spans="1:45" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A177" s="14" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="178" spans="1:45" ht="15">
+      <c r="A178" s="18" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B178" s="19"/>
+      <c r="C178" s="19"/>
+      <c r="D178" s="19"/>
+      <c r="E178" s="19"/>
+      <c r="F178" s="19"/>
+      <c r="G178" s="19"/>
+      <c r="AF178" s="18" t="s">
+        <v>1710</v>
+      </c>
+      <c r="AG178" s="19"/>
+      <c r="AH178" s="19"/>
+      <c r="AI178" s="19"/>
+      <c r="AJ178" s="19"/>
+      <c r="AK178" s="19"/>
+      <c r="AL178" s="19"/>
+      <c r="AM178" s="19"/>
+      <c r="AN178" s="19"/>
+      <c r="AO178" s="19"/>
+      <c r="AP178" s="19"/>
+      <c r="AQ178" s="19"/>
+      <c r="AR178" s="19"/>
+      <c r="AS178" s="19"/>
+    </row>
+    <row r="179" spans="1:45">
+      <c r="A179" s="11" t="s">
+        <v>1689</v>
+      </c>
+      <c r="AF179" s="11" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="180" spans="1:45">
+      <c r="A180" s="11" t="s">
+        <v>1690</v>
+      </c>
+      <c r="AF180" s="11" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="181" spans="1:45">
+      <c r="A181" s="11" t="s">
+        <v>1691</v>
+      </c>
+      <c r="AF181" s="11" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="182" spans="1:45">
+      <c r="A182" s="13"/>
+      <c r="AF182" s="13"/>
+    </row>
+    <row r="183" spans="1:45">
+      <c r="A183" s="11" t="s">
+        <v>1692</v>
+      </c>
+      <c r="AF183" s="11" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="184" spans="1:45">
+      <c r="A184" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="AF184" s="11" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="185" spans="1:45">
+      <c r="A185" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="AF185" s="11" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="186" spans="1:45">
+      <c r="A186" s="11" t="s">
+        <v>1693</v>
+      </c>
+      <c r="AF186" s="11" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="187" spans="1:45">
+      <c r="A187" s="13"/>
+      <c r="AF187" s="11" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="188" spans="1:45">
+      <c r="A188" s="11" t="s">
+        <v>1694</v>
+      </c>
+      <c r="AF188" s="11" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="189" spans="1:45">
+      <c r="A189" s="11" t="s">
+        <v>1695</v>
+      </c>
+      <c r="AF189" s="11" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="190" spans="1:45">
+      <c r="A190" s="13"/>
+      <c r="AF190" s="11" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="191" spans="1:45">
+      <c r="A191" s="11" t="s">
+        <v>1696</v>
+      </c>
+      <c r="AF191" s="11" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="192" spans="1:45">
+      <c r="A192" s="11" t="s">
+        <v>1697</v>
+      </c>
+      <c r="AF192" s="13"/>
+    </row>
+    <row r="193" spans="1:32">
+      <c r="A193" s="13"/>
+      <c r="AF193" s="11" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="194" spans="1:32">
+      <c r="A194" s="11" t="s">
+        <v>1698</v>
+      </c>
+      <c r="AF194" s="11" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="195" spans="1:32">
+      <c r="A195" s="11" t="s">
+        <v>1699</v>
+      </c>
+      <c r="AF195" s="13"/>
+    </row>
+    <row r="196" spans="1:32">
+      <c r="A196" s="11" t="s">
+        <v>1700</v>
+      </c>
+      <c r="AF196" s="11" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="197" spans="1:32">
+      <c r="A197" s="13"/>
+      <c r="AF197" s="11" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="198" spans="1:32">
+      <c r="A198" s="11" t="s">
+        <v>1701</v>
+      </c>
+      <c r="AF198" s="11" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="199" spans="1:32">
+      <c r="A199" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF199" s="13"/>
+    </row>
+    <row r="200" spans="1:32">
+      <c r="A200" s="11" t="s">
+        <v>1702</v>
+      </c>
+      <c r="AF200" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="201" spans="1:32">
+      <c r="A201" s="11" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="202" spans="1:32">
+      <c r="A202" s="11" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="203" spans="1:32">
+      <c r="A203" s="11" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="204" spans="1:32">
+      <c r="A204" s="11" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="205" spans="1:32">
+      <c r="A205" s="13"/>
+    </row>
+    <row r="206" spans="1:32">
+      <c r="A206" s="11" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="207" spans="1:32">
+      <c r="A207" s="13"/>
+    </row>
+    <row r="208" spans="1:32">
+      <c r="A208" s="11" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="209" spans="1:77">
+      <c r="A209" s="11" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="210" spans="1:77">
+      <c r="A210" s="13"/>
+    </row>
+    <row r="211" spans="1:77">
+      <c r="A211" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="212" spans="1:77" ht="15" thickBot="1"/>
+    <row r="213" spans="1:77" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A213" s="14" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="214" spans="1:77" ht="15">
+      <c r="A214" s="18" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B214" s="19"/>
+      <c r="C214" s="19"/>
+      <c r="D214" s="19"/>
+      <c r="E214" s="19"/>
+      <c r="F214" s="19"/>
+      <c r="G214" s="19"/>
+      <c r="H214" s="19"/>
+      <c r="I214" s="19"/>
+      <c r="J214" s="19"/>
+      <c r="K214" s="19"/>
+      <c r="AB214" s="18" t="s">
+        <v>1748</v>
+      </c>
+      <c r="AC214" s="19"/>
+      <c r="AD214" s="19"/>
+      <c r="AE214" s="19"/>
+      <c r="AF214" s="19"/>
+      <c r="AG214" s="19"/>
+      <c r="AH214" s="19"/>
+      <c r="AI214" s="19"/>
+      <c r="AJ214" s="19"/>
+      <c r="AK214" s="19"/>
+      <c r="AL214" s="19"/>
+      <c r="AZ214" s="18" t="s">
+        <v>1770</v>
+      </c>
+      <c r="BA214" s="19"/>
+      <c r="BB214" s="19"/>
+      <c r="BC214" s="19"/>
+      <c r="BD214" s="19"/>
+      <c r="BE214" s="19"/>
+      <c r="BF214" s="19"/>
+      <c r="BG214" s="19"/>
+      <c r="BH214" s="19"/>
+      <c r="BY214" s="9" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="215" spans="1:77">
+      <c r="A215" s="11" t="s">
+        <v>1730</v>
+      </c>
+      <c r="AB215" s="11" t="s">
+        <v>1749</v>
+      </c>
+      <c r="AZ215" s="11" t="s">
+        <v>1771</v>
+      </c>
+      <c r="BY215" s="11" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="216" spans="1:77">
+      <c r="A216" s="11" t="s">
+        <v>1731</v>
+      </c>
+      <c r="AB216" s="11" t="s">
+        <v>1750</v>
+      </c>
+      <c r="AZ216" s="11" t="s">
+        <v>1772</v>
+      </c>
+      <c r="BY216" s="11" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="217" spans="1:77">
+      <c r="A217" s="11" t="s">
+        <v>1732</v>
+      </c>
+      <c r="AB217" s="11" t="s">
+        <v>1751</v>
+      </c>
+      <c r="AZ217" s="11" t="s">
+        <v>1773</v>
+      </c>
+      <c r="BY217" s="11" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="218" spans="1:77">
+      <c r="A218" s="13"/>
+      <c r="AB218" s="13"/>
+      <c r="AZ218" s="13"/>
+      <c r="BY218" s="13"/>
+    </row>
+    <row r="219" spans="1:77">
+      <c r="A219" s="11" t="s">
+        <v>1733</v>
+      </c>
+      <c r="AB219" s="11" t="s">
+        <v>1752</v>
+      </c>
+      <c r="AZ219" s="11" t="s">
+        <v>1774</v>
+      </c>
+      <c r="BY219" s="11" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="220" spans="1:77">
+      <c r="A220" s="11" t="s">
+        <v>1734</v>
+      </c>
+      <c r="AB220" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ220" s="13"/>
+      <c r="BY220" s="13"/>
+    </row>
+    <row r="221" spans="1:77">
+      <c r="A221" s="11" t="s">
+        <v>1735</v>
+      </c>
+      <c r="AB221" s="11" t="s">
+        <v>1753</v>
+      </c>
+      <c r="AZ221" s="11" t="s">
+        <v>1775</v>
+      </c>
+      <c r="BY221" s="11" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="222" spans="1:77">
+      <c r="A222" s="13"/>
+      <c r="AB222" s="11" t="s">
+        <v>1535</v>
+      </c>
+      <c r="AZ222" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="BY222" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="223" spans="1:77">
+      <c r="A223" s="11" t="s">
+        <v>1736</v>
+      </c>
+      <c r="AB223" s="11" t="s">
+        <v>1754</v>
+      </c>
+      <c r="AZ223" s="11" t="s">
+        <v>1776</v>
+      </c>
+      <c r="BY223" s="11" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="224" spans="1:77">
+      <c r="A224" s="11" t="s">
+        <v>1737</v>
+      </c>
+      <c r="AB224" s="11" t="s">
+        <v>1755</v>
+      </c>
+      <c r="AZ224" s="11" t="s">
+        <v>1777</v>
+      </c>
+      <c r="BY224" s="11" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="225" spans="1:77">
+      <c r="A225" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="AB225" s="13"/>
+      <c r="AZ225" s="11" t="s">
+        <v>1778</v>
+      </c>
+      <c r="BY225" s="11" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="226" spans="1:77">
+      <c r="A226" s="11" t="s">
+        <v>1739</v>
+      </c>
+      <c r="AB226" s="11" t="s">
+        <v>1756</v>
+      </c>
+      <c r="AZ226" s="11" t="s">
+        <v>1779</v>
+      </c>
+      <c r="BY226" s="11" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="227" spans="1:77">
+      <c r="A227" s="11" t="s">
+        <v>1740</v>
+      </c>
+      <c r="AB227" s="11" t="s">
+        <v>1757</v>
+      </c>
+      <c r="AZ227" s="11" t="s">
+        <v>1780</v>
+      </c>
+      <c r="BY227" s="13"/>
+    </row>
+    <row r="228" spans="1:77">
+      <c r="A228" s="13"/>
+      <c r="AB228" s="11" t="s">
+        <v>1758</v>
+      </c>
+      <c r="AZ228" s="11" t="s">
+        <v>1781</v>
+      </c>
+      <c r="BY228" s="11" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="229" spans="1:77">
+      <c r="A229" s="11" t="s">
+        <v>1741</v>
+      </c>
+      <c r="AB229" s="13"/>
+      <c r="AZ229" s="13"/>
+      <c r="BY229" s="11" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="230" spans="1:77">
+      <c r="A230" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB230" s="11" t="s">
+        <v>1759</v>
+      </c>
+      <c r="AZ230" s="11" t="s">
+        <v>1782</v>
+      </c>
+      <c r="BY230" s="11" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="231" spans="1:77">
+      <c r="A231" s="11" t="s">
+        <v>1742</v>
+      </c>
+      <c r="AB231" s="11" t="s">
+        <v>1760</v>
+      </c>
+      <c r="AZ231" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="BY231" s="11" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="232" spans="1:77">
+      <c r="A232" s="11" t="s">
+        <v>1743</v>
+      </c>
+      <c r="AB232" s="11" t="s">
+        <v>1761</v>
+      </c>
+      <c r="AZ232" s="11" t="s">
+        <v>1783</v>
+      </c>
+      <c r="BY232" s="11" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="233" spans="1:77">
+      <c r="A233" s="11" t="s">
+        <v>1744</v>
+      </c>
+      <c r="AB233" s="13"/>
+      <c r="AZ233" s="11" t="s">
+        <v>1784</v>
+      </c>
+      <c r="BY233" s="13"/>
+    </row>
+    <row r="234" spans="1:77">
+      <c r="A234" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="AB234" s="11" t="s">
+        <v>1762</v>
+      </c>
+      <c r="AZ234" s="11" t="s">
+        <v>1785</v>
+      </c>
+      <c r="BY234" s="11" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="235" spans="1:77">
+      <c r="A235" s="11" t="s">
+        <v>1746</v>
+      </c>
+      <c r="AB235" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ235" s="11" t="s">
+        <v>1786</v>
+      </c>
+      <c r="BY235" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="236" spans="1:77">
+      <c r="A236" s="13"/>
+      <c r="AB236" s="11" t="s">
+        <v>1763</v>
+      </c>
+      <c r="AZ236" s="11" t="s">
+        <v>1787</v>
+      </c>
+      <c r="BY236" s="11" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="237" spans="1:77">
+      <c r="A237" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="AB237" s="11" t="s">
+        <v>1764</v>
+      </c>
+      <c r="AZ237" s="11" t="s">
+        <v>1788</v>
+      </c>
+      <c r="BY237" s="11" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="238" spans="1:77">
+      <c r="A238" s="13"/>
+      <c r="AB238" s="11" t="s">
+        <v>1765</v>
+      </c>
+      <c r="AZ238" s="13"/>
+      <c r="BY238" s="13"/>
+    </row>
+    <row r="239" spans="1:77">
+      <c r="A239" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB239" s="11" t="s">
+        <v>1766</v>
+      </c>
+      <c r="AZ239" s="11" t="s">
+        <v>1789</v>
+      </c>
+      <c r="BY239" s="11" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="240" spans="1:77">
+      <c r="AB240" s="13"/>
+      <c r="AZ240" s="11" t="s">
+        <v>1790</v>
+      </c>
+      <c r="BY240" s="11" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="241" spans="1:77">
+      <c r="AB241" s="11" t="s">
+        <v>1767</v>
+      </c>
+      <c r="AZ241" s="11" t="s">
+        <v>1791</v>
+      </c>
+      <c r="BY241" s="11" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="242" spans="1:77">
+      <c r="AB242" s="11" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AZ242" s="11" t="s">
+        <v>1792</v>
+      </c>
+      <c r="BY242" s="11" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="243" spans="1:77">
+      <c r="AB243" s="11" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AZ243" s="11" t="s">
+        <v>1793</v>
+      </c>
+      <c r="BY243" s="13"/>
+    </row>
+    <row r="244" spans="1:77">
+      <c r="AB244" s="13"/>
+      <c r="AZ244" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="BY244" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="245" spans="1:77">
+      <c r="AB245" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ245" s="11" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="246" spans="1:77">
+      <c r="AZ246" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="247" spans="1:77">
+      <c r="AZ247" s="13"/>
+    </row>
+    <row r="248" spans="1:77">
+      <c r="AZ248" s="11" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="249" spans="1:77">
+      <c r="AZ249" s="11" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="250" spans="1:77">
+      <c r="AZ250" s="11" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="251" spans="1:77">
+      <c r="AZ251" s="13"/>
+    </row>
+    <row r="252" spans="1:77">
+      <c r="AZ252" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="253" spans="1:77" ht="15" thickBot="1"/>
+    <row r="254" spans="1:77" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A254" s="14" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="255" spans="1:77" ht="15">
+      <c r="A255" s="18" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B255" s="19"/>
+      <c r="C255" s="19"/>
+      <c r="D255" s="19"/>
+      <c r="E255" s="19"/>
+      <c r="F255" s="19"/>
+      <c r="G255" s="19"/>
+      <c r="H255" s="19"/>
+      <c r="I255" s="19"/>
+      <c r="R255" s="18" t="s">
+        <v>1832</v>
+      </c>
+      <c r="S255" s="19"/>
+      <c r="T255" s="19"/>
+      <c r="U255" s="19"/>
+      <c r="V255" s="19"/>
+      <c r="W255" s="19"/>
+      <c r="X255" s="19"/>
+      <c r="Y255" s="19"/>
+      <c r="AE255" s="18" t="s">
+        <v>1851</v>
+      </c>
+      <c r="AF255" s="19"/>
+      <c r="AG255" s="19"/>
+      <c r="AH255" s="19"/>
+      <c r="AI255" s="19"/>
+      <c r="AJ255" s="19"/>
+      <c r="AK255" s="19"/>
+      <c r="AL255" s="19"/>
+      <c r="AM255" s="19"/>
+      <c r="AN255" s="19"/>
+      <c r="AO255" s="19"/>
+      <c r="AU255" s="18" t="s">
+        <v>1859</v>
+      </c>
+      <c r="AV255" s="19"/>
+      <c r="AW255" s="19"/>
+      <c r="AX255" s="19"/>
+      <c r="AY255" s="19"/>
+      <c r="AZ255" s="19"/>
+      <c r="BA255" s="19"/>
+    </row>
+    <row r="256" spans="1:77" ht="15">
+      <c r="A256" s="43" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B256" s="21"/>
+      <c r="R256" s="43" t="s">
+        <v>1833</v>
+      </c>
+      <c r="S256" s="21"/>
+      <c r="T256" s="21"/>
+      <c r="AE256" s="43" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AF256" s="21"/>
+      <c r="AG256" s="21"/>
+      <c r="AH256" s="21"/>
+      <c r="AU256" s="43" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AV256" s="21"/>
+      <c r="AW256" s="21"/>
+      <c r="AX256" s="21"/>
+    </row>
+    <row r="257" spans="1:51" ht="15">
+      <c r="A257" s="11" t="s">
+        <v>1186</v>
+      </c>
+      <c r="R257" s="11" t="s">
+        <v>1834</v>
+      </c>
+      <c r="AE257" s="11" t="s">
+        <v>1853</v>
+      </c>
+      <c r="AU257" s="17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="258" spans="1:51">
+      <c r="A258" s="16" t="s">
+        <v>1822</v>
+      </c>
+      <c r="R258" s="11" t="s">
+        <v>1835</v>
+      </c>
+      <c r="AE258" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="AU258" s="13"/>
+    </row>
+    <row r="259" spans="1:51">
+      <c r="A259" s="13"/>
+      <c r="R259" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE259" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU259" s="11" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="260" spans="1:51">
+      <c r="A260" s="11" t="s">
+        <v>1823</v>
+      </c>
+      <c r="R260" s="11" t="s">
+        <v>1836</v>
+      </c>
+      <c r="AU260" s="11" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="261" spans="1:51" ht="15">
+      <c r="A261" s="11" t="s">
+        <v>1824</v>
+      </c>
+      <c r="R261" s="11" t="s">
+        <v>1837</v>
+      </c>
+      <c r="AE261" s="43" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AF261" s="21"/>
+      <c r="AG261" s="21"/>
+      <c r="AH261" s="21"/>
+    </row>
+    <row r="262" spans="1:51" ht="15">
+      <c r="A262" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="R262" s="13"/>
+      <c r="AE262" s="11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="AU262" s="43" t="s">
+        <v>1862</v>
+      </c>
+      <c r="AV262" s="21"/>
+      <c r="AW262" s="21"/>
+      <c r="AX262" s="21"/>
+      <c r="AY262" s="21"/>
+    </row>
+    <row r="263" spans="1:51" ht="15">
+      <c r="R263" s="11" t="s">
+        <v>1838</v>
+      </c>
+      <c r="AE263" s="11" t="s">
+        <v>1857</v>
+      </c>
+      <c r="AU263" s="17" t="s">
+        <v>1863</v>
+      </c>
+      <c r="AV263" s="40"/>
+      <c r="AW263" s="40"/>
+    </row>
+    <row r="264" spans="1:51" ht="15">
+      <c r="A264" s="43" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B264" s="21"/>
+      <c r="C264" s="21"/>
+      <c r="R264" s="11" t="s">
+        <v>1839</v>
+      </c>
+      <c r="AE264" s="11" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AU264" s="17" t="s">
+        <v>1864</v>
+      </c>
+      <c r="AV264" s="40"/>
+      <c r="AW264" s="40"/>
+    </row>
+    <row r="265" spans="1:51" ht="15">
+      <c r="A265" s="11" t="s">
+        <v>1186</v>
+      </c>
+      <c r="R265" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AU265" s="17" t="s">
+        <v>1865</v>
+      </c>
+      <c r="AV265" s="40"/>
+      <c r="AW265" s="40"/>
+    </row>
+    <row r="266" spans="1:51" ht="15">
+      <c r="A266" s="16" t="s">
+        <v>1826</v>
+      </c>
+      <c r="R266" s="11" t="s">
+        <v>1840</v>
+      </c>
+      <c r="AU266" s="17" t="s">
+        <v>1866</v>
+      </c>
+      <c r="AV266" s="40"/>
+      <c r="AW266" s="40"/>
+    </row>
+    <row r="267" spans="1:51" ht="15">
+      <c r="A267" s="13"/>
+      <c r="R267" s="11" t="s">
+        <v>1841</v>
+      </c>
+      <c r="AU267" s="17" t="s">
+        <v>1867</v>
+      </c>
+      <c r="AV267" s="40"/>
+      <c r="AW267" s="40"/>
+    </row>
+    <row r="268" spans="1:51" ht="15">
+      <c r="A268" s="11" t="s">
+        <v>1827</v>
+      </c>
+      <c r="AU268" s="17" t="s">
+        <v>1868</v>
+      </c>
+      <c r="AV268" s="40"/>
+      <c r="AW268" s="40"/>
+    </row>
+    <row r="269" spans="1:51" ht="15">
+      <c r="A269" s="13"/>
+      <c r="R269" s="43" t="s">
+        <v>1842</v>
+      </c>
+      <c r="S269" s="21"/>
+      <c r="T269" s="21"/>
+      <c r="U269" s="21"/>
+      <c r="AU269" s="13"/>
+    </row>
+    <row r="270" spans="1:51" ht="15">
+      <c r="A270" s="11" t="s">
+        <v>1828</v>
+      </c>
+      <c r="R270" s="11" t="s">
+        <v>1834</v>
+      </c>
+      <c r="AU270" s="34" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="271" spans="1:51" ht="15">
+      <c r="A271" s="11" t="s">
+        <v>1829</v>
+      </c>
+      <c r="R271" s="11" t="s">
+        <v>1843</v>
+      </c>
+      <c r="AU271" s="34" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="272" spans="1:51" ht="15">
+      <c r="A272" s="11" t="s">
+        <v>1830</v>
+      </c>
+      <c r="R272" s="11" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AU272" s="34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="273" spans="1:47" ht="15">
+      <c r="A273" s="13"/>
+      <c r="R273" s="13"/>
+      <c r="AU273" s="34" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="274" spans="1:47">
+      <c r="A274" s="11" t="s">
+        <v>1831</v>
+      </c>
+      <c r="R274" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="275" spans="1:47">
+      <c r="A275" s="11" t="s">
+        <v>1824</v>
+      </c>
+      <c r="R275" s="11" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="276" spans="1:47">
+      <c r="A276" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="R276" s="13"/>
+    </row>
+    <row r="277" spans="1:47">
+      <c r="R277" s="11" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="278" spans="1:47">
+      <c r="R278" s="11" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="279" spans="1:47">
+      <c r="R279" s="11" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="280" spans="1:47">
+      <c r="R280" s="13"/>
+    </row>
+    <row r="281" spans="1:47">
+      <c r="R281" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="282" spans="1:47">
+      <c r="R282" s="13"/>
+    </row>
+    <row r="283" spans="1:47">
+      <c r="R283" s="11" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="284" spans="1:47">
+      <c r="R284" s="11" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="285" spans="1:47">
+      <c r="R285" s="11" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="286" spans="1:47">
+      <c r="R286" s="13"/>
+    </row>
+    <row r="287" spans="1:47">
+      <c r="R287" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="288" spans="1:47">
+      <c r="R288" s="11" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="289" spans="1:44">
+      <c r="R289" s="13"/>
+    </row>
+    <row r="290" spans="1:44">
+      <c r="R290" s="11" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="291" spans="1:44">
+      <c r="R291" s="11" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="292" spans="1:44">
+      <c r="R292" s="11" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="293" spans="1:44" ht="15" thickBot="1">
+      <c r="R293" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="294" spans="1:44" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A294" s="14" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="295" spans="1:44" ht="15">
+      <c r="A295" s="9" t="s">
+        <v>1871</v>
+      </c>
+      <c r="T295" s="9" t="s">
+        <v>1908</v>
+      </c>
+      <c r="AR295" s="9" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="296" spans="1:44">
+      <c r="A296" s="11" t="s">
+        <v>1872</v>
+      </c>
+      <c r="T296" s="11" t="s">
+        <v>1909</v>
+      </c>
+      <c r="AR296" s="11" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="297" spans="1:44">
+      <c r="A297" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="T297" s="11" t="s">
+        <v>1910</v>
+      </c>
+      <c r="AR297" s="11" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="298" spans="1:44">
+      <c r="A298" s="11" t="s">
+        <v>1874</v>
+      </c>
+      <c r="T298" s="11" t="s">
+        <v>1911</v>
+      </c>
+      <c r="AR298" s="11" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="299" spans="1:44">
+      <c r="A299" s="13"/>
+      <c r="T299" s="13"/>
+      <c r="AR299" s="13"/>
+    </row>
+    <row r="300" spans="1:44">
+      <c r="A300" s="11" t="s">
+        <v>1875</v>
+      </c>
+      <c r="T300" s="11" t="s">
+        <v>1912</v>
+      </c>
+      <c r="AR300" s="11" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="301" spans="1:44">
+      <c r="A301" s="11" t="s">
+        <v>1876</v>
+      </c>
+      <c r="T301" s="13"/>
+      <c r="AR301" s="11" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="302" spans="1:44">
+      <c r="A302" s="13"/>
+      <c r="T302" s="11" t="s">
+        <v>1528</v>
+      </c>
+      <c r="AR302" s="11" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="303" spans="1:44">
+      <c r="A303" s="11" t="s">
+        <v>1877</v>
+      </c>
+      <c r="T303" s="11" t="s">
+        <v>1913</v>
+      </c>
+      <c r="AR303" s="13"/>
+    </row>
+    <row r="304" spans="1:44">
+      <c r="A304" s="11" t="s">
+        <v>1878</v>
+      </c>
+      <c r="T304" s="11" t="s">
+        <v>1914</v>
+      </c>
+      <c r="AR304" s="11" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="305" spans="1:44">
+      <c r="A305" s="11" t="s">
+        <v>1879</v>
+      </c>
+      <c r="T305" s="11" t="s">
+        <v>1915</v>
+      </c>
+      <c r="AR305" s="11" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="306" spans="1:44">
+      <c r="A306" s="11" t="s">
+        <v>1880</v>
+      </c>
+      <c r="T306" s="13"/>
+      <c r="AR306" s="11" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="307" spans="1:44">
+      <c r="A307" s="11" t="s">
+        <v>1881</v>
+      </c>
+      <c r="T307" s="11" t="s">
+        <v>1741</v>
+      </c>
+      <c r="AR307" s="11" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="308" spans="1:44">
+      <c r="A308" s="13"/>
+      <c r="T308" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AR308" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="309" spans="1:44">
+      <c r="A309" s="11" t="s">
+        <v>1882</v>
+      </c>
+      <c r="T309" s="11" t="s">
+        <v>1916</v>
+      </c>
+      <c r="AR309" s="11" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="310" spans="1:44">
+      <c r="A310" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="T310" s="11" t="s">
+        <v>1917</v>
+      </c>
+      <c r="AR310" s="11" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="311" spans="1:44">
+      <c r="A311" s="11" t="s">
+        <v>1883</v>
+      </c>
+      <c r="T311" s="11" t="s">
+        <v>1918</v>
+      </c>
+      <c r="AR311" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="312" spans="1:44">
+      <c r="A312" s="11" t="s">
+        <v>1884</v>
+      </c>
+      <c r="T312" s="11" t="s">
+        <v>1919</v>
+      </c>
+      <c r="AR312" s="13"/>
+    </row>
+    <row r="313" spans="1:44">
+      <c r="A313" s="11" t="s">
+        <v>1885</v>
+      </c>
+      <c r="T313" s="11" t="s">
+        <v>1920</v>
+      </c>
+      <c r="AR313" s="11" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="314" spans="1:44">
+      <c r="A314" s="11" t="s">
+        <v>1886</v>
+      </c>
+      <c r="T314" s="11" t="s">
+        <v>1921</v>
+      </c>
+      <c r="AR314" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="315" spans="1:44">
+      <c r="A315" s="11" t="s">
+        <v>1887</v>
+      </c>
+      <c r="T315" s="13"/>
+      <c r="AR315" s="11" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="316" spans="1:44">
+      <c r="A316" s="13"/>
+      <c r="T316" s="11" t="s">
+        <v>1922</v>
+      </c>
+      <c r="AR316" s="11" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="317" spans="1:44">
+      <c r="A317" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="T317" s="11" t="s">
+        <v>1923</v>
+      </c>
+      <c r="AR317" s="11" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="318" spans="1:44">
+      <c r="A318" s="11" t="s">
+        <v>1888</v>
+      </c>
+      <c r="T318" s="11" t="s">
+        <v>1924</v>
+      </c>
+      <c r="AR318" s="11" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="319" spans="1:44">
+      <c r="A319" s="11" t="s">
+        <v>1884</v>
+      </c>
+      <c r="T319" s="11" t="s">
+        <v>1925</v>
+      </c>
+      <c r="AR319" s="11" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="320" spans="1:44">
+      <c r="A320" s="11" t="s">
+        <v>1889</v>
+      </c>
+      <c r="T320" s="13"/>
+      <c r="AR320" s="13"/>
+    </row>
+    <row r="321" spans="1:44">
+      <c r="A321" s="11" t="s">
+        <v>1890</v>
+      </c>
+      <c r="T321" s="11" t="s">
+        <v>1926</v>
+      </c>
+      <c r="AR321" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="322" spans="1:44">
+      <c r="A322" s="13"/>
+      <c r="T322" s="11" t="s">
+        <v>1927</v>
+      </c>
+      <c r="AR322" s="11" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="323" spans="1:44">
+      <c r="A323" s="11" t="s">
+        <v>1891</v>
+      </c>
+      <c r="T323" s="11" t="s">
+        <v>1928</v>
+      </c>
+      <c r="AR323" s="11" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="324" spans="1:44">
+      <c r="A324" s="11" t="s">
+        <v>1892</v>
+      </c>
+      <c r="T324" s="11" t="s">
+        <v>1929</v>
+      </c>
+      <c r="AR324" s="11" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="325" spans="1:44">
+      <c r="A325" s="11" t="s">
+        <v>1893</v>
+      </c>
+      <c r="T325" s="11" t="s">
+        <v>1930</v>
+      </c>
+      <c r="AR325" s="11" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="326" spans="1:44">
+      <c r="A326" s="11" t="s">
+        <v>1894</v>
+      </c>
+      <c r="T326" s="11" t="s">
+        <v>1931</v>
+      </c>
+      <c r="AR326" s="13"/>
+    </row>
+    <row r="327" spans="1:44">
+      <c r="A327" s="11" t="s">
+        <v>1895</v>
+      </c>
+      <c r="T327" s="13"/>
+      <c r="AR327" s="11" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="328" spans="1:44">
+      <c r="A328" s="11" t="s">
+        <v>1896</v>
+      </c>
+      <c r="T328" s="11" t="s">
+        <v>1932</v>
+      </c>
+      <c r="AR328" s="11" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="329" spans="1:44">
+      <c r="A329" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="T329" s="11" t="s">
+        <v>1933</v>
+      </c>
+      <c r="AR329" s="11" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="330" spans="1:44">
+      <c r="A330" s="11" t="s">
+        <v>1897</v>
+      </c>
+      <c r="T330" s="11" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AR330" s="11" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="331" spans="1:44">
+      <c r="A331" s="11" t="s">
+        <v>1898</v>
+      </c>
+      <c r="T331" s="11" t="s">
+        <v>1935</v>
+      </c>
+      <c r="AR331" s="11" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="332" spans="1:44">
+      <c r="A332" s="11" t="s">
+        <v>1899</v>
+      </c>
+      <c r="T332" s="11" t="s">
+        <v>1936</v>
+      </c>
+      <c r="AR332" s="11" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="333" spans="1:44">
+      <c r="A333" s="13"/>
+      <c r="T333" s="13"/>
+      <c r="AR333" s="11" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="334" spans="1:44">
+      <c r="A334" s="11" t="s">
+        <v>1900</v>
+      </c>
+      <c r="T334" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AR334" s="11" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="335" spans="1:44">
+      <c r="A335" s="11" t="s">
+        <v>1901</v>
+      </c>
+      <c r="AR335" s="11" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="336" spans="1:44">
+      <c r="A336" s="11" t="s">
+        <v>1902</v>
+      </c>
+      <c r="AR336" s="13"/>
+    </row>
+    <row r="337" spans="1:44">
+      <c r="A337" s="13"/>
+      <c r="AR337" s="11" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="338" spans="1:44">
+      <c r="A338" s="11" t="s">
+        <v>1903</v>
+      </c>
+      <c r="AR338" s="11" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="339" spans="1:44">
+      <c r="A339" s="11" t="s">
+        <v>1904</v>
+      </c>
+      <c r="AR339" s="11" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="340" spans="1:44">
+      <c r="A340" s="11" t="s">
+        <v>1905</v>
+      </c>
+      <c r="AR340" s="11" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="341" spans="1:44">
+      <c r="A341" s="13"/>
+      <c r="AR341" s="13"/>
+    </row>
+    <row r="342" spans="1:44">
+      <c r="A342" s="11" t="s">
+        <v>1906</v>
+      </c>
+      <c r="AR342" s="11" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="343" spans="1:44">
+      <c r="A343" s="11" t="s">
+        <v>1907</v>
+      </c>
+      <c r="AR343" s="11" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="344" spans="1:44">
+      <c r="A344" s="13"/>
+      <c r="AR344" s="11" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="345" spans="1:44">
+      <c r="A345" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AR345" s="11" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="346" spans="1:44">
+      <c r="AR346" s="11" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="347" spans="1:44">
+      <c r="AR347" s="13"/>
+    </row>
+    <row r="348" spans="1:44" ht="15" thickBot="1">
+      <c r="AR348" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="349" spans="1:44" s="15" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A349" s="14" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="350" spans="1:44" ht="15">
+      <c r="A350" s="18" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B350" s="19"/>
+      <c r="C350" s="19"/>
+      <c r="D350" s="19"/>
+      <c r="E350" s="19"/>
+      <c r="F350" s="19"/>
+      <c r="G350" s="19"/>
+      <c r="H350" s="19"/>
+      <c r="N350" s="18" t="s">
+        <v>1987</v>
+      </c>
+      <c r="O350" s="19"/>
+      <c r="P350" s="19"/>
+      <c r="Q350" s="19"/>
+      <c r="R350" s="19"/>
+      <c r="S350" s="19"/>
+      <c r="T350" s="19"/>
+      <c r="U350" s="19"/>
+      <c r="V350" s="19"/>
+    </row>
+    <row r="351" spans="1:44">
+      <c r="A351" s="11" t="s">
+        <v>1976</v>
+      </c>
+      <c r="N351" s="11" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="352" spans="1:44">
+      <c r="A352" s="11" t="s">
+        <v>1977</v>
+      </c>
+      <c r="N352" s="11" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="353" spans="1:14">
+      <c r="A353" s="11" t="s">
+        <v>1978</v>
+      </c>
+      <c r="N353" s="11" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14">
+      <c r="A354" s="13"/>
+      <c r="N354" s="11" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14">
+      <c r="A355" s="11" t="s">
+        <v>1979</v>
+      </c>
+      <c r="N355" s="11" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14">
+      <c r="A356" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="N356" s="11" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14">
+      <c r="A357" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="N357" s="11" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14">
+      <c r="A358" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="N358" s="13"/>
+    </row>
+    <row r="359" spans="1:14">
+      <c r="A359" s="13"/>
+      <c r="N359" s="11" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14">
+      <c r="A360" s="11" t="s">
+        <v>1980</v>
+      </c>
+      <c r="N360" s="11" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14">
+      <c r="A361" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="N361" s="13"/>
+    </row>
+    <row r="362" spans="1:14">
+      <c r="A362" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="N362" s="11" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14">
+      <c r="A363" s="13"/>
+      <c r="N363" s="11" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14">
+      <c r="A364" s="11" t="s">
+        <v>1982</v>
+      </c>
+      <c r="N364" s="11" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14">
+      <c r="A365" s="11" t="s">
+        <v>1983</v>
+      </c>
+      <c r="N365" s="11" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14">
+      <c r="A366" s="11" t="s">
+        <v>1984</v>
+      </c>
+      <c r="N366" s="11" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14">
+      <c r="A367" s="13"/>
+      <c r="N367" s="11" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14">
+      <c r="A368" s="11" t="s">
+        <v>1985</v>
+      </c>
+      <c r="N368" s="11" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14">
+      <c r="A369" s="11" t="s">
+        <v>1986</v>
+      </c>
+      <c r="N369" s="11" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14">
+      <c r="A370" s="13"/>
+      <c r="N370" s="11" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14">
+      <c r="A371" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="N371" s="11" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14">
+      <c r="N372" s="11" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14">
+      <c r="N373" s="11" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14">
+      <c r="N374" s="11" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14">
+      <c r="N375" s="11" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14">
+      <c r="N376" s="11" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14">
+      <c r="N377" s="11" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14">
+      <c r="N378" s="11" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14">
+      <c r="N379" s="11" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14">
+      <c r="N380" s="11" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14">
+      <c r="N381" s="11" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14">
+      <c r="N382" s="11" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14">
+      <c r="N383" s="11" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14">
+      <c r="N384" s="13"/>
+    </row>
+    <row r="385" spans="14:14">
+      <c r="N385" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>